--- a/kronshtatsky/ceilling/ceilling-k.xlsx
+++ b/kronshtatsky/ceilling/ceilling-k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10128" firstSheet="3" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10128" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="CF1" sheetId="4" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="3.1-CF2_Монтаж" sheetId="3" r:id="rId4"/>
     <sheet name="2.2-CF1_Краск" sheetId="6" r:id="rId5"/>
     <sheet name="1.2-CF1_СКБ" sheetId="7" r:id="rId6"/>
+    <sheet name="3.2-CF3_Монтаж" sheetId="8" r:id="rId7"/>
+    <sheet name="3.3-CF4_Монтаж" sheetId="9" r:id="rId8"/>
+    <sheet name="4.1-WD6 5" sheetId="10" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="173">
   <si>
     <t>Спецификация выполненных работ</t>
   </si>
@@ -509,6 +512,45 @@
   </si>
   <si>
     <t>1, 2, 3 этажи. Шпаклевка базовая до 5 мм. Тип: CF1; CF13</t>
+  </si>
+  <si>
+    <t>Монтаж подвесного потолка СКБ / типа Армстронг, Грильято</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип: CF3. Потолки Грильято ячейки 100х100 АЛБЕС Белый</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип: CF4. Потолочная плита Рокфон Школа A15 1200х600х20</t>
+  </si>
+  <si>
+    <t>1.12</t>
+  </si>
+  <si>
+    <t>3.35</t>
+  </si>
+  <si>
+    <t>3.33</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Зашивка приборов отопления / ГВЛВ / в 2 слоя на каркасе</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип:WD5. Зашивка вертикальных труб отопления ГKЛ тип С112 по серии Knauf толщиной 52мм. Двуслойная обшивка из КНАУФ-листов ГСП-А 12.5мм с одной стороны на одинарном металлическом каркасе из профиля ПП 60x27 Knauf.</t>
+  </si>
+  <si>
+    <t>wd6</t>
+  </si>
+  <si>
+    <t>wd5</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип:WD6. ГКЛ 2 слоя КНАУФ-Файерборд (толщина 12,5 мм) на металлическом каркасе с решеткой для воздухообмена.</t>
   </si>
 </sst>
 </file>
@@ -768,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -834,6 +876,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -855,30 +921,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -887,6 +929,45 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1293,36 +1374,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1334,18 +1415,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1355,17 +1436,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -1377,7 +1458,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -1387,7 +1468,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="27"/>
+      <c r="H5" s="35"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -1408,7 +1489,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -1418,7 +1499,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="27"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -1439,7 +1520,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -1449,7 +1530,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="27"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -1470,7 +1551,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -1480,7 +1561,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="27"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -1501,7 +1582,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -1511,7 +1592,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="27"/>
+      <c r="H9" s="35"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -1532,7 +1613,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -1542,7 +1623,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="35"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -1563,7 +1644,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -1573,7 +1654,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="27"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -1594,7 +1675,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -1604,7 +1685,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="27"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -1625,7 +1706,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -1635,7 +1716,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="27"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -1656,7 +1737,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -1666,7 +1747,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="27"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -1687,7 +1768,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -1697,7 +1778,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="27"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -1718,7 +1799,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -1729,7 +1810,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="27"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -1750,7 +1831,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="27"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -1760,7 +1841,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="27"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -1783,7 +1864,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="27"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -1793,7 +1874,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="27"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -1814,7 +1895,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="27"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -1823,7 +1904,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="27"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -1844,11 +1925,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="27"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -1868,14 +1949,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -1886,27 +1967,27 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="I21:K22"/>
+    <mergeCell ref="E20:G22"/>
+    <mergeCell ref="H5:H22"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="D5:D22"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="I21:K22"/>
-    <mergeCell ref="E20:G22"/>
-    <mergeCell ref="H5:H22"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="D5:D22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1930,36 +2011,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1971,18 +2052,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1992,17 +2073,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2014,7 +2095,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -2024,7 +2105,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="27"/>
+      <c r="H5" s="35"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -2045,7 +2126,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -2055,7 +2136,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="27"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -2076,7 +2157,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -2086,7 +2167,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="27"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -2107,7 +2188,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -2117,7 +2198,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="27"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -2138,7 +2219,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -2148,7 +2229,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="27"/>
+      <c r="H9" s="35"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -2169,7 +2250,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -2179,7 +2260,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="35"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -2200,7 +2281,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -2210,7 +2291,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="27"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -2231,7 +2312,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -2241,7 +2322,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="27"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -2262,7 +2343,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -2272,7 +2353,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="27"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -2293,7 +2374,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -2303,7 +2384,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="27"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -2324,7 +2405,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -2334,7 +2415,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="27"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -2355,7 +2436,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -2366,7 +2447,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="27"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -2387,7 +2468,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="27"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -2397,7 +2478,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="27"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -2420,7 +2501,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="27"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -2430,7 +2511,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="27"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -2451,7 +2532,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="27"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -2460,7 +2541,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="27"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -2481,11 +2562,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="27"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -2505,14 +2586,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -2523,14 +2604,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2567,36 +2648,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2608,18 +2689,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2629,17 +2710,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2651,7 +2732,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -2661,7 +2742,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="27"/>
+      <c r="H5" s="35"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -2682,7 +2763,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -2692,7 +2773,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="27"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -2713,7 +2794,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -2723,7 +2804,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="27"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -2744,7 +2825,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -2754,7 +2835,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="27"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -2775,7 +2856,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -2785,7 +2866,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="27"/>
+      <c r="H9" s="35"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -2806,7 +2887,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -2816,7 +2897,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="35"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -2837,7 +2918,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -2847,7 +2928,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="27"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -2868,7 +2949,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -2878,7 +2959,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="27"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -2899,7 +2980,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -2909,7 +2990,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="27"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -2930,7 +3011,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -2940,7 +3021,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="27"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -2961,7 +3042,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -2971,7 +3052,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="27"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -2992,7 +3073,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -3003,7 +3084,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="27"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -3024,7 +3105,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="27"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -3034,7 +3115,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="27"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -3057,7 +3138,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="27"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -3067,7 +3148,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="27"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -3088,7 +3169,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="27"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -3097,7 +3178,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="27"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -3118,11 +3199,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="27"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -3142,14 +3223,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="27"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -3160,14 +3241,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3205,36 +3286,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -3246,18 +3327,18 @@
       <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -3270,18 +3351,18 @@
       <c r="A4" s="21">
         <v>2</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="24" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
       <c r="J4" s="4" t="s">
         <v>6</v>
       </c>
@@ -3291,17 +3372,17 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -3313,7 +3394,7 @@
       <c r="C6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="29"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="6" t="s">
         <v>1</v>
       </c>
@@ -3323,7 +3404,7 @@
       <c r="G6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="27"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="9" t="s">
         <v>1</v>
       </c>
@@ -3345,7 +3426,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="12">
         <v>39</v>
       </c>
@@ -3355,7 +3436,7 @@
       <c r="G7" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H7" s="27"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="12">
         <v>76</v>
       </c>
@@ -3376,7 +3457,7 @@
       <c r="C8" s="16">
         <v>15.68</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="15">
         <v>40</v>
       </c>
@@ -3386,7 +3467,7 @@
       <c r="G8" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H8" s="27"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="15">
         <v>77</v>
       </c>
@@ -3407,7 +3488,7 @@
       <c r="C9" s="14">
         <v>5.01</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="12">
         <v>41</v>
       </c>
@@ -3417,7 +3498,7 @@
       <c r="G9" s="14">
         <v>5.15</v>
       </c>
-      <c r="H9" s="27"/>
+      <c r="H9" s="35"/>
       <c r="I9" s="12">
         <v>78</v>
       </c>
@@ -3438,7 +3519,7 @@
       <c r="C10" s="16">
         <v>6.01</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="15">
         <v>42</v>
       </c>
@@ -3448,7 +3529,7 @@
       <c r="G10" s="16">
         <v>9.48</v>
       </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="35"/>
       <c r="I10" s="15">
         <v>79</v>
       </c>
@@ -3469,7 +3550,7 @@
       <c r="C11" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="12">
         <v>43</v>
       </c>
@@ -3479,7 +3560,7 @@
       <c r="G11" s="14">
         <v>198.78</v>
       </c>
-      <c r="H11" s="27"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="12">
         <v>80</v>
       </c>
@@ -3500,7 +3581,7 @@
       <c r="C12" s="16">
         <v>97.45</v>
       </c>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="15">
         <v>44</v>
       </c>
@@ -3510,7 +3591,7 @@
       <c r="G12" s="16">
         <v>14.98</v>
       </c>
-      <c r="H12" s="27"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="15">
         <v>81</v>
       </c>
@@ -3531,7 +3612,7 @@
       <c r="C13" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="12">
         <v>45</v>
       </c>
@@ -3541,7 +3622,7 @@
       <c r="G13" s="14">
         <v>6.46</v>
       </c>
-      <c r="H13" s="27"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="12">
         <v>82</v>
       </c>
@@ -3562,7 +3643,7 @@
       <c r="C14" s="16">
         <v>10</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="15">
         <v>46</v>
       </c>
@@ -3572,7 +3653,7 @@
       <c r="G14" s="16">
         <v>106.83</v>
       </c>
-      <c r="H14" s="27"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="15">
         <v>83</v>
       </c>
@@ -3593,7 +3674,7 @@
       <c r="C15" s="14">
         <v>10.38</v>
       </c>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="12">
         <v>47</v>
       </c>
@@ -3603,11 +3684,11 @@
       <c r="G15" s="14">
         <v>359.68</v>
       </c>
-      <c r="H15" s="27"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="12">
         <v>84</v>
       </c>
-      <c r="J15" s="33" t="s">
+      <c r="J15" s="26" t="s">
         <v>68</v>
       </c>
       <c r="K15" s="14">
@@ -3624,7 +3705,7 @@
       <c r="C16" s="16">
         <v>25.29</v>
       </c>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="15">
         <v>48</v>
       </c>
@@ -3634,7 +3715,7 @@
       <c r="G16" s="16">
         <v>14.81</v>
       </c>
-      <c r="H16" s="27"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="15">
         <v>85</v>
       </c>
@@ -3655,7 +3736,7 @@
       <c r="C17" s="14">
         <v>21.62</v>
       </c>
-      <c r="D17" s="27"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="12">
         <v>49</v>
       </c>
@@ -3665,7 +3746,7 @@
       <c r="G17" s="14">
         <v>14.79</v>
       </c>
-      <c r="H17" s="27"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="12">
         <v>86</v>
       </c>
@@ -3686,7 +3767,7 @@
       <c r="C18" s="16">
         <v>28.06</v>
       </c>
-      <c r="D18" s="27"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="15">
         <v>50</v>
       </c>
@@ -3696,7 +3777,7 @@
       <c r="G18" s="16">
         <v>5.14</v>
       </c>
-      <c r="H18" s="27"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="15">
         <v>87</v>
       </c>
@@ -3717,7 +3798,7 @@
       <c r="C19" s="14">
         <v>96.32</v>
       </c>
-      <c r="D19" s="27"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="12">
         <v>51</v>
       </c>
@@ -3727,7 +3808,7 @@
       <c r="G19" s="14">
         <v>10.32</v>
       </c>
-      <c r="H19" s="27"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="12">
         <v>88</v>
       </c>
@@ -3748,7 +3829,7 @@
       <c r="C20" s="16">
         <v>111.79</v>
       </c>
-      <c r="D20" s="27"/>
+      <c r="D20" s="35"/>
       <c r="E20" s="15">
         <v>52</v>
       </c>
@@ -3758,7 +3839,7 @@
       <c r="G20" s="16">
         <v>11.76</v>
       </c>
-      <c r="H20" s="27"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="15">
         <v>89</v>
       </c>
@@ -3779,7 +3860,7 @@
       <c r="C21" s="14">
         <v>6.45</v>
       </c>
-      <c r="D21" s="27"/>
+      <c r="D21" s="35"/>
       <c r="E21" s="12">
         <v>53</v>
       </c>
@@ -3789,7 +3870,7 @@
       <c r="G21" s="14">
         <v>30.61</v>
       </c>
-      <c r="H21" s="27"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="12">
         <v>90</v>
       </c>
@@ -3810,7 +3891,7 @@
       <c r="C22" s="16">
         <v>9.91</v>
       </c>
-      <c r="D22" s="27"/>
+      <c r="D22" s="35"/>
       <c r="E22" s="15">
         <v>54</v>
       </c>
@@ -3820,7 +3901,7 @@
       <c r="G22" s="16">
         <v>26.54</v>
       </c>
-      <c r="H22" s="27"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="15">
         <v>91</v>
       </c>
@@ -3841,7 +3922,7 @@
       <c r="C23" s="14">
         <v>149.94999999999999</v>
       </c>
-      <c r="D23" s="27"/>
+      <c r="D23" s="35"/>
       <c r="E23" s="12">
         <v>55</v>
       </c>
@@ -3851,7 +3932,7 @@
       <c r="G23" s="14">
         <v>13.17</v>
       </c>
-      <c r="H23" s="27"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="12">
         <v>92</v>
       </c>
@@ -3872,7 +3953,7 @@
       <c r="C24" s="16">
         <v>14.81</v>
       </c>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="15">
         <v>56</v>
       </c>
@@ -3882,7 +3963,7 @@
       <c r="G24" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H24" s="27"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="15">
         <v>93</v>
       </c>
@@ -3903,7 +3984,7 @@
       <c r="C25" s="14">
         <v>5.19</v>
       </c>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="12">
         <v>57</v>
       </c>
@@ -3913,7 +3994,7 @@
       <c r="G25" s="14">
         <v>27.37</v>
       </c>
-      <c r="H25" s="27"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="12">
         <v>94</v>
       </c>
@@ -3934,7 +4015,7 @@
       <c r="C26" s="16">
         <v>14.79</v>
       </c>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="15">
         <v>58</v>
       </c>
@@ -3944,14 +4025,14 @@
       <c r="G26" s="16">
         <v>78.58</v>
       </c>
-      <c r="H26" s="27"/>
+      <c r="H26" s="35"/>
       <c r="I26" s="15">
         <v>95</v>
       </c>
       <c r="J26" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K26" s="30">
+      <c r="K26" s="23">
         <v>29.97</v>
       </c>
     </row>
@@ -3965,7 +4046,7 @@
       <c r="C27" s="14">
         <v>3.8</v>
       </c>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="12">
         <v>59</v>
       </c>
@@ -3975,14 +4056,14 @@
       <c r="G27" s="14">
         <v>5.09</v>
       </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="31">
+      <c r="H27" s="35"/>
+      <c r="I27" s="24">
         <v>96</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="25">
         <v>28.97</v>
       </c>
     </row>
@@ -3996,24 +4077,24 @@
       <c r="C28" s="16">
         <v>4.5</v>
       </c>
-      <c r="D28" s="27"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="15">
         <v>60</v>
       </c>
       <c r="F28" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="23">
         <v>11.06</v>
       </c>
-      <c r="H28" s="27"/>
+      <c r="H28" s="35"/>
       <c r="I28" s="15">
         <v>97</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="23">
         <v>6.65</v>
       </c>
     </row>
@@ -4027,17 +4108,17 @@
       <c r="C29" s="14">
         <v>5.67</v>
       </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="31">
+      <c r="D29" s="35"/>
+      <c r="E29" s="24">
         <v>61</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="25">
         <v>11.17</v>
       </c>
-      <c r="H29" s="27"/>
+      <c r="H29" s="35"/>
       <c r="I29" s="17"/>
       <c r="J29" s="18" t="s">
         <v>9</v>
@@ -4057,20 +4138,20 @@
       <c r="C30" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D30" s="27"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="15">
         <v>62</v>
       </c>
       <c r="F30" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G30" s="23">
         <v>8.33</v>
       </c>
-      <c r="H30" s="27"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
@@ -4082,17 +4163,17 @@
       <c r="C31" s="14">
         <v>39.9</v>
       </c>
-      <c r="D31" s="27"/>
-      <c r="E31" s="31">
+      <c r="D31" s="35"/>
+      <c r="E31" s="24">
         <v>63</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="25">
         <v>5.6</v>
       </c>
-      <c r="H31" s="27"/>
+      <c r="H31" s="35"/>
       <c r="I31" s="38" t="s">
         <v>156</v>
       </c>
@@ -4109,24 +4190,24 @@
       <c r="C32" s="16">
         <v>10.85</v>
       </c>
-      <c r="D32" s="27"/>
+      <c r="D32" s="35"/>
       <c r="E32" s="15">
         <v>64</v>
       </c>
       <c r="F32" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="23">
         <v>6.02</v>
       </c>
-      <c r="H32" s="27"/>
-      <c r="I32" s="34" t="s">
+      <c r="H32" s="35"/>
+      <c r="I32" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="J32" s="35" t="s">
+      <c r="J32" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="K32" s="36" t="s">
+      <c r="K32" s="29" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4140,24 +4221,24 @@
       <c r="C33" s="14">
         <v>5.49</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="31">
+      <c r="D33" s="35"/>
+      <c r="E33" s="24">
         <v>65</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="25">
         <v>37.04</v>
       </c>
-      <c r="H33" s="27"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="15" t="s">
         <v>153</v>
       </c>
       <c r="J33" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="K33" s="30">
+      <c r="K33" s="23">
         <f>193.4+26</f>
         <v>219.4</v>
       </c>
@@ -4172,17 +4253,17 @@
       <c r="C34" s="16">
         <v>9.66</v>
       </c>
-      <c r="D34" s="27"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="15">
         <v>66</v>
       </c>
       <c r="F34" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="23">
         <v>6.28</v>
       </c>
-      <c r="H34" s="27"/>
+      <c r="H34" s="35"/>
       <c r="I34" s="17"/>
       <c r="J34" s="18" t="s">
         <v>9</v>
@@ -4202,20 +4283,20 @@
       <c r="C35" s="14">
         <v>6.28</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="31">
+      <c r="D35" s="35"/>
+      <c r="E35" s="24">
         <v>67</v>
       </c>
       <c r="F35" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="25">
         <v>5.98</v>
       </c>
-      <c r="H35" s="27"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
@@ -4227,20 +4308,20 @@
       <c r="C36" s="16">
         <v>5.85</v>
       </c>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="15">
         <v>68</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="23">
         <v>6.34</v>
       </c>
-      <c r="H36" s="27"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
@@ -4252,7 +4333,7 @@
       <c r="C37" s="14">
         <v>29</v>
       </c>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="12">
         <v>69</v>
       </c>
@@ -4262,10 +4343,10 @@
       <c r="G37" s="14">
         <v>28.97</v>
       </c>
-      <c r="H37" s="27"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
@@ -4277,7 +4358,7 @@
       <c r="C38" s="16">
         <v>67.27</v>
       </c>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="15">
         <v>70</v>
       </c>
@@ -4287,10 +4368,10 @@
       <c r="G38" s="16">
         <v>61.92</v>
       </c>
-      <c r="H38" s="27"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="34"/>
+      <c r="K38" s="34"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
@@ -4302,7 +4383,7 @@
       <c r="C39" s="14">
         <v>60.17</v>
       </c>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="12">
         <v>71</v>
       </c>
@@ -4312,10 +4393,10 @@
       <c r="G39" s="14">
         <v>72.55</v>
       </c>
-      <c r="H39" s="27"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
@@ -4327,7 +4408,7 @@
       <c r="C40" s="16">
         <v>29.3</v>
       </c>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="15">
         <v>72</v>
       </c>
@@ -4337,10 +4418,10 @@
       <c r="G40" s="16">
         <v>6.34</v>
       </c>
-      <c r="H40" s="27"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="34"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
@@ -4352,7 +4433,7 @@
       <c r="C41" s="14">
         <v>15.63</v>
       </c>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="12">
         <v>73</v>
       </c>
@@ -4362,10 +4443,10 @@
       <c r="G41" s="14">
         <v>28.97</v>
       </c>
-      <c r="H41" s="27"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
@@ -4377,7 +4458,7 @@
       <c r="C42" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="15">
         <v>74</v>
       </c>
@@ -4387,10 +4468,10 @@
       <c r="G42" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H42" s="27"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
@@ -4402,7 +4483,7 @@
       <c r="C43" s="14">
         <v>2.57</v>
       </c>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="12">
         <v>75</v>
       </c>
@@ -4412,10 +4493,10 @@
       <c r="G43" s="14">
         <v>6.35</v>
       </c>
-      <c r="H43" s="27"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
     </row>
     <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
@@ -4427,7 +4508,7 @@
       <c r="C44" s="16">
         <v>2.84</v>
       </c>
-      <c r="D44" s="27"/>
+      <c r="D44" s="35"/>
       <c r="E44" s="17"/>
       <c r="F44" s="18" t="s">
         <v>9</v>
@@ -4436,10 +4517,10 @@
         <f>SUM(G7:G43)</f>
         <v>1417.3899999999994</v>
       </c>
-      <c r="H44" s="27"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="26"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
     </row>
     <row r="45" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
@@ -4450,31 +4531,31 @@
         <f>SUM(C7:C44)</f>
         <v>1174.6799999999998</v>
       </c>
-      <c r="D45" s="27"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="26"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="I31:K31"/>
     <mergeCell ref="D6:D45"/>
     <mergeCell ref="H6:H45"/>
     <mergeCell ref="E45:G45"/>
     <mergeCell ref="I35:K45"/>
     <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="G4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4503,36 +4584,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4544,18 +4625,18 @@
       <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -4565,17 +4646,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4587,7 +4668,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="29"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -4597,7 +4678,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="27"/>
+      <c r="H5" s="35"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -4619,7 +4700,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D6" s="27"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="12">
         <v>39</v>
       </c>
@@ -4629,7 +4710,7 @@
       <c r="G6" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H6" s="27"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="12">
         <v>76</v>
       </c>
@@ -4650,7 +4731,7 @@
       <c r="C7" s="16">
         <v>15.68</v>
       </c>
-      <c r="D7" s="27"/>
+      <c r="D7" s="35"/>
       <c r="E7" s="15">
         <v>40</v>
       </c>
@@ -4660,7 +4741,7 @@
       <c r="G7" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H7" s="27"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="15">
         <v>77</v>
       </c>
@@ -4681,7 +4762,7 @@
       <c r="C8" s="14">
         <v>5.01</v>
       </c>
-      <c r="D8" s="27"/>
+      <c r="D8" s="35"/>
       <c r="E8" s="12">
         <v>41</v>
       </c>
@@ -4691,7 +4772,7 @@
       <c r="G8" s="14">
         <v>5.15</v>
       </c>
-      <c r="H8" s="27"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="12">
         <v>78</v>
       </c>
@@ -4712,7 +4793,7 @@
       <c r="C9" s="16">
         <v>6.01</v>
       </c>
-      <c r="D9" s="27"/>
+      <c r="D9" s="35"/>
       <c r="E9" s="15">
         <v>42</v>
       </c>
@@ -4722,7 +4803,7 @@
       <c r="G9" s="16">
         <v>9.48</v>
       </c>
-      <c r="H9" s="27"/>
+      <c r="H9" s="35"/>
       <c r="I9" s="15">
         <v>79</v>
       </c>
@@ -4743,7 +4824,7 @@
       <c r="C10" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D10" s="27"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="12">
         <v>43</v>
       </c>
@@ -4753,7 +4834,7 @@
       <c r="G10" s="14">
         <v>198.78</v>
       </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="35"/>
       <c r="I10" s="12">
         <v>80</v>
       </c>
@@ -4774,7 +4855,7 @@
       <c r="C11" s="16">
         <v>97.45</v>
       </c>
-      <c r="D11" s="27"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="15">
         <v>44</v>
       </c>
@@ -4784,7 +4865,7 @@
       <c r="G11" s="16">
         <v>14.98</v>
       </c>
-      <c r="H11" s="27"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="15">
         <v>81</v>
       </c>
@@ -4805,7 +4886,7 @@
       <c r="C12" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D12" s="27"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="12">
         <v>45</v>
       </c>
@@ -4815,7 +4896,7 @@
       <c r="G12" s="14">
         <v>6.46</v>
       </c>
-      <c r="H12" s="27"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="12">
         <v>82</v>
       </c>
@@ -4836,7 +4917,7 @@
       <c r="C13" s="16">
         <v>10</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="15">
         <v>46</v>
       </c>
@@ -4846,7 +4927,7 @@
       <c r="G13" s="16">
         <v>106.83</v>
       </c>
-      <c r="H13" s="27"/>
+      <c r="H13" s="35"/>
       <c r="I13" s="15">
         <v>83</v>
       </c>
@@ -4867,7 +4948,7 @@
       <c r="C14" s="14">
         <v>10.38</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="35"/>
       <c r="E14" s="12">
         <v>47</v>
       </c>
@@ -4877,11 +4958,11 @@
       <c r="G14" s="14">
         <v>359.68</v>
       </c>
-      <c r="H14" s="27"/>
+      <c r="H14" s="35"/>
       <c r="I14" s="12">
         <v>84</v>
       </c>
-      <c r="J14" s="33" t="s">
+      <c r="J14" s="26" t="s">
         <v>68</v>
       </c>
       <c r="K14" s="14">
@@ -4898,7 +4979,7 @@
       <c r="C15" s="16">
         <v>25.29</v>
       </c>
-      <c r="D15" s="27"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="15">
         <v>48</v>
       </c>
@@ -4908,7 +4989,7 @@
       <c r="G15" s="16">
         <v>14.81</v>
       </c>
-      <c r="H15" s="27"/>
+      <c r="H15" s="35"/>
       <c r="I15" s="15">
         <v>85</v>
       </c>
@@ -4929,7 +5010,7 @@
       <c r="C16" s="14">
         <v>21.62</v>
       </c>
-      <c r="D16" s="27"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="12">
         <v>49</v>
       </c>
@@ -4939,7 +5020,7 @@
       <c r="G16" s="14">
         <v>14.79</v>
       </c>
-      <c r="H16" s="27"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="12">
         <v>86</v>
       </c>
@@ -4960,7 +5041,7 @@
       <c r="C17" s="16">
         <v>28.06</v>
       </c>
-      <c r="D17" s="27"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="15">
         <v>50</v>
       </c>
@@ -4970,7 +5051,7 @@
       <c r="G17" s="16">
         <v>5.14</v>
       </c>
-      <c r="H17" s="27"/>
+      <c r="H17" s="35"/>
       <c r="I17" s="15">
         <v>87</v>
       </c>
@@ -4991,7 +5072,7 @@
       <c r="C18" s="14">
         <v>96.32</v>
       </c>
-      <c r="D18" s="27"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="12">
         <v>51</v>
       </c>
@@ -5001,7 +5082,7 @@
       <c r="G18" s="14">
         <v>10.32</v>
       </c>
-      <c r="H18" s="27"/>
+      <c r="H18" s="35"/>
       <c r="I18" s="12">
         <v>88</v>
       </c>
@@ -5022,7 +5103,7 @@
       <c r="C19" s="16">
         <v>111.79</v>
       </c>
-      <c r="D19" s="27"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="15">
         <v>52</v>
       </c>
@@ -5032,7 +5113,7 @@
       <c r="G19" s="16">
         <v>11.76</v>
       </c>
-      <c r="H19" s="27"/>
+      <c r="H19" s="35"/>
       <c r="I19" s="15">
         <v>89</v>
       </c>
@@ -5053,7 +5134,7 @@
       <c r="C20" s="14">
         <v>6.45</v>
       </c>
-      <c r="D20" s="27"/>
+      <c r="D20" s="35"/>
       <c r="E20" s="12">
         <v>53</v>
       </c>
@@ -5063,7 +5144,7 @@
       <c r="G20" s="14">
         <v>30.61</v>
       </c>
-      <c r="H20" s="27"/>
+      <c r="H20" s="35"/>
       <c r="I20" s="12">
         <v>90</v>
       </c>
@@ -5084,7 +5165,7 @@
       <c r="C21" s="16">
         <v>9.91</v>
       </c>
-      <c r="D21" s="27"/>
+      <c r="D21" s="35"/>
       <c r="E21" s="15">
         <v>54</v>
       </c>
@@ -5094,7 +5175,7 @@
       <c r="G21" s="16">
         <v>26.54</v>
       </c>
-      <c r="H21" s="27"/>
+      <c r="H21" s="35"/>
       <c r="I21" s="15">
         <v>91</v>
       </c>
@@ -5115,7 +5196,7 @@
       <c r="C22" s="14">
         <v>149.94999999999999</v>
       </c>
-      <c r="D22" s="27"/>
+      <c r="D22" s="35"/>
       <c r="E22" s="12">
         <v>55</v>
       </c>
@@ -5125,7 +5206,7 @@
       <c r="G22" s="14">
         <v>13.17</v>
       </c>
-      <c r="H22" s="27"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="12">
         <v>92</v>
       </c>
@@ -5146,7 +5227,7 @@
       <c r="C23" s="16">
         <v>14.81</v>
       </c>
-      <c r="D23" s="27"/>
+      <c r="D23" s="35"/>
       <c r="E23" s="15">
         <v>56</v>
       </c>
@@ -5156,7 +5237,7 @@
       <c r="G23" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H23" s="27"/>
+      <c r="H23" s="35"/>
       <c r="I23" s="15">
         <v>93</v>
       </c>
@@ -5177,7 +5258,7 @@
       <c r="C24" s="14">
         <v>5.19</v>
       </c>
-      <c r="D24" s="27"/>
+      <c r="D24" s="35"/>
       <c r="E24" s="12">
         <v>57</v>
       </c>
@@ -5187,7 +5268,7 @@
       <c r="G24" s="14">
         <v>27.37</v>
       </c>
-      <c r="H24" s="27"/>
+      <c r="H24" s="35"/>
       <c r="I24" s="12">
         <v>94</v>
       </c>
@@ -5208,7 +5289,7 @@
       <c r="C25" s="16">
         <v>14.79</v>
       </c>
-      <c r="D25" s="27"/>
+      <c r="D25" s="35"/>
       <c r="E25" s="15">
         <v>58</v>
       </c>
@@ -5218,14 +5299,14 @@
       <c r="G25" s="16">
         <v>78.58</v>
       </c>
-      <c r="H25" s="27"/>
+      <c r="H25" s="35"/>
       <c r="I25" s="15">
         <v>95</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="23">
         <v>29.97</v>
       </c>
     </row>
@@ -5239,7 +5320,7 @@
       <c r="C26" s="14">
         <v>3.8</v>
       </c>
-      <c r="D26" s="27"/>
+      <c r="D26" s="35"/>
       <c r="E26" s="12">
         <v>59</v>
       </c>
@@ -5249,14 +5330,14 @@
       <c r="G26" s="14">
         <v>5.09</v>
       </c>
-      <c r="H26" s="27"/>
-      <c r="I26" s="31">
+      <c r="H26" s="35"/>
+      <c r="I26" s="24">
         <v>96</v>
       </c>
       <c r="J26" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="K26" s="32">
+      <c r="K26" s="25">
         <v>28.97</v>
       </c>
     </row>
@@ -5270,24 +5351,24 @@
       <c r="C27" s="16">
         <v>4.5</v>
       </c>
-      <c r="D27" s="27"/>
+      <c r="D27" s="35"/>
       <c r="E27" s="15">
         <v>60</v>
       </c>
       <c r="F27" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="23">
         <v>11.06</v>
       </c>
-      <c r="H27" s="27"/>
+      <c r="H27" s="35"/>
       <c r="I27" s="15">
         <v>97</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="23">
         <v>6.65</v>
       </c>
     </row>
@@ -5301,17 +5382,17 @@
       <c r="C28" s="14">
         <v>5.67</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="31">
+      <c r="D28" s="35"/>
+      <c r="E28" s="24">
         <v>61</v>
       </c>
       <c r="F28" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="25">
         <v>11.17</v>
       </c>
-      <c r="H28" s="27"/>
+      <c r="H28" s="35"/>
       <c r="I28" s="17"/>
       <c r="J28" s="18" t="s">
         <v>9</v>
@@ -5331,20 +5412,20 @@
       <c r="C29" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D29" s="27"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="15">
         <v>62</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G29" s="23">
         <v>8.33</v>
       </c>
-      <c r="H29" s="27"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
-      <c r="K29" s="37"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
     </row>
     <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
@@ -5356,17 +5437,17 @@
       <c r="C30" s="14">
         <v>39.9</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="31">
+      <c r="D30" s="35"/>
+      <c r="E30" s="24">
         <v>63</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="25">
         <v>5.6</v>
       </c>
-      <c r="H30" s="27"/>
+      <c r="H30" s="35"/>
       <c r="I30" s="38" t="s">
         <v>156</v>
       </c>
@@ -5383,24 +5464,24 @@
       <c r="C31" s="16">
         <v>10.85</v>
       </c>
-      <c r="D31" s="27"/>
+      <c r="D31" s="35"/>
       <c r="E31" s="15">
         <v>64</v>
       </c>
       <c r="F31" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="23">
         <v>6.02</v>
       </c>
-      <c r="H31" s="27"/>
-      <c r="I31" s="34" t="s">
+      <c r="H31" s="35"/>
+      <c r="I31" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="J31" s="35" t="s">
+      <c r="J31" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="36" t="s">
+      <c r="K31" s="29" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5414,24 +5495,24 @@
       <c r="C32" s="14">
         <v>5.49</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="31">
+      <c r="D32" s="35"/>
+      <c r="E32" s="24">
         <v>65</v>
       </c>
       <c r="F32" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="G32" s="32">
+      <c r="G32" s="25">
         <v>37.04</v>
       </c>
-      <c r="H32" s="27"/>
+      <c r="H32" s="35"/>
       <c r="I32" s="15" t="s">
         <v>153</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="K32" s="30">
+      <c r="K32" s="23">
         <f>193.4+26</f>
         <v>219.4</v>
       </c>
@@ -5446,17 +5527,17 @@
       <c r="C33" s="16">
         <v>9.66</v>
       </c>
-      <c r="D33" s="27"/>
+      <c r="D33" s="35"/>
       <c r="E33" s="15">
         <v>66</v>
       </c>
       <c r="F33" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="23">
         <v>6.28</v>
       </c>
-      <c r="H33" s="27"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="17"/>
       <c r="J33" s="18" t="s">
         <v>9</v>
@@ -5476,20 +5557,20 @@
       <c r="C34" s="14">
         <v>6.28</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="31">
+      <c r="D34" s="35"/>
+      <c r="E34" s="24">
         <v>67</v>
       </c>
       <c r="F34" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="25">
         <v>5.98</v>
       </c>
-      <c r="H34" s="27"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
     </row>
     <row r="35" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
@@ -5501,20 +5582,20 @@
       <c r="C35" s="16">
         <v>5.85</v>
       </c>
-      <c r="D35" s="27"/>
+      <c r="D35" s="35"/>
       <c r="E35" s="15">
         <v>68</v>
       </c>
       <c r="F35" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="23">
         <v>6.34</v>
       </c>
-      <c r="H35" s="27"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
@@ -5526,7 +5607,7 @@
       <c r="C36" s="14">
         <v>29</v>
       </c>
-      <c r="D36" s="27"/>
+      <c r="D36" s="35"/>
       <c r="E36" s="12">
         <v>69</v>
       </c>
@@ -5536,10 +5617,10 @@
       <c r="G36" s="14">
         <v>28.97</v>
       </c>
-      <c r="H36" s="27"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
@@ -5551,7 +5632,7 @@
       <c r="C37" s="16">
         <v>67.27</v>
       </c>
-      <c r="D37" s="27"/>
+      <c r="D37" s="35"/>
       <c r="E37" s="15">
         <v>70</v>
       </c>
@@ -5561,10 +5642,10 @@
       <c r="G37" s="16">
         <v>61.92</v>
       </c>
-      <c r="H37" s="27"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
@@ -5576,7 +5657,7 @@
       <c r="C38" s="14">
         <v>60.17</v>
       </c>
-      <c r="D38" s="27"/>
+      <c r="D38" s="35"/>
       <c r="E38" s="12">
         <v>71</v>
       </c>
@@ -5586,10 +5667,10 @@
       <c r="G38" s="14">
         <v>72.55</v>
       </c>
-      <c r="H38" s="27"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="34"/>
+      <c r="K38" s="34"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
@@ -5601,7 +5682,7 @@
       <c r="C39" s="16">
         <v>29.3</v>
       </c>
-      <c r="D39" s="27"/>
+      <c r="D39" s="35"/>
       <c r="E39" s="15">
         <v>72</v>
       </c>
@@ -5611,10 +5692,10 @@
       <c r="G39" s="16">
         <v>6.34</v>
       </c>
-      <c r="H39" s="27"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -5626,7 +5707,7 @@
       <c r="C40" s="14">
         <v>15.63</v>
       </c>
-      <c r="D40" s="27"/>
+      <c r="D40" s="35"/>
       <c r="E40" s="12">
         <v>73</v>
       </c>
@@ -5636,10 +5717,10 @@
       <c r="G40" s="14">
         <v>28.97</v>
       </c>
-      <c r="H40" s="27"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="34"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
@@ -5651,7 +5732,7 @@
       <c r="C41" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D41" s="27"/>
+      <c r="D41" s="35"/>
       <c r="E41" s="15">
         <v>74</v>
       </c>
@@ -5661,10 +5742,10 @@
       <c r="G41" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H41" s="27"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -5676,7 +5757,7 @@
       <c r="C42" s="14">
         <v>2.57</v>
       </c>
-      <c r="D42" s="27"/>
+      <c r="D42" s="35"/>
       <c r="E42" s="12">
         <v>75</v>
       </c>
@@ -5686,10 +5767,10 @@
       <c r="G42" s="14">
         <v>6.35</v>
       </c>
-      <c r="H42" s="27"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
@@ -5701,7 +5782,7 @@
       <c r="C43" s="16">
         <v>2.84</v>
       </c>
-      <c r="D43" s="27"/>
+      <c r="D43" s="35"/>
       <c r="E43" s="17"/>
       <c r="F43" s="18" t="s">
         <v>9</v>
@@ -5710,10 +5791,10 @@
         <f>SUM(G6:G42)</f>
         <v>1417.3899999999994</v>
       </c>
-      <c r="H43" s="27"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
     </row>
     <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
@@ -5724,17 +5805,22 @@
         <f>SUM(C6:C43)</f>
         <v>1174.6799999999998</v>
       </c>
-      <c r="D44" s="27"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="26"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="D5:D44"/>
     <mergeCell ref="H5:H44"/>
@@ -5742,13 +5828,1755 @@
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="I34:K44"/>
     <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="11.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22">
+        <v>1</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <f>C19+G22+K13</f>
+        <v>714.46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="35"/>
+      <c r="I5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>1</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="14">
+        <v>5.1100000000000003</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="12">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="14">
+        <v>5.19</v>
+      </c>
+      <c r="H6" s="35"/>
+      <c r="I6" s="12">
+        <v>30</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="14">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A7" s="44">
+        <v>2</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="16">
+        <v>5.51</v>
+      </c>
+      <c r="D7" s="35"/>
+      <c r="E7" s="44">
+        <v>15</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="16">
+        <v>11.2</v>
+      </c>
+      <c r="H7" s="35"/>
+      <c r="I7" s="44">
+        <v>31</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" s="16">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>3</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="14">
+        <v>10.08</v>
+      </c>
+      <c r="D8" s="35"/>
+      <c r="E8" s="12">
+        <v>16</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="14">
+        <v>11.31</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="I8" s="12">
+        <v>32</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="14">
+        <v>15.11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="44">
+        <v>4</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="16">
+        <v>149.28</v>
+      </c>
+      <c r="D9" s="35"/>
+      <c r="E9" s="44">
+        <v>17</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="16">
+        <v>26.54</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="44">
+        <v>33</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="K9" s="16">
+        <v>15.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="14">
+        <v>15.01</v>
+      </c>
+      <c r="D10" s="35"/>
+      <c r="E10" s="12">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="14">
+        <v>13.17</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="12">
+        <v>34</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="14">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>6</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="23">
+        <v>5.22</v>
+      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="44">
+        <v>19</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="16">
+        <v>8.19</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="44">
+        <v>35</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="16">
+        <v>29.19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="24">
+        <v>7</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="25">
+        <v>15</v>
+      </c>
+      <c r="D12" s="35"/>
+      <c r="E12" s="12">
+        <v>20</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="14">
+        <v>27.38</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="I12" s="12">
+        <v>36</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="14">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>8</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="23">
+        <v>6.27</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="44">
+        <v>21</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="23">
+        <v>10.44</v>
+      </c>
+      <c r="H13" s="35"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="19">
+        <f>SUM(K6:K12)</f>
+        <v>106.83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A14" s="24">
+        <v>9</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="25">
+        <v>5.98</v>
+      </c>
+      <c r="D14" s="35"/>
+      <c r="E14" s="12">
+        <v>22</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="25">
+        <v>11.73</v>
+      </c>
+      <c r="H14" s="35"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+    </row>
+    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>10</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="23">
+        <v>59.38</v>
+      </c>
+      <c r="D15" s="35"/>
+      <c r="E15" s="44">
+        <v>23</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G15" s="23">
+        <v>30.61</v>
+      </c>
+      <c r="H15" s="35"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+    </row>
+    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="24">
+        <v>11</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="25">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D16" s="35"/>
+      <c r="E16" s="12">
+        <v>24</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="25">
+        <v>15</v>
+      </c>
+      <c r="H16" s="35"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+    </row>
+    <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>12</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="23">
+        <v>29.22</v>
+      </c>
+      <c r="D17" s="35"/>
+      <c r="E17" s="44">
+        <v>25</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="23">
+        <v>14.98</v>
+      </c>
+      <c r="H17" s="35"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+    </row>
+    <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="24">
+        <v>13</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="25">
+        <v>29.54</v>
+      </c>
+      <c r="D18" s="35"/>
+      <c r="E18" s="12">
+        <v>26</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="25">
+        <v>5.23</v>
+      </c>
+      <c r="H18" s="35"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+    </row>
+    <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="19">
+        <f>SUM(C6:C18)</f>
+        <v>352.00000000000006</v>
+      </c>
+      <c r="D19" s="35"/>
+      <c r="E19" s="44">
+        <v>27</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="23">
+        <v>6.27</v>
+      </c>
+      <c r="H19" s="35"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+    </row>
+    <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="12">
+        <v>28</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="25">
+        <v>29.19</v>
+      </c>
+      <c r="H20" s="35"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+    </row>
+    <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="44">
+        <v>29</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="23">
+        <v>29.2</v>
+      </c>
+      <c r="H21" s="35"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+    </row>
+    <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" s="19">
+        <f>SUM(G6:G21)</f>
+        <v>255.62999999999997</v>
+      </c>
+      <c r="H22" s="35"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="D5:D22"/>
+    <mergeCell ref="H5:H22"/>
+    <mergeCell ref="I14:K22"/>
+    <mergeCell ref="A20:C22"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="A4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="11.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22">
+        <v>1</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <f>C10+G12+K16</f>
+        <v>1171.5900000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="35"/>
+      <c r="I5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>1</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="14">
+        <v>44.29</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="12">
+        <v>5</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="14">
+        <v>53.5</v>
+      </c>
+      <c r="H6" s="35"/>
+      <c r="I6" s="12">
+        <v>11</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="14">
+        <v>52.44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="16">
+        <v>47.34</v>
+      </c>
+      <c r="D7" s="35"/>
+      <c r="E7" s="15">
+        <v>6</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="16">
+        <v>74.430000000000007</v>
+      </c>
+      <c r="H7" s="35"/>
+      <c r="I7" s="15">
+        <v>12</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="16">
+        <v>75.180000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>3</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="14">
+        <v>54.22</v>
+      </c>
+      <c r="D8" s="35"/>
+      <c r="E8" s="12">
+        <v>7</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="14">
+        <v>53.83</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="I8" s="12">
+        <v>13</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="14">
+        <v>23.51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="16">
+        <v>129.11000000000001</v>
+      </c>
+      <c r="D9" s="35"/>
+      <c r="E9" s="15">
+        <v>8</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="16">
+        <v>55.33</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="15">
+        <v>14</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="16">
+        <v>54.52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="19">
+        <f>SUM(C6:C9)</f>
+        <v>274.96000000000004</v>
+      </c>
+      <c r="D10" s="35"/>
+      <c r="E10" s="12">
+        <v>9</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="14">
+        <v>54.25</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="12">
+        <v>15</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="14">
+        <v>54.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="15">
+        <v>10</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="16">
+        <v>54.3</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="15">
+        <v>16</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="16">
+        <v>54.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="19">
+        <f>SUM(G6:G11)</f>
+        <v>345.64</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="I12" s="12">
+        <v>17</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="14">
+        <v>54.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="15">
+        <v>18</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" s="16">
+        <v>54.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="12">
+        <v>19</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="K14" s="20">
+        <v>63.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="15">
+        <v>20</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="K15" s="16">
+        <v>63.68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="19">
+        <f>SUM(K6:K15)</f>
+        <v>550.99</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="D17" s="42"/>
+      <c r="H17" s="42"/>
+    </row>
+    <row r="18" spans="4:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="D18" s="42"/>
+      <c r="H18" s="42"/>
+    </row>
+    <row r="19" spans="4:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="D19" s="42"/>
+      <c r="H19" s="42"/>
+    </row>
+    <row r="20" spans="4:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="D20" s="42"/>
+      <c r="H20" s="42"/>
+    </row>
+    <row r="21" spans="4:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="D21" s="42"/>
+      <c r="H21" s="42"/>
+    </row>
+    <row r="22" spans="4:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="D22" s="42"/>
+      <c r="H22" s="42"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="D5:D16"/>
+    <mergeCell ref="H5:H16"/>
+    <mergeCell ref="A11:C16"/>
+    <mergeCell ref="E13:G16"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="A4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="6" max="6" width="13.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+    </row>
+    <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22">
+        <v>1</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <f>C20+G23+K14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22">
+        <v>2</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="49"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5">
+        <f>C21+G24+K15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+    </row>
+    <row r="6" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="43"/>
+      <c r="E6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="42"/>
+      <c r="I6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14"/>
+    </row>
+    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8" s="44"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="14"/>
+    </row>
+    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="44"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="14"/>
+    </row>
+    <row r="12" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="44"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="16"/>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>2</v>
+      </c>
+      <c r="R12" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="14"/>
+      <c r="O13" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="P13" s="1">
+        <v>85.4</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>28.7</v>
+      </c>
+      <c r="R13" s="1">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A14" s="44"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="23"/>
+    </row>
+    <row r="15" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="25"/>
+    </row>
+    <row r="16" spans="1:18" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="44"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="23"/>
+      <c r="O16" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="P16" s="1">
+        <v>183.6</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>154.5</v>
+      </c>
+      <c r="R16" s="1">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="25"/>
+    </row>
+    <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="44"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="23"/>
+    </row>
+    <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A20" s="44"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="23"/>
+    </row>
+    <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+    </row>
+    <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="44"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="23"/>
+    </row>
+    <row r="23" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="19">
+        <f>SUM(C7:C22)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="42"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="19">
+        <f>SUM(G7:G22)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="42"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="19">
+        <f>SUM(K7:K22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="43"/>
+      <c r="E26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="42"/>
+      <c r="I26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A27" s="12"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="14"/>
+    </row>
+    <row r="28" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="16"/>
+    </row>
+    <row r="29" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="14"/>
+    </row>
+    <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A30" s="44"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="14"/>
+    </row>
+    <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A32" s="44"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="14"/>
+    </row>
+    <row r="34" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A34" s="44"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="23"/>
+    </row>
+    <row r="35" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="25"/>
+    </row>
+    <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A36" s="44"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="23"/>
+    </row>
+    <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="25"/>
+    </row>
+    <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A38" s="44"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="23"/>
+    </row>
+    <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+    </row>
+    <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A40" s="44"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="23"/>
+    </row>
+    <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
+    </row>
+    <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A42" s="44"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="23"/>
+    </row>
+    <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="19">
+        <f>SUM(C27:C42)</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="42"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="19">
+        <f>SUM(G27:G42)</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="42"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="19">
+        <f>SUM(K27:K42)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/kronshtatsky/ceilling/ceilling-k.xlsx
+++ b/kronshtatsky/ceilling/ceilling-k.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10128" firstSheet="4" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10128" firstSheet="6" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="CF1" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="1.2-CF1_СКБ" sheetId="7" r:id="rId6"/>
     <sheet name="3.2-CF3_Монтаж" sheetId="8" r:id="rId7"/>
     <sheet name="3.3-CF4_Монтаж" sheetId="9" r:id="rId8"/>
-    <sheet name="4.1-WD6 5" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511" refMode="R1C1"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="168">
   <si>
     <t>Спецификация выполненных работ</t>
   </si>
@@ -536,21 +535,6 @@
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>Зашивка приборов отопления / ГВЛВ / в 2 слоя на каркасе</t>
-  </si>
-  <si>
-    <t>1, 2, 3 этажи. Тип:WD5. Зашивка вертикальных труб отопления ГKЛ тип С112 по серии Knauf толщиной 52мм. Двуслойная обшивка из КНАУФ-листов ГСП-А 12.5мм с одной стороны на одинарном металлическом каркасе из профиля ПП 60x27 Knauf.</t>
-  </si>
-  <si>
-    <t>wd6</t>
-  </si>
-  <si>
-    <t>wd5</t>
-  </si>
-  <si>
-    <t>1, 2, 3 этажи. Тип:WD6. ГКЛ 2 слоя КНАУФ-Файерборд (толщина 12,5 мм) на металлическом каркасе с решеткой для воздухообмена.</t>
   </si>
 </sst>
 </file>
@@ -810,7 +794,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -897,6 +881,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -932,42 +919,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1374,36 +1325,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1415,18 +1366,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1436,17 +1387,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -1458,7 +1409,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -1468,7 +1419,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -1489,7 +1440,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -1499,7 +1450,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -1520,7 +1471,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -1530,7 +1481,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="35"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -1551,7 +1502,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -1561,7 +1512,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -1582,7 +1533,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -1592,7 +1543,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -1613,7 +1564,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -1623,7 +1574,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -1644,7 +1595,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -1654,7 +1605,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -1675,7 +1626,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -1685,7 +1636,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -1706,7 +1657,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="36"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -1716,7 +1667,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -1737,7 +1688,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -1747,7 +1698,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="35"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -1768,7 +1719,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="35"/>
+      <c r="D15" s="36"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -1778,7 +1729,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="35"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -1799,7 +1750,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="35"/>
+      <c r="D16" s="36"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -1810,7 +1761,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="35"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -1831,7 +1782,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="35"/>
+      <c r="D17" s="36"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -1841,7 +1792,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="35"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -1864,7 +1815,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="35"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -1874,7 +1825,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -1895,7 +1846,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -1904,7 +1855,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -1925,11 +1876,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="35"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="36"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -1949,14 +1900,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -1967,14 +1918,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2011,36 +1962,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2052,18 +2003,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2073,17 +2024,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2095,7 +2046,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -2105,7 +2056,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -2126,7 +2077,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -2136,7 +2087,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -2157,7 +2108,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -2167,7 +2118,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="35"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -2188,7 +2139,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -2198,7 +2149,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -2219,7 +2170,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -2229,7 +2180,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -2250,7 +2201,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -2260,7 +2211,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -2281,7 +2232,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -2291,7 +2242,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -2312,7 +2263,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -2322,7 +2273,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -2343,7 +2294,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="36"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -2353,7 +2304,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -2374,7 +2325,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -2384,7 +2335,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="35"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -2405,7 +2356,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="35"/>
+      <c r="D15" s="36"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -2415,7 +2366,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="35"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -2436,7 +2387,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="35"/>
+      <c r="D16" s="36"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -2447,7 +2398,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="35"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -2468,7 +2419,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="35"/>
+      <c r="D17" s="36"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -2478,7 +2429,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="35"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -2501,7 +2452,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="35"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -2511,7 +2462,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -2532,7 +2483,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -2541,7 +2492,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -2562,11 +2513,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="35"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="36"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -2586,14 +2537,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -2604,14 +2555,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2648,36 +2599,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2689,18 +2640,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2710,17 +2661,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2732,7 +2683,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -2742,7 +2693,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -2763,7 +2714,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -2773,7 +2724,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -2794,7 +2745,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -2804,7 +2755,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="35"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -2825,7 +2776,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -2835,7 +2786,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -2856,7 +2807,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -2866,7 +2817,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -2887,7 +2838,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -2897,7 +2848,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -2918,7 +2869,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -2928,7 +2879,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -2949,7 +2900,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -2959,7 +2910,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -2980,7 +2931,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="36"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -2990,7 +2941,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -3011,7 +2962,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -3021,7 +2972,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="35"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -3042,7 +2993,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="35"/>
+      <c r="D15" s="36"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -3052,7 +3003,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="35"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -3073,7 +3024,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="35"/>
+      <c r="D16" s="36"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -3084,7 +3035,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="35"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -3105,7 +3056,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="35"/>
+      <c r="D17" s="36"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -3115,7 +3066,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="35"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -3138,7 +3089,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="35"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -3148,7 +3099,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -3169,7 +3120,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -3178,7 +3129,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -3199,11 +3150,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="35"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="36"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -3223,14 +3174,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="35"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -3241,14 +3192,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3286,36 +3237,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -3327,18 +3278,18 @@
       <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -3351,18 +3302,18 @@
       <c r="A4" s="21">
         <v>2</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="32" t="s">
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
       <c r="J4" s="4" t="s">
         <v>6</v>
       </c>
@@ -3372,17 +3323,17 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -3394,7 +3345,7 @@
       <c r="C6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="37"/>
+      <c r="D6" s="38"/>
       <c r="E6" s="6" t="s">
         <v>1</v>
       </c>
@@ -3404,7 +3355,7 @@
       <c r="G6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="9" t="s">
         <v>1</v>
       </c>
@@ -3426,7 +3377,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="12">
         <v>39</v>
       </c>
@@ -3436,7 +3387,7 @@
       <c r="G7" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H7" s="35"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="12">
         <v>76</v>
       </c>
@@ -3457,7 +3408,7 @@
       <c r="C8" s="16">
         <v>15.68</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="15">
         <v>40</v>
       </c>
@@ -3467,7 +3418,7 @@
       <c r="G8" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="15">
         <v>77</v>
       </c>
@@ -3488,7 +3439,7 @@
       <c r="C9" s="14">
         <v>5.01</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="12">
         <v>41</v>
       </c>
@@ -3498,7 +3449,7 @@
       <c r="G9" s="14">
         <v>5.15</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="12">
         <v>78</v>
       </c>
@@ -3519,7 +3470,7 @@
       <c r="C10" s="16">
         <v>6.01</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="15">
         <v>42</v>
       </c>
@@ -3529,7 +3480,7 @@
       <c r="G10" s="16">
         <v>9.48</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="15">
         <v>79</v>
       </c>
@@ -3550,7 +3501,7 @@
       <c r="C11" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="12">
         <v>43</v>
       </c>
@@ -3560,7 +3511,7 @@
       <c r="G11" s="14">
         <v>198.78</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="12">
         <v>80</v>
       </c>
@@ -3581,7 +3532,7 @@
       <c r="C12" s="16">
         <v>97.45</v>
       </c>
-      <c r="D12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="15">
         <v>44</v>
       </c>
@@ -3591,7 +3542,7 @@
       <c r="G12" s="16">
         <v>14.98</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="15">
         <v>81</v>
       </c>
@@ -3612,7 +3563,7 @@
       <c r="C13" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="36"/>
       <c r="E13" s="12">
         <v>45</v>
       </c>
@@ -3622,7 +3573,7 @@
       <c r="G13" s="14">
         <v>6.46</v>
       </c>
-      <c r="H13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="12">
         <v>82</v>
       </c>
@@ -3643,7 +3594,7 @@
       <c r="C14" s="16">
         <v>10</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="15">
         <v>46</v>
       </c>
@@ -3653,7 +3604,7 @@
       <c r="G14" s="16">
         <v>106.83</v>
       </c>
-      <c r="H14" s="35"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="15">
         <v>83</v>
       </c>
@@ -3674,7 +3625,7 @@
       <c r="C15" s="14">
         <v>10.38</v>
       </c>
-      <c r="D15" s="35"/>
+      <c r="D15" s="36"/>
       <c r="E15" s="12">
         <v>47</v>
       </c>
@@ -3684,7 +3635,7 @@
       <c r="G15" s="14">
         <v>359.68</v>
       </c>
-      <c r="H15" s="35"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="12">
         <v>84</v>
       </c>
@@ -3705,7 +3656,7 @@
       <c r="C16" s="16">
         <v>25.29</v>
       </c>
-      <c r="D16" s="35"/>
+      <c r="D16" s="36"/>
       <c r="E16" s="15">
         <v>48</v>
       </c>
@@ -3715,7 +3666,7 @@
       <c r="G16" s="16">
         <v>14.81</v>
       </c>
-      <c r="H16" s="35"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="15">
         <v>85</v>
       </c>
@@ -3736,7 +3687,7 @@
       <c r="C17" s="14">
         <v>21.62</v>
       </c>
-      <c r="D17" s="35"/>
+      <c r="D17" s="36"/>
       <c r="E17" s="12">
         <v>49</v>
       </c>
@@ -3746,7 +3697,7 @@
       <c r="G17" s="14">
         <v>14.79</v>
       </c>
-      <c r="H17" s="35"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="12">
         <v>86</v>
       </c>
@@ -3767,7 +3718,7 @@
       <c r="C18" s="16">
         <v>28.06</v>
       </c>
-      <c r="D18" s="35"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="15">
         <v>50</v>
       </c>
@@ -3777,7 +3728,7 @@
       <c r="G18" s="16">
         <v>5.14</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="15">
         <v>87</v>
       </c>
@@ -3798,7 +3749,7 @@
       <c r="C19" s="14">
         <v>96.32</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="12">
         <v>51</v>
       </c>
@@ -3808,7 +3759,7 @@
       <c r="G19" s="14">
         <v>10.32</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="12">
         <v>88</v>
       </c>
@@ -3829,7 +3780,7 @@
       <c r="C20" s="16">
         <v>111.79</v>
       </c>
-      <c r="D20" s="35"/>
+      <c r="D20" s="36"/>
       <c r="E20" s="15">
         <v>52</v>
       </c>
@@ -3839,7 +3790,7 @@
       <c r="G20" s="16">
         <v>11.76</v>
       </c>
-      <c r="H20" s="35"/>
+      <c r="H20" s="36"/>
       <c r="I20" s="15">
         <v>89</v>
       </c>
@@ -3860,7 +3811,7 @@
       <c r="C21" s="14">
         <v>6.45</v>
       </c>
-      <c r="D21" s="35"/>
+      <c r="D21" s="36"/>
       <c r="E21" s="12">
         <v>53</v>
       </c>
@@ -3870,7 +3821,7 @@
       <c r="G21" s="14">
         <v>30.61</v>
       </c>
-      <c r="H21" s="35"/>
+      <c r="H21" s="36"/>
       <c r="I21" s="12">
         <v>90</v>
       </c>
@@ -3891,7 +3842,7 @@
       <c r="C22" s="16">
         <v>9.91</v>
       </c>
-      <c r="D22" s="35"/>
+      <c r="D22" s="36"/>
       <c r="E22" s="15">
         <v>54</v>
       </c>
@@ -3901,7 +3852,7 @@
       <c r="G22" s="16">
         <v>26.54</v>
       </c>
-      <c r="H22" s="35"/>
+      <c r="H22" s="36"/>
       <c r="I22" s="15">
         <v>91</v>
       </c>
@@ -3922,7 +3873,7 @@
       <c r="C23" s="14">
         <v>149.94999999999999</v>
       </c>
-      <c r="D23" s="35"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="12">
         <v>55</v>
       </c>
@@ -3932,7 +3883,7 @@
       <c r="G23" s="14">
         <v>13.17</v>
       </c>
-      <c r="H23" s="35"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="12">
         <v>92</v>
       </c>
@@ -3953,7 +3904,7 @@
       <c r="C24" s="16">
         <v>14.81</v>
       </c>
-      <c r="D24" s="35"/>
+      <c r="D24" s="36"/>
       <c r="E24" s="15">
         <v>56</v>
       </c>
@@ -3963,7 +3914,7 @@
       <c r="G24" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H24" s="35"/>
+      <c r="H24" s="36"/>
       <c r="I24" s="15">
         <v>93</v>
       </c>
@@ -3984,7 +3935,7 @@
       <c r="C25" s="14">
         <v>5.19</v>
       </c>
-      <c r="D25" s="35"/>
+      <c r="D25" s="36"/>
       <c r="E25" s="12">
         <v>57</v>
       </c>
@@ -3994,7 +3945,7 @@
       <c r="G25" s="14">
         <v>27.37</v>
       </c>
-      <c r="H25" s="35"/>
+      <c r="H25" s="36"/>
       <c r="I25" s="12">
         <v>94</v>
       </c>
@@ -4015,7 +3966,7 @@
       <c r="C26" s="16">
         <v>14.79</v>
       </c>
-      <c r="D26" s="35"/>
+      <c r="D26" s="36"/>
       <c r="E26" s="15">
         <v>58</v>
       </c>
@@ -4025,7 +3976,7 @@
       <c r="G26" s="16">
         <v>78.58</v>
       </c>
-      <c r="H26" s="35"/>
+      <c r="H26" s="36"/>
       <c r="I26" s="15">
         <v>95</v>
       </c>
@@ -4046,7 +3997,7 @@
       <c r="C27" s="14">
         <v>3.8</v>
       </c>
-      <c r="D27" s="35"/>
+      <c r="D27" s="36"/>
       <c r="E27" s="12">
         <v>59</v>
       </c>
@@ -4056,7 +4007,7 @@
       <c r="G27" s="14">
         <v>5.09</v>
       </c>
-      <c r="H27" s="35"/>
+      <c r="H27" s="36"/>
       <c r="I27" s="24">
         <v>96</v>
       </c>
@@ -4077,7 +4028,7 @@
       <c r="C28" s="16">
         <v>4.5</v>
       </c>
-      <c r="D28" s="35"/>
+      <c r="D28" s="36"/>
       <c r="E28" s="15">
         <v>60</v>
       </c>
@@ -4087,7 +4038,7 @@
       <c r="G28" s="23">
         <v>11.06</v>
       </c>
-      <c r="H28" s="35"/>
+      <c r="H28" s="36"/>
       <c r="I28" s="15">
         <v>97</v>
       </c>
@@ -4108,7 +4059,7 @@
       <c r="C29" s="14">
         <v>5.67</v>
       </c>
-      <c r="D29" s="35"/>
+      <c r="D29" s="36"/>
       <c r="E29" s="24">
         <v>61</v>
       </c>
@@ -4118,7 +4069,7 @@
       <c r="G29" s="25">
         <v>11.17</v>
       </c>
-      <c r="H29" s="35"/>
+      <c r="H29" s="36"/>
       <c r="I29" s="17"/>
       <c r="J29" s="18" t="s">
         <v>9</v>
@@ -4138,7 +4089,7 @@
       <c r="C30" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D30" s="35"/>
+      <c r="D30" s="36"/>
       <c r="E30" s="15">
         <v>62</v>
       </c>
@@ -4148,10 +4099,10 @@
       <c r="G30" s="23">
         <v>8.33</v>
       </c>
-      <c r="H30" s="35"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
@@ -4163,7 +4114,7 @@
       <c r="C31" s="14">
         <v>39.9</v>
       </c>
-      <c r="D31" s="35"/>
+      <c r="D31" s="36"/>
       <c r="E31" s="24">
         <v>63</v>
       </c>
@@ -4173,12 +4124,12 @@
       <c r="G31" s="25">
         <v>5.6</v>
       </c>
-      <c r="H31" s="35"/>
-      <c r="I31" s="38" t="s">
+      <c r="H31" s="36"/>
+      <c r="I31" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="J31" s="39"/>
-      <c r="K31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="41"/>
     </row>
     <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
@@ -4190,7 +4141,7 @@
       <c r="C32" s="16">
         <v>10.85</v>
       </c>
-      <c r="D32" s="35"/>
+      <c r="D32" s="36"/>
       <c r="E32" s="15">
         <v>64</v>
       </c>
@@ -4200,7 +4151,7 @@
       <c r="G32" s="23">
         <v>6.02</v>
       </c>
-      <c r="H32" s="35"/>
+      <c r="H32" s="36"/>
       <c r="I32" s="27" t="s">
         <v>1</v>
       </c>
@@ -4221,7 +4172,7 @@
       <c r="C33" s="14">
         <v>5.49</v>
       </c>
-      <c r="D33" s="35"/>
+      <c r="D33" s="36"/>
       <c r="E33" s="24">
         <v>65</v>
       </c>
@@ -4231,7 +4182,7 @@
       <c r="G33" s="25">
         <v>37.04</v>
       </c>
-      <c r="H33" s="35"/>
+      <c r="H33" s="36"/>
       <c r="I33" s="15" t="s">
         <v>153</v>
       </c>
@@ -4253,7 +4204,7 @@
       <c r="C34" s="16">
         <v>9.66</v>
       </c>
-      <c r="D34" s="35"/>
+      <c r="D34" s="36"/>
       <c r="E34" s="15">
         <v>66</v>
       </c>
@@ -4263,7 +4214,7 @@
       <c r="G34" s="23">
         <v>6.28</v>
       </c>
-      <c r="H34" s="35"/>
+      <c r="H34" s="36"/>
       <c r="I34" s="17"/>
       <c r="J34" s="18" t="s">
         <v>9</v>
@@ -4283,7 +4234,7 @@
       <c r="C35" s="14">
         <v>6.28</v>
       </c>
-      <c r="D35" s="35"/>
+      <c r="D35" s="36"/>
       <c r="E35" s="24">
         <v>67</v>
       </c>
@@ -4293,10 +4244,10 @@
       <c r="G35" s="25">
         <v>5.98</v>
       </c>
-      <c r="H35" s="35"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
@@ -4308,7 +4259,7 @@
       <c r="C36" s="16">
         <v>5.85</v>
       </c>
-      <c r="D36" s="35"/>
+      <c r="D36" s="36"/>
       <c r="E36" s="15">
         <v>68</v>
       </c>
@@ -4318,10 +4269,10 @@
       <c r="G36" s="23">
         <v>6.34</v>
       </c>
-      <c r="H36" s="35"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
@@ -4333,7 +4284,7 @@
       <c r="C37" s="14">
         <v>29</v>
       </c>
-      <c r="D37" s="35"/>
+      <c r="D37" s="36"/>
       <c r="E37" s="12">
         <v>69</v>
       </c>
@@ -4343,10 +4294,10 @@
       <c r="G37" s="14">
         <v>28.97</v>
       </c>
-      <c r="H37" s="35"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
@@ -4358,7 +4309,7 @@
       <c r="C38" s="16">
         <v>67.27</v>
       </c>
-      <c r="D38" s="35"/>
+      <c r="D38" s="36"/>
       <c r="E38" s="15">
         <v>70</v>
       </c>
@@ -4368,10 +4319,10 @@
       <c r="G38" s="16">
         <v>61.92</v>
       </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
@@ -4383,7 +4334,7 @@
       <c r="C39" s="14">
         <v>60.17</v>
       </c>
-      <c r="D39" s="35"/>
+      <c r="D39" s="36"/>
       <c r="E39" s="12">
         <v>71</v>
       </c>
@@ -4393,10 +4344,10 @@
       <c r="G39" s="14">
         <v>72.55</v>
       </c>
-      <c r="H39" s="35"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
@@ -4408,7 +4359,7 @@
       <c r="C40" s="16">
         <v>29.3</v>
       </c>
-      <c r="D40" s="35"/>
+      <c r="D40" s="36"/>
       <c r="E40" s="15">
         <v>72</v>
       </c>
@@ -4418,10 +4369,10 @@
       <c r="G40" s="16">
         <v>6.34</v>
       </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
@@ -4433,7 +4384,7 @@
       <c r="C41" s="14">
         <v>15.63</v>
       </c>
-      <c r="D41" s="35"/>
+      <c r="D41" s="36"/>
       <c r="E41" s="12">
         <v>73</v>
       </c>
@@ -4443,10 +4394,10 @@
       <c r="G41" s="14">
         <v>28.97</v>
       </c>
-      <c r="H41" s="35"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
@@ -4458,7 +4409,7 @@
       <c r="C42" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D42" s="35"/>
+      <c r="D42" s="36"/>
       <c r="E42" s="15">
         <v>74</v>
       </c>
@@ -4468,10 +4419,10 @@
       <c r="G42" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H42" s="35"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
@@ -4483,7 +4434,7 @@
       <c r="C43" s="14">
         <v>2.57</v>
       </c>
-      <c r="D43" s="35"/>
+      <c r="D43" s="36"/>
       <c r="E43" s="12">
         <v>75</v>
       </c>
@@ -4493,10 +4444,10 @@
       <c r="G43" s="14">
         <v>6.35</v>
       </c>
-      <c r="H43" s="35"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
     </row>
     <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
@@ -4508,7 +4459,7 @@
       <c r="C44" s="16">
         <v>2.84</v>
       </c>
-      <c r="D44" s="35"/>
+      <c r="D44" s="36"/>
       <c r="E44" s="17"/>
       <c r="F44" s="18" t="s">
         <v>9</v>
@@ -4517,10 +4468,10 @@
         <f>SUM(G7:G43)</f>
         <v>1417.3899999999994</v>
       </c>
-      <c r="H44" s="35"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
     </row>
     <row r="45" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
@@ -4531,14 +4482,14 @@
         <f>SUM(C7:C44)</f>
         <v>1174.6799999999998</v>
       </c>
-      <c r="D45" s="35"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="34"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4584,36 +4535,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4625,18 +4576,18 @@
       <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -4646,17 +4597,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4668,7 +4619,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -4678,7 +4629,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -4700,7 +4651,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="12">
         <v>39</v>
       </c>
@@ -4710,7 +4661,7 @@
       <c r="G6" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="12">
         <v>76</v>
       </c>
@@ -4731,7 +4682,7 @@
       <c r="C7" s="16">
         <v>15.68</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="15">
         <v>40</v>
       </c>
@@ -4741,7 +4692,7 @@
       <c r="G7" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H7" s="35"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="15">
         <v>77</v>
       </c>
@@ -4762,7 +4713,7 @@
       <c r="C8" s="14">
         <v>5.01</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="12">
         <v>41</v>
       </c>
@@ -4772,7 +4723,7 @@
       <c r="G8" s="14">
         <v>5.15</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="12">
         <v>78</v>
       </c>
@@ -4793,7 +4744,7 @@
       <c r="C9" s="16">
         <v>6.01</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="15">
         <v>42</v>
       </c>
@@ -4803,7 +4754,7 @@
       <c r="G9" s="16">
         <v>9.48</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="15">
         <v>79</v>
       </c>
@@ -4824,7 +4775,7 @@
       <c r="C10" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="12">
         <v>43</v>
       </c>
@@ -4834,7 +4785,7 @@
       <c r="G10" s="14">
         <v>198.78</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="12">
         <v>80</v>
       </c>
@@ -4855,7 +4806,7 @@
       <c r="C11" s="16">
         <v>97.45</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="15">
         <v>44</v>
       </c>
@@ -4865,7 +4816,7 @@
       <c r="G11" s="16">
         <v>14.98</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="15">
         <v>81</v>
       </c>
@@ -4886,7 +4837,7 @@
       <c r="C12" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="12">
         <v>45</v>
       </c>
@@ -4896,7 +4847,7 @@
       <c r="G12" s="14">
         <v>6.46</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="12">
         <v>82</v>
       </c>
@@ -4917,7 +4868,7 @@
       <c r="C13" s="16">
         <v>10</v>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="36"/>
       <c r="E13" s="15">
         <v>46</v>
       </c>
@@ -4927,7 +4878,7 @@
       <c r="G13" s="16">
         <v>106.83</v>
       </c>
-      <c r="H13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="15">
         <v>83</v>
       </c>
@@ -4948,7 +4899,7 @@
       <c r="C14" s="14">
         <v>10.38</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="12">
         <v>47</v>
       </c>
@@ -4958,7 +4909,7 @@
       <c r="G14" s="14">
         <v>359.68</v>
       </c>
-      <c r="H14" s="35"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="12">
         <v>84</v>
       </c>
@@ -4979,7 +4930,7 @@
       <c r="C15" s="16">
         <v>25.29</v>
       </c>
-      <c r="D15" s="35"/>
+      <c r="D15" s="36"/>
       <c r="E15" s="15">
         <v>48</v>
       </c>
@@ -4989,7 +4940,7 @@
       <c r="G15" s="16">
         <v>14.81</v>
       </c>
-      <c r="H15" s="35"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="15">
         <v>85</v>
       </c>
@@ -5010,7 +4961,7 @@
       <c r="C16" s="14">
         <v>21.62</v>
       </c>
-      <c r="D16" s="35"/>
+      <c r="D16" s="36"/>
       <c r="E16" s="12">
         <v>49</v>
       </c>
@@ -5020,7 +4971,7 @@
       <c r="G16" s="14">
         <v>14.79</v>
       </c>
-      <c r="H16" s="35"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="12">
         <v>86</v>
       </c>
@@ -5041,7 +4992,7 @@
       <c r="C17" s="16">
         <v>28.06</v>
       </c>
-      <c r="D17" s="35"/>
+      <c r="D17" s="36"/>
       <c r="E17" s="15">
         <v>50</v>
       </c>
@@ -5051,7 +5002,7 @@
       <c r="G17" s="16">
         <v>5.14</v>
       </c>
-      <c r="H17" s="35"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="15">
         <v>87</v>
       </c>
@@ -5072,7 +5023,7 @@
       <c r="C18" s="14">
         <v>96.32</v>
       </c>
-      <c r="D18" s="35"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="12">
         <v>51</v>
       </c>
@@ -5082,7 +5033,7 @@
       <c r="G18" s="14">
         <v>10.32</v>
       </c>
-      <c r="H18" s="35"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="12">
         <v>88</v>
       </c>
@@ -5103,7 +5054,7 @@
       <c r="C19" s="16">
         <v>111.79</v>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="15">
         <v>52</v>
       </c>
@@ -5113,7 +5064,7 @@
       <c r="G19" s="16">
         <v>11.76</v>
       </c>
-      <c r="H19" s="35"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="15">
         <v>89</v>
       </c>
@@ -5134,7 +5085,7 @@
       <c r="C20" s="14">
         <v>6.45</v>
       </c>
-      <c r="D20" s="35"/>
+      <c r="D20" s="36"/>
       <c r="E20" s="12">
         <v>53</v>
       </c>
@@ -5144,7 +5095,7 @@
       <c r="G20" s="14">
         <v>30.61</v>
       </c>
-      <c r="H20" s="35"/>
+      <c r="H20" s="36"/>
       <c r="I20" s="12">
         <v>90</v>
       </c>
@@ -5165,7 +5116,7 @@
       <c r="C21" s="16">
         <v>9.91</v>
       </c>
-      <c r="D21" s="35"/>
+      <c r="D21" s="36"/>
       <c r="E21" s="15">
         <v>54</v>
       </c>
@@ -5175,7 +5126,7 @@
       <c r="G21" s="16">
         <v>26.54</v>
       </c>
-      <c r="H21" s="35"/>
+      <c r="H21" s="36"/>
       <c r="I21" s="15">
         <v>91</v>
       </c>
@@ -5196,7 +5147,7 @@
       <c r="C22" s="14">
         <v>149.94999999999999</v>
       </c>
-      <c r="D22" s="35"/>
+      <c r="D22" s="36"/>
       <c r="E22" s="12">
         <v>55</v>
       </c>
@@ -5206,7 +5157,7 @@
       <c r="G22" s="14">
         <v>13.17</v>
       </c>
-      <c r="H22" s="35"/>
+      <c r="H22" s="36"/>
       <c r="I22" s="12">
         <v>92</v>
       </c>
@@ -5227,7 +5178,7 @@
       <c r="C23" s="16">
         <v>14.81</v>
       </c>
-      <c r="D23" s="35"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="15">
         <v>56</v>
       </c>
@@ -5237,7 +5188,7 @@
       <c r="G23" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H23" s="35"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="15">
         <v>93</v>
       </c>
@@ -5258,7 +5209,7 @@
       <c r="C24" s="14">
         <v>5.19</v>
       </c>
-      <c r="D24" s="35"/>
+      <c r="D24" s="36"/>
       <c r="E24" s="12">
         <v>57</v>
       </c>
@@ -5268,7 +5219,7 @@
       <c r="G24" s="14">
         <v>27.37</v>
       </c>
-      <c r="H24" s="35"/>
+      <c r="H24" s="36"/>
       <c r="I24" s="12">
         <v>94</v>
       </c>
@@ -5289,7 +5240,7 @@
       <c r="C25" s="16">
         <v>14.79</v>
       </c>
-      <c r="D25" s="35"/>
+      <c r="D25" s="36"/>
       <c r="E25" s="15">
         <v>58</v>
       </c>
@@ -5299,7 +5250,7 @@
       <c r="G25" s="16">
         <v>78.58</v>
       </c>
-      <c r="H25" s="35"/>
+      <c r="H25" s="36"/>
       <c r="I25" s="15">
         <v>95</v>
       </c>
@@ -5320,7 +5271,7 @@
       <c r="C26" s="14">
         <v>3.8</v>
       </c>
-      <c r="D26" s="35"/>
+      <c r="D26" s="36"/>
       <c r="E26" s="12">
         <v>59</v>
       </c>
@@ -5330,7 +5281,7 @@
       <c r="G26" s="14">
         <v>5.09</v>
       </c>
-      <c r="H26" s="35"/>
+      <c r="H26" s="36"/>
       <c r="I26" s="24">
         <v>96</v>
       </c>
@@ -5351,7 +5302,7 @@
       <c r="C27" s="16">
         <v>4.5</v>
       </c>
-      <c r="D27" s="35"/>
+      <c r="D27" s="36"/>
       <c r="E27" s="15">
         <v>60</v>
       </c>
@@ -5361,7 +5312,7 @@
       <c r="G27" s="23">
         <v>11.06</v>
       </c>
-      <c r="H27" s="35"/>
+      <c r="H27" s="36"/>
       <c r="I27" s="15">
         <v>97</v>
       </c>
@@ -5382,7 +5333,7 @@
       <c r="C28" s="14">
         <v>5.67</v>
       </c>
-      <c r="D28" s="35"/>
+      <c r="D28" s="36"/>
       <c r="E28" s="24">
         <v>61</v>
       </c>
@@ -5392,7 +5343,7 @@
       <c r="G28" s="25">
         <v>11.17</v>
       </c>
-      <c r="H28" s="35"/>
+      <c r="H28" s="36"/>
       <c r="I28" s="17"/>
       <c r="J28" s="18" t="s">
         <v>9</v>
@@ -5412,7 +5363,7 @@
       <c r="C29" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D29" s="35"/>
+      <c r="D29" s="36"/>
       <c r="E29" s="15">
         <v>62</v>
       </c>
@@ -5422,10 +5373,10 @@
       <c r="G29" s="23">
         <v>8.33</v>
       </c>
-      <c r="H29" s="35"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
     </row>
     <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
@@ -5437,7 +5388,7 @@
       <c r="C30" s="14">
         <v>39.9</v>
       </c>
-      <c r="D30" s="35"/>
+      <c r="D30" s="36"/>
       <c r="E30" s="24">
         <v>63</v>
       </c>
@@ -5447,12 +5398,12 @@
       <c r="G30" s="25">
         <v>5.6</v>
       </c>
-      <c r="H30" s="35"/>
-      <c r="I30" s="38" t="s">
+      <c r="H30" s="36"/>
+      <c r="I30" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="J30" s="39"/>
-      <c r="K30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="41"/>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
@@ -5464,7 +5415,7 @@
       <c r="C31" s="16">
         <v>10.85</v>
       </c>
-      <c r="D31" s="35"/>
+      <c r="D31" s="36"/>
       <c r="E31" s="15">
         <v>64</v>
       </c>
@@ -5474,7 +5425,7 @@
       <c r="G31" s="23">
         <v>6.02</v>
       </c>
-      <c r="H31" s="35"/>
+      <c r="H31" s="36"/>
       <c r="I31" s="27" t="s">
         <v>1</v>
       </c>
@@ -5495,7 +5446,7 @@
       <c r="C32" s="14">
         <v>5.49</v>
       </c>
-      <c r="D32" s="35"/>
+      <c r="D32" s="36"/>
       <c r="E32" s="24">
         <v>65</v>
       </c>
@@ -5505,7 +5456,7 @@
       <c r="G32" s="25">
         <v>37.04</v>
       </c>
-      <c r="H32" s="35"/>
+      <c r="H32" s="36"/>
       <c r="I32" s="15" t="s">
         <v>153</v>
       </c>
@@ -5527,7 +5478,7 @@
       <c r="C33" s="16">
         <v>9.66</v>
       </c>
-      <c r="D33" s="35"/>
+      <c r="D33" s="36"/>
       <c r="E33" s="15">
         <v>66</v>
       </c>
@@ -5537,7 +5488,7 @@
       <c r="G33" s="23">
         <v>6.28</v>
       </c>
-      <c r="H33" s="35"/>
+      <c r="H33" s="36"/>
       <c r="I33" s="17"/>
       <c r="J33" s="18" t="s">
         <v>9</v>
@@ -5557,7 +5508,7 @@
       <c r="C34" s="14">
         <v>6.28</v>
       </c>
-      <c r="D34" s="35"/>
+      <c r="D34" s="36"/>
       <c r="E34" s="24">
         <v>67</v>
       </c>
@@ -5567,10 +5518,10 @@
       <c r="G34" s="25">
         <v>5.98</v>
       </c>
-      <c r="H34" s="35"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
     </row>
     <row r="35" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
@@ -5582,7 +5533,7 @@
       <c r="C35" s="16">
         <v>5.85</v>
       </c>
-      <c r="D35" s="35"/>
+      <c r="D35" s="36"/>
       <c r="E35" s="15">
         <v>68</v>
       </c>
@@ -5592,10 +5543,10 @@
       <c r="G35" s="23">
         <v>6.34</v>
       </c>
-      <c r="H35" s="35"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
@@ -5607,7 +5558,7 @@
       <c r="C36" s="14">
         <v>29</v>
       </c>
-      <c r="D36" s="35"/>
+      <c r="D36" s="36"/>
       <c r="E36" s="12">
         <v>69</v>
       </c>
@@ -5617,10 +5568,10 @@
       <c r="G36" s="14">
         <v>28.97</v>
       </c>
-      <c r="H36" s="35"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
@@ -5632,7 +5583,7 @@
       <c r="C37" s="16">
         <v>67.27</v>
       </c>
-      <c r="D37" s="35"/>
+      <c r="D37" s="36"/>
       <c r="E37" s="15">
         <v>70</v>
       </c>
@@ -5642,10 +5593,10 @@
       <c r="G37" s="16">
         <v>61.92</v>
       </c>
-      <c r="H37" s="35"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
@@ -5657,7 +5608,7 @@
       <c r="C38" s="14">
         <v>60.17</v>
       </c>
-      <c r="D38" s="35"/>
+      <c r="D38" s="36"/>
       <c r="E38" s="12">
         <v>71</v>
       </c>
@@ -5667,10 +5618,10 @@
       <c r="G38" s="14">
         <v>72.55</v>
       </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
@@ -5682,7 +5633,7 @@
       <c r="C39" s="16">
         <v>29.3</v>
       </c>
-      <c r="D39" s="35"/>
+      <c r="D39" s="36"/>
       <c r="E39" s="15">
         <v>72</v>
       </c>
@@ -5692,10 +5643,10 @@
       <c r="G39" s="16">
         <v>6.34</v>
       </c>
-      <c r="H39" s="35"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -5707,7 +5658,7 @@
       <c r="C40" s="14">
         <v>15.63</v>
       </c>
-      <c r="D40" s="35"/>
+      <c r="D40" s="36"/>
       <c r="E40" s="12">
         <v>73</v>
       </c>
@@ -5717,10 +5668,10 @@
       <c r="G40" s="14">
         <v>28.97</v>
       </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
@@ -5732,7 +5683,7 @@
       <c r="C41" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D41" s="35"/>
+      <c r="D41" s="36"/>
       <c r="E41" s="15">
         <v>74</v>
       </c>
@@ -5742,10 +5693,10 @@
       <c r="G41" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H41" s="35"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -5757,7 +5708,7 @@
       <c r="C42" s="14">
         <v>2.57</v>
       </c>
-      <c r="D42" s="35"/>
+      <c r="D42" s="36"/>
       <c r="E42" s="12">
         <v>75</v>
       </c>
@@ -5767,10 +5718,10 @@
       <c r="G42" s="14">
         <v>6.35</v>
       </c>
-      <c r="H42" s="35"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
@@ -5782,7 +5733,7 @@
       <c r="C43" s="16">
         <v>2.84</v>
       </c>
-      <c r="D43" s="35"/>
+      <c r="D43" s="36"/>
       <c r="E43" s="17"/>
       <c r="F43" s="18" t="s">
         <v>9</v>
@@ -5791,10 +5742,10 @@
         <f>SUM(G6:G42)</f>
         <v>1417.3899999999994</v>
       </c>
-      <c r="H43" s="35"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
     </row>
     <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
@@ -5805,14 +5756,14 @@
         <f>SUM(C6:C43)</f>
         <v>1174.6799999999998</v>
       </c>
-      <c r="D44" s="35"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5857,36 +5808,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -5898,18 +5849,18 @@
       <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -5919,17 +5870,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -5941,7 +5892,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -5951,7 +5902,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -5972,7 +5923,7 @@
       <c r="C6" s="14">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="12">
         <v>14</v>
       </c>
@@ -5982,7 +5933,7 @@
       <c r="G6" s="14">
         <v>5.19</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -5994,7 +5945,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A7" s="44">
+      <c r="A7" s="30">
         <v>2</v>
       </c>
       <c r="B7" s="15" t="s">
@@ -6003,8 +5954,8 @@
       <c r="C7" s="16">
         <v>5.51</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="44">
+      <c r="D7" s="36"/>
+      <c r="E7" s="30">
         <v>15</v>
       </c>
       <c r="F7" s="15" t="s">
@@ -6013,8 +5964,8 @@
       <c r="G7" s="16">
         <v>11.2</v>
       </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="44">
+      <c r="H7" s="36"/>
+      <c r="I7" s="30">
         <v>31</v>
       </c>
       <c r="J7" s="16" t="s">
@@ -6034,7 +5985,7 @@
       <c r="C8" s="14">
         <v>10.08</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="12">
         <v>16</v>
       </c>
@@ -6044,7 +5995,7 @@
       <c r="G8" s="14">
         <v>11.31</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -6056,7 +6007,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="44">
+      <c r="A9" s="30">
         <v>4</v>
       </c>
       <c r="B9" s="15" t="s">
@@ -6065,8 +6016,8 @@
       <c r="C9" s="16">
         <v>149.28</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="44">
+      <c r="D9" s="36"/>
+      <c r="E9" s="30">
         <v>17</v>
       </c>
       <c r="F9" s="15" t="s">
@@ -6075,8 +6026,8 @@
       <c r="G9" s="16">
         <v>26.54</v>
       </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="44">
+      <c r="H9" s="36"/>
+      <c r="I9" s="30">
         <v>33</v>
       </c>
       <c r="J9" s="16" t="s">
@@ -6096,7 +6047,7 @@
       <c r="C10" s="14">
         <v>15.01</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="12">
         <v>18</v>
       </c>
@@ -6106,7 +6057,7 @@
       <c r="G10" s="14">
         <v>13.17</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -6127,8 +6078,8 @@
       <c r="C11" s="23">
         <v>5.22</v>
       </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="44">
+      <c r="D11" s="36"/>
+      <c r="E11" s="30">
         <v>19</v>
       </c>
       <c r="F11" s="15" t="s">
@@ -6137,8 +6088,8 @@
       <c r="G11" s="16">
         <v>8.19</v>
       </c>
-      <c r="H11" s="35"/>
-      <c r="I11" s="44">
+      <c r="H11" s="36"/>
+      <c r="I11" s="30">
         <v>35</v>
       </c>
       <c r="J11" s="16" t="s">
@@ -6158,7 +6109,7 @@
       <c r="C12" s="25">
         <v>15</v>
       </c>
-      <c r="D12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="12">
         <v>20</v>
       </c>
@@ -6168,7 +6119,7 @@
       <c r="G12" s="14">
         <v>27.38</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -6189,8 +6140,8 @@
       <c r="C13" s="23">
         <v>6.27</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="44">
+      <c r="D13" s="36"/>
+      <c r="E13" s="30">
         <v>21</v>
       </c>
       <c r="F13" s="15" t="s">
@@ -6199,7 +6150,7 @@
       <c r="G13" s="23">
         <v>10.44</v>
       </c>
-      <c r="H13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="17"/>
       <c r="J13" s="18" t="s">
         <v>9</v>
@@ -6219,7 +6170,7 @@
       <c r="C14" s="25">
         <v>5.98</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="36"/>
       <c r="E14" s="12">
         <v>22</v>
       </c>
@@ -6229,10 +6180,10 @@
       <c r="G14" s="25">
         <v>11.73</v>
       </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
     </row>
     <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
@@ -6244,8 +6195,8 @@
       <c r="C15" s="23">
         <v>59.38</v>
       </c>
-      <c r="D15" s="35"/>
-      <c r="E15" s="44">
+      <c r="D15" s="36"/>
+      <c r="E15" s="30">
         <v>23</v>
       </c>
       <c r="F15" s="15" t="s">
@@ -6254,10 +6205,10 @@
       <c r="G15" s="23">
         <v>30.61</v>
       </c>
-      <c r="H15" s="35"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
@@ -6269,7 +6220,7 @@
       <c r="C16" s="25">
         <v>16.399999999999999</v>
       </c>
-      <c r="D16" s="35"/>
+      <c r="D16" s="36"/>
       <c r="E16" s="12">
         <v>24</v>
       </c>
@@ -6279,10 +6230,10 @@
       <c r="G16" s="25">
         <v>15</v>
       </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
     </row>
     <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
@@ -6294,8 +6245,8 @@
       <c r="C17" s="23">
         <v>29.22</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="44">
+      <c r="D17" s="36"/>
+      <c r="E17" s="30">
         <v>25</v>
       </c>
       <c r="F17" s="15" t="s">
@@ -6304,10 +6255,10 @@
       <c r="G17" s="23">
         <v>14.98</v>
       </c>
-      <c r="H17" s="35"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
     </row>
     <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
@@ -6319,7 +6270,7 @@
       <c r="C18" s="25">
         <v>29.54</v>
       </c>
-      <c r="D18" s="35"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="12">
         <v>26</v>
       </c>
@@ -6329,10 +6280,10 @@
       <c r="G18" s="25">
         <v>5.23</v>
       </c>
-      <c r="H18" s="35"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
     </row>
     <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
@@ -6343,8 +6294,8 @@
         <f>SUM(C6:C18)</f>
         <v>352.00000000000006</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="44">
+      <c r="D19" s="36"/>
+      <c r="E19" s="30">
         <v>27</v>
       </c>
       <c r="F19" s="15" t="s">
@@ -6353,16 +6304,16 @@
       <c r="G19" s="23">
         <v>6.27</v>
       </c>
-      <c r="H19" s="35"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
     </row>
     <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="35"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="36"/>
       <c r="E20" s="12">
         <v>28</v>
       </c>
@@ -6372,17 +6323,17 @@
       <c r="G20" s="25">
         <v>29.19</v>
       </c>
-      <c r="H20" s="35"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
     </row>
     <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="44">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="30">
         <v>29</v>
       </c>
       <c r="F21" s="15" t="s">
@@ -6391,16 +6342,16 @@
       <c r="G21" s="23">
         <v>29.2</v>
       </c>
-      <c r="H21" s="35"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="36"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18" t="s">
         <v>9</v>
@@ -6409,10 +6360,10 @@
         <f>SUM(G6:G21)</f>
         <v>255.62999999999997</v>
       </c>
-      <c r="H22" s="35"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6436,7 +6387,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -6454,36 +6405,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6495,18 +6446,18 @@
       <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -6516,17 +6467,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -6538,7 +6489,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -6548,7 +6499,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="35"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -6569,7 +6520,7 @@
       <c r="C6" s="14">
         <v>44.29</v>
       </c>
-      <c r="D6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="12">
         <v>5</v>
       </c>
@@ -6579,7 +6530,7 @@
       <c r="G6" s="14">
         <v>53.5</v>
       </c>
-      <c r="H6" s="35"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="12">
         <v>11</v>
       </c>
@@ -6600,7 +6551,7 @@
       <c r="C7" s="16">
         <v>47.34</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="15">
         <v>6</v>
       </c>
@@ -6610,7 +6561,7 @@
       <c r="G7" s="16">
         <v>74.430000000000007</v>
       </c>
-      <c r="H7" s="35"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="15">
         <v>12</v>
       </c>
@@ -6631,7 +6582,7 @@
       <c r="C8" s="14">
         <v>54.22</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
       <c r="E8" s="12">
         <v>7</v>
       </c>
@@ -6641,7 +6592,7 @@
       <c r="G8" s="14">
         <v>53.83</v>
       </c>
-      <c r="H8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="12">
         <v>13</v>
       </c>
@@ -6662,7 +6613,7 @@
       <c r="C9" s="16">
         <v>129.11000000000001</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="36"/>
       <c r="E9" s="15">
         <v>8</v>
       </c>
@@ -6672,7 +6623,7 @@
       <c r="G9" s="16">
         <v>55.33</v>
       </c>
-      <c r="H9" s="35"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="15">
         <v>14</v>
       </c>
@@ -6692,7 +6643,7 @@
         <f>SUM(C6:C9)</f>
         <v>274.96000000000004</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="36"/>
       <c r="E10" s="12">
         <v>9</v>
       </c>
@@ -6702,7 +6653,7 @@
       <c r="G10" s="14">
         <v>54.25</v>
       </c>
-      <c r="H10" s="35"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="12">
         <v>15</v>
       </c>
@@ -6714,10 +6665,10 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="35"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="15">
         <v>10</v>
       </c>
@@ -6727,7 +6678,7 @@
       <c r="G11" s="16">
         <v>54.3</v>
       </c>
-      <c r="H11" s="35"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="15">
         <v>16</v>
       </c>
@@ -6739,10 +6690,10 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="35"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18" t="s">
         <v>9</v>
@@ -6751,7 +6702,7 @@
         <f>SUM(G6:G11)</f>
         <v>345.64</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="12">
         <v>17</v>
       </c>
@@ -6763,14 +6714,14 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="35"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="15">
         <v>18</v>
       </c>
@@ -6782,14 +6733,14 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="12">
         <v>19</v>
       </c>
@@ -6801,14 +6752,14 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="15">
         <v>20</v>
       </c>
@@ -6820,14 +6771,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="17"/>
       <c r="J16" s="18" t="s">
         <v>9</v>
@@ -6836,30 +6787,6 @@
         <f>SUM(K6:K15)</f>
         <v>550.99</v>
       </c>
-    </row>
-    <row r="17" spans="4:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="D17" s="42"/>
-      <c r="H17" s="42"/>
-    </row>
-    <row r="18" spans="4:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="D18" s="42"/>
-      <c r="H18" s="42"/>
-    </row>
-    <row r="19" spans="4:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="D19" s="42"/>
-      <c r="H19" s="42"/>
-    </row>
-    <row r="20" spans="4:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="D20" s="42"/>
-      <c r="H20" s="42"/>
-    </row>
-    <row r="21" spans="4:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="D21" s="42"/>
-      <c r="H21" s="42"/>
-    </row>
-    <row r="22" spans="4:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="D22" s="42"/>
-      <c r="H22" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6876,707 +6803,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="4.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
-    <col min="6" max="6" width="13.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="4.21875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-    </row>
-    <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
-        <v>1</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="5">
-        <f>C20+G23+K14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
-        <v>2</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="5">
-        <f>C21+G24+K15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-    </row>
-    <row r="6" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-    </row>
-    <row r="8" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="16"/>
-    </row>
-    <row r="9" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="14"/>
-    </row>
-    <row r="10" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="16"/>
-    </row>
-    <row r="11" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
-    </row>
-    <row r="12" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="16"/>
-      <c r="P12" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>2</v>
-      </c>
-      <c r="R12" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="14"/>
-      <c r="O13" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="P13" s="1">
-        <v>85.4</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>28.7</v>
-      </c>
-      <c r="R13" s="1">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="23"/>
-    </row>
-    <row r="15" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="25"/>
-    </row>
-    <row r="16" spans="1:18" ht="18" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="23"/>
-      <c r="O16" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="P16" s="1">
-        <v>183.6</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>154.5</v>
-      </c>
-      <c r="R16" s="1">
-        <v>20.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="25"/>
-    </row>
-    <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="23"/>
-    </row>
-    <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-    </row>
-    <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="23"/>
-    </row>
-    <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-    </row>
-    <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="44"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="23"/>
-    </row>
-    <row r="23" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="19">
-        <f>SUM(C7:C22)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="42"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="19">
-        <f>SUM(G7:G22)</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="42"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="19">
-        <f>SUM(K7:K22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="43"/>
-      <c r="E26" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="14"/>
-    </row>
-    <row r="28" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="16"/>
-    </row>
-    <row r="29" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="14"/>
-    </row>
-    <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="16"/>
-    </row>
-    <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="14"/>
-    </row>
-    <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A32" s="44"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="16"/>
-    </row>
-    <row r="33" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="14"/>
-    </row>
-    <row r="34" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A34" s="44"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="23"/>
-    </row>
-    <row r="35" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="25"/>
-    </row>
-    <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A36" s="44"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="23"/>
-    </row>
-    <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="25"/>
-    </row>
-    <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A38" s="44"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="23"/>
-    </row>
-    <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A39" s="12"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="25"/>
-    </row>
-    <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A40" s="44"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="23"/>
-    </row>
-    <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A41" s="12"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="25"/>
-    </row>
-    <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A42" s="44"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="23"/>
-    </row>
-    <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="19">
-        <f>SUM(C27:C42)</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="42"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="19">
-        <f>SUM(G27:G42)</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="42"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="K43" s="19">
-        <f>SUM(K27:K42)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="E2:I2"/>
-    <mergeCell ref="B2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/kronshtatsky/ceilling/ceilling-k.xlsx
+++ b/kronshtatsky/ceilling/ceilling-k.xlsx
@@ -9,17 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10128" firstSheet="6" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10128" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="CF1" sheetId="4" r:id="rId1"/>
     <sheet name="1.1-CF2_СКБ" sheetId="1" r:id="rId2"/>
     <sheet name="2.1-CF2_Краска" sheetId="2" r:id="rId3"/>
     <sheet name="3.1-CF2_Монтаж" sheetId="3" r:id="rId4"/>
-    <sheet name="2.2-CF1_Краск" sheetId="6" r:id="rId5"/>
-    <sheet name="1.2-CF1_СКБ" sheetId="7" r:id="rId6"/>
-    <sheet name="3.2-CF3_Монтаж" sheetId="8" r:id="rId7"/>
-    <sheet name="3.3-CF4_Монтаж" sheetId="9" r:id="rId8"/>
+    <sheet name="2.2-CF1_КрскДопСл" sheetId="10" r:id="rId5"/>
+    <sheet name="2.2-CF1_Краск" sheetId="6" r:id="rId6"/>
+    <sheet name="1.2-CF1_СКБ" sheetId="7" r:id="rId7"/>
+    <sheet name="3.2-CF3_Монтаж" sheetId="8" r:id="rId8"/>
+    <sheet name="3.3-CF4_Монтаж" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511" refMode="R1C1"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="170">
   <si>
     <t>Спецификация выполненных работ</t>
   </si>
@@ -535,6 +536,12 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>Лакокрасочные работы СКБ / окраска потолков</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип: CF1. Покраска Потолка</t>
   </si>
 </sst>
 </file>
@@ -794,7 +801,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -887,12 +894,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -907,6 +908,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1325,36 +1338,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1366,18 +1379,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1387,17 +1400,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -1409,7 +1422,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="38"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -1419,7 +1432,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="34"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -1440,7 +1453,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -1450,7 +1463,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -1471,7 +1484,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -1481,7 +1494,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -1502,7 +1515,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -1512,7 +1525,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -1533,7 +1546,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -1543,7 +1556,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -1564,7 +1577,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -1574,7 +1587,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -1595,7 +1608,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -1605,7 +1618,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -1626,7 +1639,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -1636,7 +1649,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -1657,7 +1670,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -1667,7 +1680,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="36"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -1688,7 +1701,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="36"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -1698,7 +1711,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="36"/>
+      <c r="H14" s="34"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -1719,7 +1732,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -1729,7 +1742,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="36"/>
+      <c r="H15" s="34"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -1750,7 +1763,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="36"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -1761,7 +1774,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -1782,7 +1795,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="36"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -1792,7 +1805,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="36"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -1815,7 +1828,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="34"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -1825,7 +1838,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="36"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -1846,7 +1859,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="34"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -1855,7 +1868,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="36"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -1876,11 +1889,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="36"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -1900,14 +1913,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -1918,27 +1931,27 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G2:I2"/>
     <mergeCell ref="I21:K22"/>
     <mergeCell ref="E20:G22"/>
     <mergeCell ref="H5:H22"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="D5:D22"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="G2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1962,36 +1975,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2003,18 +2016,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2024,17 +2037,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2046,7 +2059,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="38"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -2056,7 +2069,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="34"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -2077,7 +2090,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -2087,7 +2100,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -2108,7 +2121,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -2118,7 +2131,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -2139,7 +2152,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -2149,7 +2162,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -2170,7 +2183,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -2180,7 +2193,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -2201,7 +2214,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -2211,7 +2224,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -2232,7 +2245,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -2242,7 +2255,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -2263,7 +2276,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -2273,7 +2286,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -2294,7 +2307,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -2304,7 +2317,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="36"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -2325,7 +2338,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="36"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -2335,7 +2348,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="36"/>
+      <c r="H14" s="34"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -2356,7 +2369,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -2366,7 +2379,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="36"/>
+      <c r="H15" s="34"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -2387,7 +2400,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="36"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -2398,7 +2411,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -2419,7 +2432,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="36"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -2429,7 +2442,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="36"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -2452,7 +2465,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="34"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -2462,7 +2475,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="36"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -2483,7 +2496,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="34"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -2492,7 +2505,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="36"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -2513,11 +2526,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="36"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -2537,14 +2550,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -2555,14 +2568,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2599,36 +2612,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2640,18 +2653,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2661,17 +2674,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2683,7 +2696,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="38"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -2693,7 +2706,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="34"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -2714,7 +2727,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -2724,7 +2737,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -2745,7 +2758,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -2755,7 +2768,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -2776,7 +2789,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -2786,7 +2799,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -2807,7 +2820,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -2817,7 +2830,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -2838,7 +2851,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -2848,7 +2861,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -2869,7 +2882,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -2879,7 +2892,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -2900,7 +2913,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -2910,7 +2923,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -2931,7 +2944,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -2941,7 +2954,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="36"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -2962,7 +2975,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="36"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -2972,7 +2985,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="36"/>
+      <c r="H14" s="34"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -2993,7 +3006,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -3003,7 +3016,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="36"/>
+      <c r="H15" s="34"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -3024,7 +3037,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="36"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -3035,7 +3048,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -3056,7 +3069,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="36"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -3066,7 +3079,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="36"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -3089,7 +3102,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="34"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -3099,7 +3112,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="36"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -3120,7 +3133,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="34"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -3129,7 +3142,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="36"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -3150,11 +3163,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="36"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -3174,14 +3187,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -3192,14 +3205,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3220,6 +3233,1228 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="11.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5546875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="4.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="63.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31">
+        <v>1</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="5">
+        <f>K28+G42+C43</f>
+        <v>2919.5279739999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="36"/>
+      <c r="E5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="34"/>
+      <c r="I5" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>1</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="14">
+        <f>114.61+85.5+5.75</f>
+        <v>205.86</v>
+      </c>
+      <c r="D6" s="34"/>
+      <c r="E6" s="12">
+        <v>38</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="14">
+        <v>76.349999999999994</v>
+      </c>
+      <c r="H6" s="34"/>
+      <c r="I6" s="12">
+        <v>74</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="14">
+        <v>85.255876000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>2</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="16">
+        <v>15.68</v>
+      </c>
+      <c r="D7" s="34"/>
+      <c r="E7" s="15">
+        <v>39</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="16">
+        <v>17.690000000000001</v>
+      </c>
+      <c r="H7" s="34"/>
+      <c r="I7" s="15">
+        <v>75</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="16">
+        <v>21.566807000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>3</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="14">
+        <v>5.01</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="12">
+        <v>40</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5.15</v>
+      </c>
+      <c r="H8" s="34"/>
+      <c r="I8" s="12">
+        <v>76</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="14">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>4</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="16">
+        <v>6.01</v>
+      </c>
+      <c r="D9" s="34"/>
+      <c r="E9" s="15">
+        <v>41</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="16">
+        <v>9.48</v>
+      </c>
+      <c r="H9" s="34"/>
+      <c r="I9" s="15">
+        <v>77</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" s="16">
+        <v>11.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>5</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="14">
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="12">
+        <v>42</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="14">
+        <v>198.78</v>
+      </c>
+      <c r="H10" s="34"/>
+      <c r="I10" s="12">
+        <v>78</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="14">
+        <v>114.03</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>6</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="16">
+        <v>97.45</v>
+      </c>
+      <c r="D11" s="34"/>
+      <c r="E11" s="15">
+        <v>43</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="16">
+        <v>14.98</v>
+      </c>
+      <c r="H11" s="34"/>
+      <c r="I11" s="15">
+        <v>79</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="16">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
+        <v>7</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="14">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="D12" s="34"/>
+      <c r="E12" s="12">
+        <v>44</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6.46</v>
+      </c>
+      <c r="H12" s="34"/>
+      <c r="I12" s="12">
+        <v>80</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="14">
+        <v>106.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>8</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="16">
+        <v>10</v>
+      </c>
+      <c r="D13" s="34"/>
+      <c r="E13" s="15">
+        <v>45</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="16">
+        <v>106.83</v>
+      </c>
+      <c r="H13" s="34"/>
+      <c r="I13" s="15">
+        <v>81</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" s="16">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <v>9</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="14">
+        <v>10.38</v>
+      </c>
+      <c r="D14" s="34"/>
+      <c r="E14" s="15">
+        <v>46</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="16">
+        <v>14.81</v>
+      </c>
+      <c r="H14" s="34"/>
+      <c r="I14" s="12">
+        <v>82</v>
+      </c>
+      <c r="J14" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="14">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
+        <v>10</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="16">
+        <v>25.29</v>
+      </c>
+      <c r="D15" s="34"/>
+      <c r="E15" s="12">
+        <v>47</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="14">
+        <v>14.79</v>
+      </c>
+      <c r="H15" s="34"/>
+      <c r="I15" s="15">
+        <v>83</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="16">
+        <v>14.92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="12">
+        <v>11</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="14">
+        <v>21.62</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="15">
+        <v>48</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="16">
+        <v>5.14</v>
+      </c>
+      <c r="H16" s="34"/>
+      <c r="I16" s="12">
+        <v>84</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="14">
+        <v>244.875291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>12</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="16">
+        <v>28.06</v>
+      </c>
+      <c r="D17" s="34"/>
+      <c r="E17" s="12">
+        <v>49</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="14">
+        <v>10.32</v>
+      </c>
+      <c r="H17" s="34"/>
+      <c r="I17" s="15">
+        <v>85</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17" s="16">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="12">
+        <v>13</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="14">
+        <v>96.32</v>
+      </c>
+      <c r="D18" s="34"/>
+      <c r="E18" s="15">
+        <v>50</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="16">
+        <v>11.76</v>
+      </c>
+      <c r="H18" s="34"/>
+      <c r="I18" s="12">
+        <v>86</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" s="14">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>14</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="16">
+        <v>111.79</v>
+      </c>
+      <c r="D19" s="34"/>
+      <c r="E19" s="12">
+        <v>51</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" s="14">
+        <v>30.61</v>
+      </c>
+      <c r="H19" s="34"/>
+      <c r="I19" s="15">
+        <v>87</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="16">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A20" s="12">
+        <v>15</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="14">
+        <v>6.45</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="15">
+        <v>52</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" s="16">
+        <v>26.54</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="12">
+        <v>88</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" s="14">
+        <v>5.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>16</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="16">
+        <v>9.91</v>
+      </c>
+      <c r="D21" s="34"/>
+      <c r="E21" s="12">
+        <v>53</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="14">
+        <v>13.17</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="15">
+        <v>89</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="16">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
+        <v>17</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="16">
+        <v>14.81</v>
+      </c>
+      <c r="D22" s="34"/>
+      <c r="E22" s="15">
+        <v>54</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="16">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="H22" s="34"/>
+      <c r="I22" s="12">
+        <v>90</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="14">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A23" s="12">
+        <v>18</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="14">
+        <v>5.19</v>
+      </c>
+      <c r="D23" s="34"/>
+      <c r="E23" s="12">
+        <v>55</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="14">
+        <v>27.37</v>
+      </c>
+      <c r="H23" s="34"/>
+      <c r="I23" s="15">
+        <v>91</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="16">
+        <v>36.46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A24" s="15">
+        <v>19</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="16">
+        <v>14.79</v>
+      </c>
+      <c r="D24" s="34"/>
+      <c r="E24" s="15">
+        <v>56</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="16">
+        <v>78.58</v>
+      </c>
+      <c r="H24" s="34"/>
+      <c r="I24" s="12">
+        <v>92</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="14">
+        <v>59.68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A25" s="12">
+        <v>20</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="14">
+        <v>3.8</v>
+      </c>
+      <c r="D25" s="34"/>
+      <c r="E25" s="12">
+        <v>57</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5.09</v>
+      </c>
+      <c r="H25" s="34"/>
+      <c r="I25" s="15">
+        <v>93</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K25" s="23">
+        <v>29.97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A26" s="15">
+        <v>21</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="D26" s="34"/>
+      <c r="E26" s="15">
+        <v>58</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="23">
+        <v>11.06</v>
+      </c>
+      <c r="H26" s="34"/>
+      <c r="I26" s="24">
+        <v>94</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K26" s="25">
+        <v>28.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A27" s="12">
+        <v>22</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="14">
+        <v>5.67</v>
+      </c>
+      <c r="D27" s="34"/>
+      <c r="E27" s="24">
+        <v>59</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G27" s="25">
+        <v>11.17</v>
+      </c>
+      <c r="H27" s="34"/>
+      <c r="I27" s="15">
+        <v>95</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="23">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
+        <v>23</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="16">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D28" s="34"/>
+      <c r="E28" s="15">
+        <v>60</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" s="23">
+        <v>8.33</v>
+      </c>
+      <c r="H28" s="34"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="19">
+        <f>SUM(K6:K27)</f>
+        <v>837.08797400000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A29" s="12">
+        <v>24</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="14">
+        <v>39.9</v>
+      </c>
+      <c r="D29" s="34"/>
+      <c r="E29" s="24">
+        <v>61</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="25">
+        <v>5.6</v>
+      </c>
+      <c r="H29" s="34"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+    </row>
+    <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A30" s="15">
+        <v>25</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="16">
+        <v>10.85</v>
+      </c>
+      <c r="D30" s="34"/>
+      <c r="E30" s="15">
+        <v>62</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="23">
+        <v>6.02</v>
+      </c>
+      <c r="H30" s="34"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
+      <c r="K30" s="40"/>
+    </row>
+    <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A31" s="12">
+        <v>26</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="14">
+        <v>5.49</v>
+      </c>
+      <c r="D31" s="34"/>
+      <c r="E31" s="24">
+        <v>63</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="25">
+        <v>37.04</v>
+      </c>
+      <c r="H31" s="34"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+    </row>
+    <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A32" s="15">
+        <v>27</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="16">
+        <v>9.66</v>
+      </c>
+      <c r="D32" s="34"/>
+      <c r="E32" s="15">
+        <v>64</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="23">
+        <v>6.28</v>
+      </c>
+      <c r="H32" s="34"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40"/>
+    </row>
+    <row r="33" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A33" s="12">
+        <v>28</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="14">
+        <v>6.28</v>
+      </c>
+      <c r="D33" s="34"/>
+      <c r="E33" s="24">
+        <v>65</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="25">
+        <v>5.98</v>
+      </c>
+      <c r="H33" s="34"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="40"/>
+    </row>
+    <row r="34" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A34" s="15">
+        <v>29</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" s="16">
+        <v>5.85</v>
+      </c>
+      <c r="D34" s="34"/>
+      <c r="E34" s="15">
+        <v>66</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G34" s="23">
+        <v>6.34</v>
+      </c>
+      <c r="H34" s="34"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+    </row>
+    <row r="35" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <v>30</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" s="14">
+        <v>29</v>
+      </c>
+      <c r="D35" s="34"/>
+      <c r="E35" s="12">
+        <v>67</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" s="14">
+        <v>28.97</v>
+      </c>
+      <c r="H35" s="34"/>
+      <c r="I35" s="40"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+    </row>
+    <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A36" s="15">
+        <v>31</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="16">
+        <v>67.27</v>
+      </c>
+      <c r="D36" s="34"/>
+      <c r="E36" s="15">
+        <v>68</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="G36" s="16">
+        <v>61.92</v>
+      </c>
+      <c r="H36" s="34"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
+    </row>
+    <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <v>32</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60.17</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="E37" s="12">
+        <v>69</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="G37" s="14">
+        <v>72.55</v>
+      </c>
+      <c r="H37" s="34"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+    </row>
+    <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A38" s="15">
+        <v>33</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="16">
+        <v>29.3</v>
+      </c>
+      <c r="D38" s="34"/>
+      <c r="E38" s="15">
+        <v>70</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G38" s="16">
+        <v>6.34</v>
+      </c>
+      <c r="H38" s="34"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="40"/>
+    </row>
+    <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A39" s="12">
+        <v>34</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C39" s="14">
+        <v>15.63</v>
+      </c>
+      <c r="D39" s="34"/>
+      <c r="E39" s="12">
+        <v>71</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G39" s="14">
+        <v>28.97</v>
+      </c>
+      <c r="H39" s="34"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+    </row>
+    <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A40" s="15">
+        <v>35</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" s="16">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="D40" s="34"/>
+      <c r="E40" s="15">
+        <v>72</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" s="16">
+        <v>72.760000000000005</v>
+      </c>
+      <c r="H40" s="34"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+    </row>
+    <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A41" s="12">
+        <v>36</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="14">
+        <v>2.57</v>
+      </c>
+      <c r="D41" s="34"/>
+      <c r="E41" s="12">
+        <v>73</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6.35</v>
+      </c>
+      <c r="H41" s="34"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+    </row>
+    <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A42" s="15">
+        <v>37</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="16">
+        <v>2.84</v>
+      </c>
+      <c r="D42" s="34"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="19">
+        <f>SUM(G6:G41)</f>
+        <v>1057.7099999999998</v>
+      </c>
+      <c r="H42" s="34"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="40"/>
+      <c r="K42" s="40"/>
+    </row>
+    <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A43" s="17"/>
+      <c r="B43" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="19">
+        <f>SUM(C6:C42)</f>
+        <v>1024.7299999999998</v>
+      </c>
+      <c r="D43" s="34"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="D5:D43"/>
+    <mergeCell ref="H5:H43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="I29:K43"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3237,36 +4472,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -3278,18 +4513,18 @@
       <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -3302,18 +4537,18 @@
       <c r="A4" s="21">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="33" t="s">
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="39" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
       <c r="J4" s="4" t="s">
         <v>6</v>
       </c>
@@ -3323,17 +4558,17 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -3345,7 +4580,7 @@
       <c r="C6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="38"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="6" t="s">
         <v>1</v>
       </c>
@@ -3355,7 +4590,7 @@
       <c r="G6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="9" t="s">
         <v>1</v>
       </c>
@@ -3377,7 +4612,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="12">
         <v>39</v>
       </c>
@@ -3387,7 +4622,7 @@
       <c r="G7" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="12">
         <v>76</v>
       </c>
@@ -3408,7 +4643,7 @@
       <c r="C8" s="16">
         <v>15.68</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="15">
         <v>40</v>
       </c>
@@ -3418,7 +4653,7 @@
       <c r="G8" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="15">
         <v>77</v>
       </c>
@@ -3439,7 +4674,7 @@
       <c r="C9" s="14">
         <v>5.01</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="12">
         <v>41</v>
       </c>
@@ -3449,7 +4684,7 @@
       <c r="G9" s="14">
         <v>5.15</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="12">
         <v>78</v>
       </c>
@@ -3470,7 +4705,7 @@
       <c r="C10" s="16">
         <v>6.01</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="15">
         <v>42</v>
       </c>
@@ -3480,7 +4715,7 @@
       <c r="G10" s="16">
         <v>9.48</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="15">
         <v>79</v>
       </c>
@@ -3501,7 +4736,7 @@
       <c r="C11" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="12">
         <v>43</v>
       </c>
@@ -3511,7 +4746,7 @@
       <c r="G11" s="14">
         <v>198.78</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="12">
         <v>80</v>
       </c>
@@ -3532,7 +4767,7 @@
       <c r="C12" s="16">
         <v>97.45</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="15">
         <v>44</v>
       </c>
@@ -3542,7 +4777,7 @@
       <c r="G12" s="16">
         <v>14.98</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="15">
         <v>81</v>
       </c>
@@ -3563,7 +4798,7 @@
       <c r="C13" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="12">
         <v>45</v>
       </c>
@@ -3573,7 +4808,7 @@
       <c r="G13" s="14">
         <v>6.46</v>
       </c>
-      <c r="H13" s="36"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="12">
         <v>82</v>
       </c>
@@ -3594,7 +4829,7 @@
       <c r="C14" s="16">
         <v>10</v>
       </c>
-      <c r="D14" s="36"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="15">
         <v>46</v>
       </c>
@@ -3604,7 +4839,7 @@
       <c r="G14" s="16">
         <v>106.83</v>
       </c>
-      <c r="H14" s="36"/>
+      <c r="H14" s="34"/>
       <c r="I14" s="15">
         <v>83</v>
       </c>
@@ -3625,7 +4860,7 @@
       <c r="C15" s="14">
         <v>10.38</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="12">
         <v>47</v>
       </c>
@@ -3635,7 +4870,7 @@
       <c r="G15" s="14">
         <v>359.68</v>
       </c>
-      <c r="H15" s="36"/>
+      <c r="H15" s="34"/>
       <c r="I15" s="12">
         <v>84</v>
       </c>
@@ -3656,7 +4891,7 @@
       <c r="C16" s="16">
         <v>25.29</v>
       </c>
-      <c r="D16" s="36"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="15">
         <v>48</v>
       </c>
@@ -3666,7 +4901,7 @@
       <c r="G16" s="16">
         <v>14.81</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="15">
         <v>85</v>
       </c>
@@ -3687,7 +4922,7 @@
       <c r="C17" s="14">
         <v>21.62</v>
       </c>
-      <c r="D17" s="36"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="12">
         <v>49</v>
       </c>
@@ -3697,7 +4932,7 @@
       <c r="G17" s="14">
         <v>14.79</v>
       </c>
-      <c r="H17" s="36"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="12">
         <v>86</v>
       </c>
@@ -3718,7 +4953,7 @@
       <c r="C18" s="16">
         <v>28.06</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="34"/>
       <c r="E18" s="15">
         <v>50</v>
       </c>
@@ -3728,7 +4963,7 @@
       <c r="G18" s="16">
         <v>5.14</v>
       </c>
-      <c r="H18" s="36"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="15">
         <v>87</v>
       </c>
@@ -3749,7 +4984,7 @@
       <c r="C19" s="14">
         <v>96.32</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="34"/>
       <c r="E19" s="12">
         <v>51</v>
       </c>
@@ -3759,7 +4994,7 @@
       <c r="G19" s="14">
         <v>10.32</v>
       </c>
-      <c r="H19" s="36"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="12">
         <v>88</v>
       </c>
@@ -3780,7 +5015,7 @@
       <c r="C20" s="16">
         <v>111.79</v>
       </c>
-      <c r="D20" s="36"/>
+      <c r="D20" s="34"/>
       <c r="E20" s="15">
         <v>52</v>
       </c>
@@ -3790,7 +5025,7 @@
       <c r="G20" s="16">
         <v>11.76</v>
       </c>
-      <c r="H20" s="36"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="15">
         <v>89</v>
       </c>
@@ -3811,7 +5046,7 @@
       <c r="C21" s="14">
         <v>6.45</v>
       </c>
-      <c r="D21" s="36"/>
+      <c r="D21" s="34"/>
       <c r="E21" s="12">
         <v>53</v>
       </c>
@@ -3821,7 +5056,7 @@
       <c r="G21" s="14">
         <v>30.61</v>
       </c>
-      <c r="H21" s="36"/>
+      <c r="H21" s="34"/>
       <c r="I21" s="12">
         <v>90</v>
       </c>
@@ -3842,7 +5077,7 @@
       <c r="C22" s="16">
         <v>9.91</v>
       </c>
-      <c r="D22" s="36"/>
+      <c r="D22" s="34"/>
       <c r="E22" s="15">
         <v>54</v>
       </c>
@@ -3852,7 +5087,7 @@
       <c r="G22" s="16">
         <v>26.54</v>
       </c>
-      <c r="H22" s="36"/>
+      <c r="H22" s="34"/>
       <c r="I22" s="15">
         <v>91</v>
       </c>
@@ -3873,7 +5108,7 @@
       <c r="C23" s="14">
         <v>149.94999999999999</v>
       </c>
-      <c r="D23" s="36"/>
+      <c r="D23" s="34"/>
       <c r="E23" s="12">
         <v>55</v>
       </c>
@@ -3883,7 +5118,7 @@
       <c r="G23" s="14">
         <v>13.17</v>
       </c>
-      <c r="H23" s="36"/>
+      <c r="H23" s="34"/>
       <c r="I23" s="12">
         <v>92</v>
       </c>
@@ -3904,7 +5139,7 @@
       <c r="C24" s="16">
         <v>14.81</v>
       </c>
-      <c r="D24" s="36"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="15">
         <v>56</v>
       </c>
@@ -3914,7 +5149,7 @@
       <c r="G24" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H24" s="36"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="15">
         <v>93</v>
       </c>
@@ -3935,7 +5170,7 @@
       <c r="C25" s="14">
         <v>5.19</v>
       </c>
-      <c r="D25" s="36"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="12">
         <v>57</v>
       </c>
@@ -3945,7 +5180,7 @@
       <c r="G25" s="14">
         <v>27.37</v>
       </c>
-      <c r="H25" s="36"/>
+      <c r="H25" s="34"/>
       <c r="I25" s="12">
         <v>94</v>
       </c>
@@ -3966,7 +5201,7 @@
       <c r="C26" s="16">
         <v>14.79</v>
       </c>
-      <c r="D26" s="36"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="15">
         <v>58</v>
       </c>
@@ -3976,7 +5211,7 @@
       <c r="G26" s="16">
         <v>78.58</v>
       </c>
-      <c r="H26" s="36"/>
+      <c r="H26" s="34"/>
       <c r="I26" s="15">
         <v>95</v>
       </c>
@@ -3997,7 +5232,7 @@
       <c r="C27" s="14">
         <v>3.8</v>
       </c>
-      <c r="D27" s="36"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="12">
         <v>59</v>
       </c>
@@ -4007,7 +5242,7 @@
       <c r="G27" s="14">
         <v>5.09</v>
       </c>
-      <c r="H27" s="36"/>
+      <c r="H27" s="34"/>
       <c r="I27" s="24">
         <v>96</v>
       </c>
@@ -4028,7 +5263,7 @@
       <c r="C28" s="16">
         <v>4.5</v>
       </c>
-      <c r="D28" s="36"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="15">
         <v>60</v>
       </c>
@@ -4038,7 +5273,7 @@
       <c r="G28" s="23">
         <v>11.06</v>
       </c>
-      <c r="H28" s="36"/>
+      <c r="H28" s="34"/>
       <c r="I28" s="15">
         <v>97</v>
       </c>
@@ -4059,7 +5294,7 @@
       <c r="C29" s="14">
         <v>5.67</v>
       </c>
-      <c r="D29" s="36"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="24">
         <v>61</v>
       </c>
@@ -4069,7 +5304,7 @@
       <c r="G29" s="25">
         <v>11.17</v>
       </c>
-      <c r="H29" s="36"/>
+      <c r="H29" s="34"/>
       <c r="I29" s="17"/>
       <c r="J29" s="18" t="s">
         <v>9</v>
@@ -4089,7 +5324,7 @@
       <c r="C30" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D30" s="36"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="15">
         <v>62</v>
       </c>
@@ -4099,10 +5334,10 @@
       <c r="G30" s="23">
         <v>8.33</v>
       </c>
-      <c r="H30" s="36"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="42"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
@@ -4114,7 +5349,7 @@
       <c r="C31" s="14">
         <v>39.9</v>
       </c>
-      <c r="D31" s="36"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="24">
         <v>63</v>
       </c>
@@ -4124,12 +5359,12 @@
       <c r="G31" s="25">
         <v>5.6</v>
       </c>
-      <c r="H31" s="36"/>
-      <c r="I31" s="39" t="s">
+      <c r="H31" s="34"/>
+      <c r="I31" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="J31" s="40"/>
-      <c r="K31" s="41"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="43"/>
     </row>
     <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
@@ -4141,7 +5376,7 @@
       <c r="C32" s="16">
         <v>10.85</v>
       </c>
-      <c r="D32" s="36"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="15">
         <v>64</v>
       </c>
@@ -4151,7 +5386,7 @@
       <c r="G32" s="23">
         <v>6.02</v>
       </c>
-      <c r="H32" s="36"/>
+      <c r="H32" s="34"/>
       <c r="I32" s="27" t="s">
         <v>1</v>
       </c>
@@ -4172,7 +5407,7 @@
       <c r="C33" s="14">
         <v>5.49</v>
       </c>
-      <c r="D33" s="36"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="24">
         <v>65</v>
       </c>
@@ -4182,7 +5417,7 @@
       <c r="G33" s="25">
         <v>37.04</v>
       </c>
-      <c r="H33" s="36"/>
+      <c r="H33" s="34"/>
       <c r="I33" s="15" t="s">
         <v>153</v>
       </c>
@@ -4204,7 +5439,7 @@
       <c r="C34" s="16">
         <v>9.66</v>
       </c>
-      <c r="D34" s="36"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="15">
         <v>66</v>
       </c>
@@ -4214,7 +5449,7 @@
       <c r="G34" s="23">
         <v>6.28</v>
       </c>
-      <c r="H34" s="36"/>
+      <c r="H34" s="34"/>
       <c r="I34" s="17"/>
       <c r="J34" s="18" t="s">
         <v>9</v>
@@ -4234,7 +5469,7 @@
       <c r="C35" s="14">
         <v>6.28</v>
       </c>
-      <c r="D35" s="36"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="24">
         <v>67</v>
       </c>
@@ -4244,10 +5479,10 @@
       <c r="G35" s="25">
         <v>5.98</v>
       </c>
-      <c r="H35" s="36"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
@@ -4259,7 +5494,7 @@
       <c r="C36" s="16">
         <v>5.85</v>
       </c>
-      <c r="D36" s="36"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="15">
         <v>68</v>
       </c>
@@ -4269,10 +5504,10 @@
       <c r="G36" s="23">
         <v>6.34</v>
       </c>
-      <c r="H36" s="36"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
@@ -4284,7 +5519,7 @@
       <c r="C37" s="14">
         <v>29</v>
       </c>
-      <c r="D37" s="36"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="12">
         <v>69</v>
       </c>
@@ -4294,10 +5529,10 @@
       <c r="G37" s="14">
         <v>28.97</v>
       </c>
-      <c r="H37" s="36"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
@@ -4309,7 +5544,7 @@
       <c r="C38" s="16">
         <v>67.27</v>
       </c>
-      <c r="D38" s="36"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="15">
         <v>70</v>
       </c>
@@ -4319,10 +5554,10 @@
       <c r="G38" s="16">
         <v>61.92</v>
       </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="35"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
@@ -4334,7 +5569,7 @@
       <c r="C39" s="14">
         <v>60.17</v>
       </c>
-      <c r="D39" s="36"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="12">
         <v>71</v>
       </c>
@@ -4344,10 +5579,10 @@
       <c r="G39" s="14">
         <v>72.55</v>
       </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
@@ -4359,7 +5594,7 @@
       <c r="C40" s="16">
         <v>29.3</v>
       </c>
-      <c r="D40" s="36"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="15">
         <v>72</v>
       </c>
@@ -4369,10 +5604,10 @@
       <c r="G40" s="16">
         <v>6.34</v>
       </c>
-      <c r="H40" s="36"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
@@ -4384,7 +5619,7 @@
       <c r="C41" s="14">
         <v>15.63</v>
       </c>
-      <c r="D41" s="36"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="12">
         <v>73</v>
       </c>
@@ -4394,10 +5629,10 @@
       <c r="G41" s="14">
         <v>28.97</v>
       </c>
-      <c r="H41" s="36"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="35"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
@@ -4409,7 +5644,7 @@
       <c r="C42" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D42" s="36"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="15">
         <v>74</v>
       </c>
@@ -4419,10 +5654,10 @@
       <c r="G42" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H42" s="36"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="35"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
@@ -4434,7 +5669,7 @@
       <c r="C43" s="14">
         <v>2.57</v>
       </c>
-      <c r="D43" s="36"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="12">
         <v>75</v>
       </c>
@@ -4444,10 +5679,10 @@
       <c r="G43" s="14">
         <v>6.35</v>
       </c>
-      <c r="H43" s="36"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
     </row>
     <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
@@ -4459,7 +5694,7 @@
       <c r="C44" s="16">
         <v>2.84</v>
       </c>
-      <c r="D44" s="36"/>
+      <c r="D44" s="34"/>
       <c r="E44" s="17"/>
       <c r="F44" s="18" t="s">
         <v>9</v>
@@ -4468,10 +5703,10 @@
         <f>SUM(G7:G43)</f>
         <v>1417.3899999999994</v>
       </c>
-      <c r="H44" s="36"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
     </row>
     <row r="45" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
@@ -4482,17 +5717,23 @@
         <f>SUM(C7:C44)</f>
         <v>1174.6799999999998</v>
       </c>
-      <c r="D45" s="36"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="D6:D45"/>
+    <mergeCell ref="H6:H45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="I35:K45"/>
+    <mergeCell ref="I30:K30"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="G4:I4"/>
@@ -4501,12 +5742,6 @@
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="D6:D45"/>
-    <mergeCell ref="H6:H45"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="I35:K45"/>
-    <mergeCell ref="I30:K30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -4516,7 +5751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4535,36 +5770,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4576,18 +5811,18 @@
       <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -4597,17 +5832,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -4619,7 +5854,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="38"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -4629,7 +5864,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="34"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -4651,7 +5886,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="12">
         <v>39</v>
       </c>
@@ -4661,7 +5896,7 @@
       <c r="G6" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="12">
         <v>76</v>
       </c>
@@ -4682,7 +5917,7 @@
       <c r="C7" s="16">
         <v>15.68</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="15">
         <v>40</v>
       </c>
@@ -4692,7 +5927,7 @@
       <c r="G7" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="15">
         <v>77</v>
       </c>
@@ -4713,7 +5948,7 @@
       <c r="C8" s="14">
         <v>5.01</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="12">
         <v>41</v>
       </c>
@@ -4723,7 +5958,7 @@
       <c r="G8" s="14">
         <v>5.15</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="12">
         <v>78</v>
       </c>
@@ -4744,7 +5979,7 @@
       <c r="C9" s="16">
         <v>6.01</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="15">
         <v>42</v>
       </c>
@@ -4754,7 +5989,7 @@
       <c r="G9" s="16">
         <v>9.48</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="15">
         <v>79</v>
       </c>
@@ -4775,7 +6010,7 @@
       <c r="C10" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="12">
         <v>43</v>
       </c>
@@ -4785,7 +6020,7 @@
       <c r="G10" s="14">
         <v>198.78</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="12">
         <v>80</v>
       </c>
@@ -4806,7 +6041,7 @@
       <c r="C11" s="16">
         <v>97.45</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="15">
         <v>44</v>
       </c>
@@ -4816,7 +6051,7 @@
       <c r="G11" s="16">
         <v>14.98</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="15">
         <v>81</v>
       </c>
@@ -4837,7 +6072,7 @@
       <c r="C12" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="12">
         <v>45</v>
       </c>
@@ -4847,7 +6082,7 @@
       <c r="G12" s="14">
         <v>6.46</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="12">
         <v>82</v>
       </c>
@@ -4868,7 +6103,7 @@
       <c r="C13" s="16">
         <v>10</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="15">
         <v>46</v>
       </c>
@@ -4878,7 +6113,7 @@
       <c r="G13" s="16">
         <v>106.83</v>
       </c>
-      <c r="H13" s="36"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="15">
         <v>83</v>
       </c>
@@ -4899,7 +6134,7 @@
       <c r="C14" s="14">
         <v>10.38</v>
       </c>
-      <c r="D14" s="36"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="12">
         <v>47</v>
       </c>
@@ -4909,7 +6144,7 @@
       <c r="G14" s="14">
         <v>359.68</v>
       </c>
-      <c r="H14" s="36"/>
+      <c r="H14" s="34"/>
       <c r="I14" s="12">
         <v>84</v>
       </c>
@@ -4930,7 +6165,7 @@
       <c r="C15" s="16">
         <v>25.29</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="15">
         <v>48</v>
       </c>
@@ -4940,7 +6175,7 @@
       <c r="G15" s="16">
         <v>14.81</v>
       </c>
-      <c r="H15" s="36"/>
+      <c r="H15" s="34"/>
       <c r="I15" s="15">
         <v>85</v>
       </c>
@@ -4961,7 +6196,7 @@
       <c r="C16" s="14">
         <v>21.62</v>
       </c>
-      <c r="D16" s="36"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="12">
         <v>49</v>
       </c>
@@ -4971,7 +6206,7 @@
       <c r="G16" s="14">
         <v>14.79</v>
       </c>
-      <c r="H16" s="36"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="12">
         <v>86</v>
       </c>
@@ -4992,7 +6227,7 @@
       <c r="C17" s="16">
         <v>28.06</v>
       </c>
-      <c r="D17" s="36"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="15">
         <v>50</v>
       </c>
@@ -5002,7 +6237,7 @@
       <c r="G17" s="16">
         <v>5.14</v>
       </c>
-      <c r="H17" s="36"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="15">
         <v>87</v>
       </c>
@@ -5023,7 +6258,7 @@
       <c r="C18" s="14">
         <v>96.32</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="34"/>
       <c r="E18" s="12">
         <v>51</v>
       </c>
@@ -5033,7 +6268,7 @@
       <c r="G18" s="14">
         <v>10.32</v>
       </c>
-      <c r="H18" s="36"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="12">
         <v>88</v>
       </c>
@@ -5054,7 +6289,7 @@
       <c r="C19" s="16">
         <v>111.79</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="34"/>
       <c r="E19" s="15">
         <v>52</v>
       </c>
@@ -5064,7 +6299,7 @@
       <c r="G19" s="16">
         <v>11.76</v>
       </c>
-      <c r="H19" s="36"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="15">
         <v>89</v>
       </c>
@@ -5085,7 +6320,7 @@
       <c r="C20" s="14">
         <v>6.45</v>
       </c>
-      <c r="D20" s="36"/>
+      <c r="D20" s="34"/>
       <c r="E20" s="12">
         <v>53</v>
       </c>
@@ -5095,7 +6330,7 @@
       <c r="G20" s="14">
         <v>30.61</v>
       </c>
-      <c r="H20" s="36"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="12">
         <v>90</v>
       </c>
@@ -5116,7 +6351,7 @@
       <c r="C21" s="16">
         <v>9.91</v>
       </c>
-      <c r="D21" s="36"/>
+      <c r="D21" s="34"/>
       <c r="E21" s="15">
         <v>54</v>
       </c>
@@ -5126,7 +6361,7 @@
       <c r="G21" s="16">
         <v>26.54</v>
       </c>
-      <c r="H21" s="36"/>
+      <c r="H21" s="34"/>
       <c r="I21" s="15">
         <v>91</v>
       </c>
@@ -5147,7 +6382,7 @@
       <c r="C22" s="14">
         <v>149.94999999999999</v>
       </c>
-      <c r="D22" s="36"/>
+      <c r="D22" s="34"/>
       <c r="E22" s="12">
         <v>55</v>
       </c>
@@ -5157,7 +6392,7 @@
       <c r="G22" s="14">
         <v>13.17</v>
       </c>
-      <c r="H22" s="36"/>
+      <c r="H22" s="34"/>
       <c r="I22" s="12">
         <v>92</v>
       </c>
@@ -5178,7 +6413,7 @@
       <c r="C23" s="16">
         <v>14.81</v>
       </c>
-      <c r="D23" s="36"/>
+      <c r="D23" s="34"/>
       <c r="E23" s="15">
         <v>56</v>
       </c>
@@ -5188,7 +6423,7 @@
       <c r="G23" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H23" s="36"/>
+      <c r="H23" s="34"/>
       <c r="I23" s="15">
         <v>93</v>
       </c>
@@ -5209,7 +6444,7 @@
       <c r="C24" s="14">
         <v>5.19</v>
       </c>
-      <c r="D24" s="36"/>
+      <c r="D24" s="34"/>
       <c r="E24" s="12">
         <v>57</v>
       </c>
@@ -5219,7 +6454,7 @@
       <c r="G24" s="14">
         <v>27.37</v>
       </c>
-      <c r="H24" s="36"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="12">
         <v>94</v>
       </c>
@@ -5240,7 +6475,7 @@
       <c r="C25" s="16">
         <v>14.79</v>
       </c>
-      <c r="D25" s="36"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="15">
         <v>58</v>
       </c>
@@ -5250,7 +6485,7 @@
       <c r="G25" s="16">
         <v>78.58</v>
       </c>
-      <c r="H25" s="36"/>
+      <c r="H25" s="34"/>
       <c r="I25" s="15">
         <v>95</v>
       </c>
@@ -5271,7 +6506,7 @@
       <c r="C26" s="14">
         <v>3.8</v>
       </c>
-      <c r="D26" s="36"/>
+      <c r="D26" s="34"/>
       <c r="E26" s="12">
         <v>59</v>
       </c>
@@ -5281,7 +6516,7 @@
       <c r="G26" s="14">
         <v>5.09</v>
       </c>
-      <c r="H26" s="36"/>
+      <c r="H26" s="34"/>
       <c r="I26" s="24">
         <v>96</v>
       </c>
@@ -5302,7 +6537,7 @@
       <c r="C27" s="16">
         <v>4.5</v>
       </c>
-      <c r="D27" s="36"/>
+      <c r="D27" s="34"/>
       <c r="E27" s="15">
         <v>60</v>
       </c>
@@ -5312,7 +6547,7 @@
       <c r="G27" s="23">
         <v>11.06</v>
       </c>
-      <c r="H27" s="36"/>
+      <c r="H27" s="34"/>
       <c r="I27" s="15">
         <v>97</v>
       </c>
@@ -5333,7 +6568,7 @@
       <c r="C28" s="14">
         <v>5.67</v>
       </c>
-      <c r="D28" s="36"/>
+      <c r="D28" s="34"/>
       <c r="E28" s="24">
         <v>61</v>
       </c>
@@ -5343,7 +6578,7 @@
       <c r="G28" s="25">
         <v>11.17</v>
       </c>
-      <c r="H28" s="36"/>
+      <c r="H28" s="34"/>
       <c r="I28" s="17"/>
       <c r="J28" s="18" t="s">
         <v>9</v>
@@ -5363,7 +6598,7 @@
       <c r="C29" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D29" s="36"/>
+      <c r="D29" s="34"/>
       <c r="E29" s="15">
         <v>62</v>
       </c>
@@ -5373,10 +6608,10 @@
       <c r="G29" s="23">
         <v>8.33</v>
       </c>
-      <c r="H29" s="36"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
     </row>
     <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
@@ -5388,7 +6623,7 @@
       <c r="C30" s="14">
         <v>39.9</v>
       </c>
-      <c r="D30" s="36"/>
+      <c r="D30" s="34"/>
       <c r="E30" s="24">
         <v>63</v>
       </c>
@@ -5398,12 +6633,12 @@
       <c r="G30" s="25">
         <v>5.6</v>
       </c>
-      <c r="H30" s="36"/>
-      <c r="I30" s="39" t="s">
+      <c r="H30" s="34"/>
+      <c r="I30" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="J30" s="40"/>
-      <c r="K30" s="41"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="43"/>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
@@ -5415,7 +6650,7 @@
       <c r="C31" s="16">
         <v>10.85</v>
       </c>
-      <c r="D31" s="36"/>
+      <c r="D31" s="34"/>
       <c r="E31" s="15">
         <v>64</v>
       </c>
@@ -5425,7 +6660,7 @@
       <c r="G31" s="23">
         <v>6.02</v>
       </c>
-      <c r="H31" s="36"/>
+      <c r="H31" s="34"/>
       <c r="I31" s="27" t="s">
         <v>1</v>
       </c>
@@ -5446,7 +6681,7 @@
       <c r="C32" s="14">
         <v>5.49</v>
       </c>
-      <c r="D32" s="36"/>
+      <c r="D32" s="34"/>
       <c r="E32" s="24">
         <v>65</v>
       </c>
@@ -5456,7 +6691,7 @@
       <c r="G32" s="25">
         <v>37.04</v>
       </c>
-      <c r="H32" s="36"/>
+      <c r="H32" s="34"/>
       <c r="I32" s="15" t="s">
         <v>153</v>
       </c>
@@ -5478,7 +6713,7 @@
       <c r="C33" s="16">
         <v>9.66</v>
       </c>
-      <c r="D33" s="36"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="15">
         <v>66</v>
       </c>
@@ -5488,7 +6723,7 @@
       <c r="G33" s="23">
         <v>6.28</v>
       </c>
-      <c r="H33" s="36"/>
+      <c r="H33" s="34"/>
       <c r="I33" s="17"/>
       <c r="J33" s="18" t="s">
         <v>9</v>
@@ -5508,7 +6743,7 @@
       <c r="C34" s="14">
         <v>6.28</v>
       </c>
-      <c r="D34" s="36"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="24">
         <v>67</v>
       </c>
@@ -5518,10 +6753,10 @@
       <c r="G34" s="25">
         <v>5.98</v>
       </c>
-      <c r="H34" s="36"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
     </row>
     <row r="35" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
@@ -5533,7 +6768,7 @@
       <c r="C35" s="16">
         <v>5.85</v>
       </c>
-      <c r="D35" s="36"/>
+      <c r="D35" s="34"/>
       <c r="E35" s="15">
         <v>68</v>
       </c>
@@ -5543,10 +6778,10 @@
       <c r="G35" s="23">
         <v>6.34</v>
       </c>
-      <c r="H35" s="36"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="35"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
@@ -5558,7 +6793,7 @@
       <c r="C36" s="14">
         <v>29</v>
       </c>
-      <c r="D36" s="36"/>
+      <c r="D36" s="34"/>
       <c r="E36" s="12">
         <v>69</v>
       </c>
@@ -5568,10 +6803,10 @@
       <c r="G36" s="14">
         <v>28.97</v>
       </c>
-      <c r="H36" s="36"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
@@ -5583,7 +6818,7 @@
       <c r="C37" s="16">
         <v>67.27</v>
       </c>
-      <c r="D37" s="36"/>
+      <c r="D37" s="34"/>
       <c r="E37" s="15">
         <v>70</v>
       </c>
@@ -5593,10 +6828,10 @@
       <c r="G37" s="16">
         <v>61.92</v>
       </c>
-      <c r="H37" s="36"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
@@ -5608,7 +6843,7 @@
       <c r="C38" s="14">
         <v>60.17</v>
       </c>
-      <c r="D38" s="36"/>
+      <c r="D38" s="34"/>
       <c r="E38" s="12">
         <v>71</v>
       </c>
@@ -5618,10 +6853,10 @@
       <c r="G38" s="14">
         <v>72.55</v>
       </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="35"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
@@ -5633,7 +6868,7 @@
       <c r="C39" s="16">
         <v>29.3</v>
       </c>
-      <c r="D39" s="36"/>
+      <c r="D39" s="34"/>
       <c r="E39" s="15">
         <v>72</v>
       </c>
@@ -5643,10 +6878,10 @@
       <c r="G39" s="16">
         <v>6.34</v>
       </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -5658,7 +6893,7 @@
       <c r="C40" s="14">
         <v>15.63</v>
       </c>
-      <c r="D40" s="36"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="12">
         <v>73</v>
       </c>
@@ -5668,10 +6903,10 @@
       <c r="G40" s="14">
         <v>28.97</v>
       </c>
-      <c r="H40" s="36"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
@@ -5683,7 +6918,7 @@
       <c r="C41" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D41" s="36"/>
+      <c r="D41" s="34"/>
       <c r="E41" s="15">
         <v>74</v>
       </c>
@@ -5693,10 +6928,10 @@
       <c r="G41" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H41" s="36"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="35"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -5708,7 +6943,7 @@
       <c r="C42" s="14">
         <v>2.57</v>
       </c>
-      <c r="D42" s="36"/>
+      <c r="D42" s="34"/>
       <c r="E42" s="12">
         <v>75</v>
       </c>
@@ -5718,10 +6953,10 @@
       <c r="G42" s="14">
         <v>6.35</v>
       </c>
-      <c r="H42" s="36"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="35"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
@@ -5733,7 +6968,7 @@
       <c r="C43" s="16">
         <v>2.84</v>
       </c>
-      <c r="D43" s="36"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="17"/>
       <c r="F43" s="18" t="s">
         <v>9</v>
@@ -5742,10 +6977,10 @@
         <f>SUM(G6:G42)</f>
         <v>1417.3899999999994</v>
       </c>
-      <c r="H43" s="36"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
     </row>
     <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
@@ -5756,22 +6991,17 @@
         <f>SUM(C6:C43)</f>
         <v>1174.6799999999998</v>
       </c>
-      <c r="D44" s="36"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="D5:D44"/>
     <mergeCell ref="H5:H44"/>
@@ -5779,13 +7009,18 @@
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="I34:K44"/>
     <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="G3:I3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -5808,36 +7043,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -5849,18 +7084,18 @@
       <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -5870,17 +7105,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -5892,7 +7127,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="38"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -5902,7 +7137,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="34"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -5923,7 +7158,7 @@
       <c r="C6" s="14">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="12">
         <v>14</v>
       </c>
@@ -5933,7 +7168,7 @@
       <c r="G6" s="14">
         <v>5.19</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -5954,7 +7189,7 @@
       <c r="C7" s="16">
         <v>5.51</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="30">
         <v>15</v>
       </c>
@@ -5964,7 +7199,7 @@
       <c r="G7" s="16">
         <v>11.2</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="30">
         <v>31</v>
       </c>
@@ -5985,7 +7220,7 @@
       <c r="C8" s="14">
         <v>10.08</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="12">
         <v>16</v>
       </c>
@@ -5995,7 +7230,7 @@
       <c r="G8" s="14">
         <v>11.31</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -6016,7 +7251,7 @@
       <c r="C9" s="16">
         <v>149.28</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="30">
         <v>17</v>
       </c>
@@ -6026,7 +7261,7 @@
       <c r="G9" s="16">
         <v>26.54</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="30">
         <v>33</v>
       </c>
@@ -6047,7 +7282,7 @@
       <c r="C10" s="14">
         <v>15.01</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="12">
         <v>18</v>
       </c>
@@ -6057,7 +7292,7 @@
       <c r="G10" s="14">
         <v>13.17</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -6078,7 +7313,7 @@
       <c r="C11" s="23">
         <v>5.22</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="30">
         <v>19</v>
       </c>
@@ -6088,7 +7323,7 @@
       <c r="G11" s="16">
         <v>8.19</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="30">
         <v>35</v>
       </c>
@@ -6109,7 +7344,7 @@
       <c r="C12" s="25">
         <v>15</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="12">
         <v>20</v>
       </c>
@@ -6119,7 +7354,7 @@
       <c r="G12" s="14">
         <v>27.38</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -6140,7 +7375,7 @@
       <c r="C13" s="23">
         <v>6.27</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="34"/>
       <c r="E13" s="30">
         <v>21</v>
       </c>
@@ -6150,7 +7385,7 @@
       <c r="G13" s="23">
         <v>10.44</v>
       </c>
-      <c r="H13" s="36"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="17"/>
       <c r="J13" s="18" t="s">
         <v>9</v>
@@ -6170,7 +7405,7 @@
       <c r="C14" s="25">
         <v>5.98</v>
       </c>
-      <c r="D14" s="36"/>
+      <c r="D14" s="34"/>
       <c r="E14" s="12">
         <v>22</v>
       </c>
@@ -6180,10 +7415,10 @@
       <c r="G14" s="25">
         <v>11.73</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
     </row>
     <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
@@ -6195,7 +7430,7 @@
       <c r="C15" s="23">
         <v>59.38</v>
       </c>
-      <c r="D15" s="36"/>
+      <c r="D15" s="34"/>
       <c r="E15" s="30">
         <v>23</v>
       </c>
@@ -6205,10 +7440,10 @@
       <c r="G15" s="23">
         <v>30.61</v>
       </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
     </row>
     <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
@@ -6220,7 +7455,7 @@
       <c r="C16" s="25">
         <v>16.399999999999999</v>
       </c>
-      <c r="D16" s="36"/>
+      <c r="D16" s="34"/>
       <c r="E16" s="12">
         <v>24</v>
       </c>
@@ -6230,10 +7465,10 @@
       <c r="G16" s="25">
         <v>15</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
     </row>
     <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
@@ -6245,7 +7480,7 @@
       <c r="C17" s="23">
         <v>29.22</v>
       </c>
-      <c r="D17" s="36"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="30">
         <v>25</v>
       </c>
@@ -6255,10 +7490,10 @@
       <c r="G17" s="23">
         <v>14.98</v>
       </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
     </row>
     <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
@@ -6270,7 +7505,7 @@
       <c r="C18" s="25">
         <v>29.54</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="34"/>
       <c r="E18" s="12">
         <v>26</v>
       </c>
@@ -6280,10 +7515,10 @@
       <c r="G18" s="25">
         <v>5.23</v>
       </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
     </row>
     <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
@@ -6294,7 +7529,7 @@
         <f>SUM(C6:C18)</f>
         <v>352.00000000000006</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="34"/>
       <c r="E19" s="30">
         <v>27</v>
       </c>
@@ -6304,16 +7539,16 @@
       <c r="G19" s="23">
         <v>6.27</v>
       </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
     </row>
     <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="36"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="34"/>
       <c r="E20" s="12">
         <v>28</v>
       </c>
@@ -6323,16 +7558,16 @@
       <c r="G20" s="25">
         <v>29.19</v>
       </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
     </row>
     <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="36"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="34"/>
       <c r="E21" s="30">
         <v>29</v>
       </c>
@@ -6342,16 +7577,16 @@
       <c r="G21" s="23">
         <v>29.2</v>
       </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="34"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18" t="s">
         <v>9</v>
@@ -6360,10 +7595,10 @@
         <f>SUM(G6:G21)</f>
         <v>255.62999999999997</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6382,7 +7617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -6405,36 +7640,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -6446,18 +7681,18 @@
       <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -6467,17 +7702,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -6489,7 +7724,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="38"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -6499,7 +7734,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="34"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -6520,7 +7755,7 @@
       <c r="C6" s="14">
         <v>44.29</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="12">
         <v>5</v>
       </c>
@@ -6530,7 +7765,7 @@
       <c r="G6" s="14">
         <v>53.5</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="34"/>
       <c r="I6" s="12">
         <v>11</v>
       </c>
@@ -6551,7 +7786,7 @@
       <c r="C7" s="16">
         <v>47.34</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="15">
         <v>6</v>
       </c>
@@ -6561,7 +7796,7 @@
       <c r="G7" s="16">
         <v>74.430000000000007</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="15">
         <v>12</v>
       </c>
@@ -6582,7 +7817,7 @@
       <c r="C8" s="14">
         <v>54.22</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="12">
         <v>7</v>
       </c>
@@ -6592,7 +7827,7 @@
       <c r="G8" s="14">
         <v>53.83</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="12">
         <v>13</v>
       </c>
@@ -6613,7 +7848,7 @@
       <c r="C9" s="16">
         <v>129.11000000000001</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="15">
         <v>8</v>
       </c>
@@ -6623,7 +7858,7 @@
       <c r="G9" s="16">
         <v>55.33</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="15">
         <v>14</v>
       </c>
@@ -6643,7 +7878,7 @@
         <f>SUM(C6:C9)</f>
         <v>274.96000000000004</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="34"/>
       <c r="E10" s="12">
         <v>9</v>
       </c>
@@ -6653,7 +7888,7 @@
       <c r="G10" s="14">
         <v>54.25</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="12">
         <v>15</v>
       </c>
@@ -6665,10 +7900,10 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="36"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="15">
         <v>10</v>
       </c>
@@ -6678,7 +7913,7 @@
       <c r="G11" s="16">
         <v>54.3</v>
       </c>
-      <c r="H11" s="36"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="15">
         <v>16</v>
       </c>
@@ -6690,10 +7925,10 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="34"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18" t="s">
         <v>9</v>
@@ -6702,7 +7937,7 @@
         <f>SUM(G6:G11)</f>
         <v>345.64</v>
       </c>
-      <c r="H12" s="36"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="12">
         <v>17</v>
       </c>
@@ -6714,14 +7949,14 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="36"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="15">
         <v>18</v>
       </c>
@@ -6733,14 +7968,14 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="36"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="34"/>
       <c r="I14" s="12">
         <v>19</v>
       </c>
@@ -6752,14 +7987,14 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="36"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="34"/>
       <c r="I15" s="15">
         <v>20</v>
       </c>
@@ -6771,14 +8006,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="17"/>
       <c r="J16" s="18" t="s">
         <v>9</v>

--- a/kronshtatsky/ceilling/ceilling-k.xlsx
+++ b/kronshtatsky/ceilling/ceilling-k.xlsx
@@ -9,20 +9,32 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10128" firstSheet="3" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10128"/>
   </bookViews>
   <sheets>
-    <sheet name="CF1" sheetId="4" r:id="rId1"/>
-    <sheet name="1.1-CF2_СКБ" sheetId="1" r:id="rId2"/>
-    <sheet name="2.1-CF2_Краска" sheetId="2" r:id="rId3"/>
-    <sheet name="3.1-CF2_Монтаж" sheetId="3" r:id="rId4"/>
-    <sheet name="2.2-CF1_КрскДопСл" sheetId="10" r:id="rId5"/>
-    <sheet name="2.2-CF1_Краск" sheetId="6" r:id="rId6"/>
-    <sheet name="1.2-CF1_СКБ" sheetId="7" r:id="rId7"/>
-    <sheet name="3.2-CF3_Монтаж" sheetId="8" r:id="rId8"/>
-    <sheet name="3.3-CF4_Монтаж" sheetId="9" r:id="rId9"/>
+    <sheet name="1144" sheetId="22" r:id="rId1"/>
+    <sheet name="1140" sheetId="21" r:id="rId2"/>
+    <sheet name="1048" sheetId="18" r:id="rId3"/>
+    <sheet name="1005" sheetId="17" r:id="rId4"/>
+    <sheet name="971" sheetId="20" r:id="rId5"/>
+    <sheet name="968" sheetId="19" r:id="rId6"/>
+    <sheet name="965" sheetId="16" r:id="rId7"/>
+    <sheet name="947" sheetId="15" r:id="rId8"/>
+    <sheet name="CF6" sheetId="14" r:id="rId9"/>
+    <sheet name="CF3" sheetId="13" r:id="rId10"/>
+    <sheet name="CF4" sheetId="12" r:id="rId11"/>
+    <sheet name="CF7,17" sheetId="11" r:id="rId12"/>
+    <sheet name="CF1" sheetId="4" r:id="rId13"/>
+    <sheet name="1.1-CF2_СКБ" sheetId="1" r:id="rId14"/>
+    <sheet name="2.1-CF2_Краска" sheetId="2" r:id="rId15"/>
+    <sheet name="3.1-CF2_Монтаж" sheetId="3" r:id="rId16"/>
+    <sheet name="2.2-CF1_КрскДопСл" sheetId="10" r:id="rId17"/>
+    <sheet name="2.2-CF1_Краск" sheetId="6" r:id="rId18"/>
+    <sheet name="1.2-CF1_СКБ" sheetId="7" r:id="rId19"/>
+    <sheet name="3.2-CF3_Монтаж" sheetId="8" r:id="rId20"/>
+    <sheet name="3.3-CF4_Монтаж" sheetId="9" r:id="rId21"/>
   </sheets>
-  <calcPr calcId="152511" refMode="R1C1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="205">
   <si>
     <t>Спецификация выполненных работ</t>
   </si>
@@ -542,16 +554,122 @@
   </si>
   <si>
     <t>1, 2, 3 этажи. Тип: CF1. Покраска Потолка</t>
+  </si>
+  <si>
+    <t>АРОР "ЧИСТОВЫЕ отделочные работы" от 19.02.2026. CF7 и CF17. Подвесной кассетный потолок Albes с кромками Tegular. Кассета AP600A6/90-T-15, несущий профиль T 15-38 PRIM (L 3700мм), поперечный профиль T 15-29 PRIM (L 600мм), уголок PLL, подвес АП. Цвет: белый.</t>
+  </si>
+  <si>
+    <t>CF7</t>
+  </si>
+  <si>
+    <t>CF17</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип: CF4. Потолочная плита Baffle Acoustic (арт. BA 1200x600). Подвесная система -Alaid T24. Кромка не окрашена. Размер панели 1200х600х20, цвет белый</t>
+  </si>
+  <si>
+    <t>CF4</t>
+  </si>
+  <si>
+    <t>есть в РД</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип: CF3. Потолки грильято, кассетный GL-15 , металлическая решетка 600х600 с ячейками 100х100, AL 0,3-0,4 мм, h профиля (база) 37 мм; подвесная система Т-15/29 PRIM АЛБЕС Белый</t>
+  </si>
+  <si>
+    <t>CF3</t>
+  </si>
+  <si>
+    <t>новый</t>
+  </si>
+  <si>
+    <t>старый</t>
+  </si>
+  <si>
+    <t>CF6</t>
+  </si>
+  <si>
+    <t>Простая штукатурка потолка сухими смесями с предварительной огрунтовкой поверхности / толщ. до 6,5 мм</t>
+  </si>
+  <si>
+    <t>Подготовка поверхности СКБ / потолка / по штукатурке / 2мм</t>
+  </si>
+  <si>
+    <t>Монтаж подвесного потолка / типа Армстронг, Грильято</t>
+  </si>
+  <si>
+    <t>ЛК. Выравнивание цементными штукатурными смесями т.5 мм потолков по ж/б плите, низа площадок и лестничных маршей. Подвал</t>
+  </si>
+  <si>
+    <t>1-й, 2-й, 3-й этажи. Выравнивание гипсовыми штукатурными смесями 5 мм в составе потолков  CF1, CF13 и стен запотолочного пространства CF1.3.</t>
+  </si>
+  <si>
+    <t>ЛК. Выравнивание гипсовыми штукатурными смесями низа площадок и лестничных маршей, и потолка  CF15.1. 1-3 этажи</t>
+  </si>
+  <si>
+    <t>Шпаклевка зашивных потолков под окраску гипсовая базовая CF2, CF14, CF19, CF25</t>
+  </si>
+  <si>
+    <t>Подвал: шпаклевка цементными смесями потолков по ж/б плите, низа площадок и лестничных маршей. Базовый слой 2 мм.</t>
+  </si>
+  <si>
+    <t>Потолки 1-й, 2-й и 3-й этаж: шпаклевка гипсовая базовая в составе потолков CF1, CF13 и стен запотолочного пространства CF1.3.</t>
+  </si>
+  <si>
+    <t>Шпаклевка гипсовая базовая низа площадок и лестничных маршей, и потолка  CF15.1. 1-3 этаж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 2, 3 этажи. Тип: CF15.1. Покраска жб плиты перекрытия и нижняя поверхность лестничных маршей и площадок. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF13. Покраска жб плиты перекрытия, включая инженерное оборудование, расположенное в зоне открытого потолка. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF1.1. Покраска балок. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF1.3. Покраска запотолочного пространства (стены). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF1.2. Покраска балок (стены). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF13.1. Покраска балок. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF13.2. Покраска балок (стены). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF15. Торцы лестничных маршей в ЛК: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подвал. Покраска потолка </t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип: CF4. Потолочная плита. Подвесная система</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип: CF3. Потолки грильято. подвесная система.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 2, 3 этажи. Тип: CF6. Кубообразный Потолки </t>
+  </si>
+  <si>
+    <t>CF7 и CF17. Подвесной кассетный потолок с кромками Tegular.</t>
+  </si>
+  <si>
+    <t>1, 2, 3 этажи. Тип: CF17 Подвесной металлический кассетный потолок.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -570,6 +688,8 @@
     <font>
       <sz val="12"/>
       <name val="XO Thames"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="14"/>
@@ -599,8 +719,47 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -613,8 +772,32 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99FF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99FF99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -797,11 +980,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -894,6 +1120,57 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -908,9 +1185,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1213,6 +1487,371 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="3" max="3" width="42.5546875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A3" s="46">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>455.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="38">
+        <v>1</v>
+      </c>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40">
+        <v>731.9</v>
+      </c>
+      <c r="H1" s="41">
+        <v>17.439999999999941</v>
+      </c>
+      <c r="I1" s="42">
+        <v>714.46</v>
+      </c>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41">
+        <v>574</v>
+      </c>
+      <c r="L1" s="43"/>
+      <c r="M1" s="44">
+        <v>140.46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>257.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>106.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>356.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>257.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>118.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="38">
+        <v>1</v>
+      </c>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40">
+        <v>1222.2</v>
+      </c>
+      <c r="H1" s="41">
+        <v>50.6099999999999</v>
+      </c>
+      <c r="I1" s="42">
+        <v>1171.5900000000001</v>
+      </c>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41">
+        <v>705.6</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="M1" s="44">
+        <v>465.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>277.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>348.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>550.79999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="35">
+        <v>455.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>399.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1320,7 +1959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1338,36 +1977,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -1379,18 +2018,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1400,17 +2039,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -1422,7 +2061,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="36"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -1432,7 +2071,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="34"/>
+      <c r="H5" s="51"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -1453,7 +2092,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -1463,7 +2102,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -1484,7 +2123,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -1494,7 +2133,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -1515,7 +2154,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -1525,7 +2164,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -1546,7 +2185,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -1556,7 +2195,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -1577,7 +2216,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -1587,7 +2226,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -1608,7 +2247,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -1618,7 +2257,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -1639,7 +2278,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -1649,7 +2288,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -1670,7 +2309,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -1680,7 +2319,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="34"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -1701,7 +2340,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -1711,7 +2350,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="34"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -1732,7 +2371,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -1742,7 +2381,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="34"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -1763,7 +2402,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -1774,7 +2413,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="51"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -1795,7 +2434,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="34"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -1805,7 +2444,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="34"/>
+      <c r="H17" s="51"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -1828,7 +2467,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -1838,7 +2477,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -1859,7 +2498,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="34"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -1868,7 +2507,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="34"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -1889,11 +2528,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="34"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -1913,14 +2552,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -1931,14 +2570,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1957,7 +2596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1975,36 +2614,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2016,18 +2655,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2037,17 +2676,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2059,7 +2698,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="36"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -2069,7 +2708,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="34"/>
+      <c r="H5" s="51"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -2090,7 +2729,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -2100,7 +2739,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -2121,7 +2760,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -2131,7 +2770,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -2152,7 +2791,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -2162,7 +2801,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -2183,7 +2822,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -2193,7 +2832,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -2214,7 +2853,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -2224,7 +2863,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -2245,7 +2884,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -2255,7 +2894,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -2276,7 +2915,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -2286,7 +2925,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -2307,7 +2946,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -2317,7 +2956,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="34"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -2338,7 +2977,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -2348,7 +2987,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="34"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -2369,7 +3008,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -2379,7 +3018,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="34"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -2400,7 +3039,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -2411,7 +3050,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="51"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -2432,7 +3071,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="34"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -2442,7 +3081,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="34"/>
+      <c r="H17" s="51"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -2465,7 +3104,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -2475,7 +3114,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -2496,7 +3135,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="34"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -2505,7 +3144,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="34"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -2526,11 +3165,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="34"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -2550,14 +3189,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -2568,14 +3207,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2594,7 +3233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2612,36 +3251,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2653,18 +3292,18 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="39" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2674,17 +3313,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -2696,7 +3335,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="36"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -2706,7 +3345,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="34"/>
+      <c r="H5" s="51"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -2727,7 +3366,7 @@
       <c r="C6" s="14">
         <v>12.85</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="12">
         <v>17</v>
       </c>
@@ -2737,7 +3376,7 @@
       <c r="G6" s="14">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -2758,7 +3397,7 @@
       <c r="C7" s="16">
         <v>9.52</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="15">
         <v>18</v>
       </c>
@@ -2768,7 +3407,7 @@
       <c r="G7" s="16">
         <v>3.79</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="15">
         <v>31</v>
       </c>
@@ -2789,7 +3428,7 @@
       <c r="C8" s="14">
         <v>17.600000000000001</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="12">
         <v>19</v>
       </c>
@@ -2799,7 +3438,7 @@
       <c r="G8" s="14">
         <v>1.56</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -2820,7 +3459,7 @@
       <c r="C9" s="16">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="15">
         <v>20</v>
       </c>
@@ -2830,7 +3469,7 @@
       <c r="G9" s="16">
         <v>2.54</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="15">
         <v>33</v>
       </c>
@@ -2851,7 +3490,7 @@
       <c r="C10" s="14">
         <v>2.5299999999999998</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="12">
         <v>21</v>
       </c>
@@ -2861,7 +3500,7 @@
       <c r="G10" s="14">
         <v>2.5499999999999998</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -2882,7 +3521,7 @@
       <c r="C11" s="16">
         <v>2.54</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="15">
         <v>22</v>
       </c>
@@ -2892,7 +3531,7 @@
       <c r="G11" s="16">
         <v>2.6</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="15">
         <v>35</v>
       </c>
@@ -2913,7 +3552,7 @@
       <c r="C12" s="14">
         <v>2.71</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="12">
         <v>23</v>
       </c>
@@ -2923,7 +3562,7 @@
       <c r="G12" s="14">
         <v>2.6</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -2944,7 +3583,7 @@
       <c r="C13" s="16">
         <v>14.88</v>
       </c>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="15">
         <v>24</v>
       </c>
@@ -2954,7 +3593,7 @@
       <c r="G13" s="16">
         <v>23.22</v>
       </c>
-      <c r="H13" s="34"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="15">
         <v>37</v>
       </c>
@@ -2975,7 +3614,7 @@
       <c r="C14" s="20">
         <v>16.38</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="12">
         <v>25</v>
       </c>
@@ -2985,7 +3624,7 @@
       <c r="G14" s="20">
         <v>49.93</v>
       </c>
-      <c r="H14" s="34"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="12">
         <v>38</v>
       </c>
@@ -3006,7 +3645,7 @@
       <c r="C15" s="16">
         <v>23.46</v>
       </c>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="15">
         <v>26</v>
       </c>
@@ -3016,7 +3655,7 @@
       <c r="G15" s="16">
         <v>55.58</v>
       </c>
-      <c r="H15" s="34"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="15">
         <v>39</v>
       </c>
@@ -3037,7 +3676,7 @@
       <c r="C16" s="20">
         <v>50.03</v>
       </c>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="12">
         <v>27</v>
       </c>
@@ -3048,7 +3687,7 @@
         <f>22.67</f>
         <v>22.67</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="51"/>
       <c r="I16" s="12">
         <v>40</v>
       </c>
@@ -3069,7 +3708,7 @@
       <c r="C17" s="16">
         <v>55.72</v>
       </c>
-      <c r="D17" s="34"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="15">
         <v>28</v>
       </c>
@@ -3079,7 +3718,7 @@
       <c r="G17" s="16">
         <v>49.72</v>
       </c>
-      <c r="H17" s="34"/>
+      <c r="H17" s="51"/>
       <c r="I17" s="15">
         <v>41</v>
       </c>
@@ -3102,7 +3741,7 @@
         <f>23.03-C19</f>
         <v>18.200000000000003</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="12">
         <v>29</v>
       </c>
@@ -3112,7 +3751,7 @@
       <c r="G18" s="20">
         <v>55.25</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="12">
         <v>42</v>
       </c>
@@ -3133,7 +3772,7 @@
       <c r="C19" s="16">
         <v>4.83</v>
       </c>
-      <c r="D19" s="34"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18" t="s">
         <v>9</v>
@@ -3142,7 +3781,7 @@
         <f>SUM(G6:G18)</f>
         <v>274.46000000000004</v>
       </c>
-      <c r="H19" s="34"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="15">
         <v>43</v>
       </c>
@@ -3163,11 +3802,11 @@
       <c r="C20" s="20">
         <v>49.98</v>
       </c>
-      <c r="D20" s="34"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="34"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18" t="s">
         <v>9</v>
@@ -3187,14 +3826,14 @@
       <c r="C21" s="16">
         <v>55.31</v>
       </c>
-      <c r="D21" s="34"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="17"/>
@@ -3205,14 +3844,14 @@
         <f>SUM(C6:C21)</f>
         <v>341.65</v>
       </c>
-      <c r="D22" s="34"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3231,7 +3870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3250,36 +3889,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -3291,18 +3930,18 @@
       <c r="A3" s="31">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="54" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55" t="s">
         <v>169</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -3312,17 +3951,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -3334,7 +3973,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="36"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -3344,7 +3983,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="34"/>
+      <c r="H5" s="51"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -3366,7 +4005,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="12">
         <v>38</v>
       </c>
@@ -3376,7 +4015,7 @@
       <c r="G6" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="12">
         <v>74</v>
       </c>
@@ -3397,7 +4036,7 @@
       <c r="C7" s="16">
         <v>15.68</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="15">
         <v>39</v>
       </c>
@@ -3407,7 +4046,7 @@
       <c r="G7" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="15">
         <v>75</v>
       </c>
@@ -3428,7 +4067,7 @@
       <c r="C8" s="14">
         <v>5.01</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="12">
         <v>40</v>
       </c>
@@ -3438,7 +4077,7 @@
       <c r="G8" s="14">
         <v>5.15</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="12">
         <v>76</v>
       </c>
@@ -3459,7 +4098,7 @@
       <c r="C9" s="16">
         <v>6.01</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="15">
         <v>41</v>
       </c>
@@ -3469,7 +4108,7 @@
       <c r="G9" s="16">
         <v>9.48</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="15">
         <v>77</v>
       </c>
@@ -3490,7 +4129,7 @@
       <c r="C10" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="12">
         <v>42</v>
       </c>
@@ -3500,7 +4139,7 @@
       <c r="G10" s="14">
         <v>198.78</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="12">
         <v>78</v>
       </c>
@@ -3521,7 +4160,7 @@
       <c r="C11" s="16">
         <v>97.45</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="15">
         <v>43</v>
       </c>
@@ -3531,7 +4170,7 @@
       <c r="G11" s="16">
         <v>14.98</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="15">
         <v>79</v>
       </c>
@@ -3552,7 +4191,7 @@
       <c r="C12" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="12">
         <v>44</v>
       </c>
@@ -3562,7 +4201,7 @@
       <c r="G12" s="14">
         <v>6.46</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="12">
         <v>80</v>
       </c>
@@ -3583,7 +4222,7 @@
       <c r="C13" s="16">
         <v>10</v>
       </c>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="15">
         <v>45</v>
       </c>
@@ -3593,7 +4232,7 @@
       <c r="G13" s="16">
         <v>106.83</v>
       </c>
-      <c r="H13" s="34"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="15">
         <v>81</v>
       </c>
@@ -3614,7 +4253,7 @@
       <c r="C14" s="14">
         <v>10.38</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="15">
         <v>46</v>
       </c>
@@ -3624,7 +4263,7 @@
       <c r="G14" s="16">
         <v>14.81</v>
       </c>
-      <c r="H14" s="34"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="12">
         <v>82</v>
       </c>
@@ -3645,7 +4284,7 @@
       <c r="C15" s="16">
         <v>25.29</v>
       </c>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="12">
         <v>47</v>
       </c>
@@ -3655,7 +4294,7 @@
       <c r="G15" s="14">
         <v>14.79</v>
       </c>
-      <c r="H15" s="34"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="15">
         <v>83</v>
       </c>
@@ -3676,7 +4315,7 @@
       <c r="C16" s="14">
         <v>21.62</v>
       </c>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="15">
         <v>48</v>
       </c>
@@ -3686,7 +4325,7 @@
       <c r="G16" s="16">
         <v>5.14</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="51"/>
       <c r="I16" s="12">
         <v>84</v>
       </c>
@@ -3707,7 +4346,7 @@
       <c r="C17" s="16">
         <v>28.06</v>
       </c>
-      <c r="D17" s="34"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="12">
         <v>49</v>
       </c>
@@ -3717,7 +4356,7 @@
       <c r="G17" s="14">
         <v>10.32</v>
       </c>
-      <c r="H17" s="34"/>
+      <c r="H17" s="51"/>
       <c r="I17" s="15">
         <v>85</v>
       </c>
@@ -3738,7 +4377,7 @@
       <c r="C18" s="14">
         <v>96.32</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="15">
         <v>50</v>
       </c>
@@ -3748,7 +4387,7 @@
       <c r="G18" s="16">
         <v>11.76</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="12">
         <v>86</v>
       </c>
@@ -3769,7 +4408,7 @@
       <c r="C19" s="16">
         <v>111.79</v>
       </c>
-      <c r="D19" s="34"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="12">
         <v>51</v>
       </c>
@@ -3779,7 +4418,7 @@
       <c r="G19" s="14">
         <v>30.61</v>
       </c>
-      <c r="H19" s="34"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="15">
         <v>87</v>
       </c>
@@ -3800,7 +4439,7 @@
       <c r="C20" s="14">
         <v>6.45</v>
       </c>
-      <c r="D20" s="34"/>
+      <c r="D20" s="51"/>
       <c r="E20" s="15">
         <v>52</v>
       </c>
@@ -3810,7 +4449,7 @@
       <c r="G20" s="16">
         <v>26.54</v>
       </c>
-      <c r="H20" s="34"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="12">
         <v>88</v>
       </c>
@@ -3831,7 +4470,7 @@
       <c r="C21" s="16">
         <v>9.91</v>
       </c>
-      <c r="D21" s="34"/>
+      <c r="D21" s="51"/>
       <c r="E21" s="12">
         <v>53</v>
       </c>
@@ -3841,7 +4480,7 @@
       <c r="G21" s="14">
         <v>13.17</v>
       </c>
-      <c r="H21" s="34"/>
+      <c r="H21" s="51"/>
       <c r="I21" s="15">
         <v>89</v>
       </c>
@@ -3862,7 +4501,7 @@
       <c r="C22" s="16">
         <v>14.81</v>
       </c>
-      <c r="D22" s="34"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="15">
         <v>54</v>
       </c>
@@ -3872,7 +4511,7 @@
       <c r="G22" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H22" s="34"/>
+      <c r="H22" s="51"/>
       <c r="I22" s="12">
         <v>90</v>
       </c>
@@ -3893,7 +4532,7 @@
       <c r="C23" s="14">
         <v>5.19</v>
       </c>
-      <c r="D23" s="34"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="12">
         <v>55</v>
       </c>
@@ -3903,7 +4542,7 @@
       <c r="G23" s="14">
         <v>27.37</v>
       </c>
-      <c r="H23" s="34"/>
+      <c r="H23" s="51"/>
       <c r="I23" s="15">
         <v>91</v>
       </c>
@@ -3924,7 +4563,7 @@
       <c r="C24" s="16">
         <v>14.79</v>
       </c>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="15">
         <v>56</v>
       </c>
@@ -3934,7 +4573,7 @@
       <c r="G24" s="16">
         <v>78.58</v>
       </c>
-      <c r="H24" s="34"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="12">
         <v>92</v>
       </c>
@@ -3955,7 +4594,7 @@
       <c r="C25" s="14">
         <v>3.8</v>
       </c>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="12">
         <v>57</v>
       </c>
@@ -3965,7 +4604,7 @@
       <c r="G25" s="14">
         <v>5.09</v>
       </c>
-      <c r="H25" s="34"/>
+      <c r="H25" s="51"/>
       <c r="I25" s="15">
         <v>93</v>
       </c>
@@ -3986,7 +4625,7 @@
       <c r="C26" s="16">
         <v>4.5</v>
       </c>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="15">
         <v>58</v>
       </c>
@@ -3996,7 +4635,7 @@
       <c r="G26" s="23">
         <v>11.06</v>
       </c>
-      <c r="H26" s="34"/>
+      <c r="H26" s="51"/>
       <c r="I26" s="24">
         <v>94</v>
       </c>
@@ -4017,7 +4656,7 @@
       <c r="C27" s="14">
         <v>5.67</v>
       </c>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="24">
         <v>59</v>
       </c>
@@ -4027,7 +4666,7 @@
       <c r="G27" s="25">
         <v>11.17</v>
       </c>
-      <c r="H27" s="34"/>
+      <c r="H27" s="51"/>
       <c r="I27" s="15">
         <v>95</v>
       </c>
@@ -4048,7 +4687,7 @@
       <c r="C28" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="15">
         <v>60</v>
       </c>
@@ -4058,7 +4697,7 @@
       <c r="G28" s="23">
         <v>8.33</v>
       </c>
-      <c r="H28" s="34"/>
+      <c r="H28" s="51"/>
       <c r="I28" s="17"/>
       <c r="J28" s="18" t="s">
         <v>9</v>
@@ -4078,7 +4717,7 @@
       <c r="C29" s="14">
         <v>39.9</v>
       </c>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="24">
         <v>61</v>
       </c>
@@ -4088,10 +4727,10 @@
       <c r="G29" s="25">
         <v>5.6</v>
       </c>
-      <c r="H29" s="34"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49"/>
     </row>
     <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A30" s="15">
@@ -4103,7 +4742,7 @@
       <c r="C30" s="16">
         <v>10.85</v>
       </c>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="15">
         <v>62</v>
       </c>
@@ -4113,10 +4752,10 @@
       <c r="G30" s="23">
         <v>6.02</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
@@ -4128,7 +4767,7 @@
       <c r="C31" s="14">
         <v>5.49</v>
       </c>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="24">
         <v>63</v>
       </c>
@@ -4138,10 +4777,10 @@
       <c r="G31" s="25">
         <v>37.04</v>
       </c>
-      <c r="H31" s="34"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="56"/>
     </row>
     <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
@@ -4153,7 +4792,7 @@
       <c r="C32" s="16">
         <v>9.66</v>
       </c>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="15">
         <v>64</v>
       </c>
@@ -4163,10 +4802,10 @@
       <c r="G32" s="23">
         <v>6.28</v>
       </c>
-      <c r="H32" s="34"/>
-      <c r="I32" s="40"/>
-      <c r="J32" s="40"/>
-      <c r="K32" s="40"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
     </row>
     <row r="33" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
@@ -4178,7 +4817,7 @@
       <c r="C33" s="14">
         <v>6.28</v>
       </c>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="24">
         <v>65</v>
       </c>
@@ -4188,10 +4827,10 @@
       <c r="G33" s="25">
         <v>5.98</v>
       </c>
-      <c r="H33" s="34"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="40"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
     </row>
     <row r="34" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A34" s="15">
@@ -4203,7 +4842,7 @@
       <c r="C34" s="16">
         <v>5.85</v>
       </c>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="15">
         <v>66</v>
       </c>
@@ -4213,10 +4852,10 @@
       <c r="G34" s="23">
         <v>6.34</v>
       </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
     </row>
     <row r="35" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
@@ -4228,7 +4867,7 @@
       <c r="C35" s="14">
         <v>29</v>
       </c>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="12">
         <v>67</v>
       </c>
@@ -4238,10 +4877,10 @@
       <c r="G35" s="14">
         <v>28.97</v>
       </c>
-      <c r="H35" s="34"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="40"/>
-      <c r="K35" s="40"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
@@ -4253,7 +4892,7 @@
       <c r="C36" s="16">
         <v>67.27</v>
       </c>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="15">
         <v>68</v>
       </c>
@@ -4263,10 +4902,10 @@
       <c r="G36" s="16">
         <v>61.92</v>
       </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
@@ -4278,7 +4917,7 @@
       <c r="C37" s="14">
         <v>60.17</v>
       </c>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="12">
         <v>69</v>
       </c>
@@ -4288,10 +4927,10 @@
       <c r="G37" s="14">
         <v>72.55</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
@@ -4303,7 +4942,7 @@
       <c r="C38" s="16">
         <v>29.3</v>
       </c>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="15">
         <v>70</v>
       </c>
@@ -4313,10 +4952,10 @@
       <c r="G38" s="16">
         <v>6.34</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
@@ -4328,7 +4967,7 @@
       <c r="C39" s="14">
         <v>15.63</v>
       </c>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="12">
         <v>71</v>
       </c>
@@ -4338,10 +4977,10 @@
       <c r="G39" s="14">
         <v>28.97</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="40"/>
-      <c r="J39" s="40"/>
-      <c r="K39" s="40"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
@@ -4353,7 +4992,7 @@
       <c r="C40" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="15">
         <v>72</v>
       </c>
@@ -4363,10 +5002,10 @@
       <c r="G40" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H40" s="34"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="40"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
@@ -4378,7 +5017,7 @@
       <c r="C41" s="14">
         <v>2.57</v>
       </c>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="12">
         <v>73</v>
       </c>
@@ -4388,10 +5027,10 @@
       <c r="G41" s="14">
         <v>6.35</v>
       </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="56"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
@@ -4403,7 +5042,7 @@
       <c r="C42" s="16">
         <v>2.84</v>
       </c>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="17"/>
       <c r="F42" s="18" t="s">
         <v>9</v>
@@ -4412,10 +5051,10 @@
         <f>SUM(G6:G41)</f>
         <v>1057.7099999999998</v>
       </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="40"/>
-      <c r="J42" s="40"/>
-      <c r="K42" s="40"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="56"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="17"/>
@@ -4426,14 +5065,14 @@
         <f>SUM(C6:C42)</f>
         <v>1024.7299999999998</v>
       </c>
-      <c r="D43" s="34"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="40"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4453,7 +5092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4472,36 +5111,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -4513,18 +5152,18 @@
       <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -4537,18 +5176,18 @@
       <c r="A4" s="21">
         <v>2</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="39" t="s">
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
       <c r="J4" s="4" t="s">
         <v>6</v>
       </c>
@@ -4558,17 +5197,17 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
     </row>
     <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
@@ -4580,7 +5219,7 @@
       <c r="C6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="6" t="s">
         <v>1</v>
       </c>
@@ -4590,7 +5229,7 @@
       <c r="G6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="9" t="s">
         <v>1</v>
       </c>
@@ -4612,7 +5251,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="12">
         <v>39</v>
       </c>
@@ -4622,7 +5261,7 @@
       <c r="G7" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="12">
         <v>76</v>
       </c>
@@ -4643,7 +5282,7 @@
       <c r="C8" s="16">
         <v>15.68</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="15">
         <v>40</v>
       </c>
@@ -4653,7 +5292,7 @@
       <c r="G8" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="15">
         <v>77</v>
       </c>
@@ -4674,7 +5313,7 @@
       <c r="C9" s="14">
         <v>5.01</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="12">
         <v>41</v>
       </c>
@@ -4684,7 +5323,7 @@
       <c r="G9" s="14">
         <v>5.15</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="12">
         <v>78</v>
       </c>
@@ -4705,7 +5344,7 @@
       <c r="C10" s="16">
         <v>6.01</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="15">
         <v>42</v>
       </c>
@@ -4715,7 +5354,7 @@
       <c r="G10" s="16">
         <v>9.48</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="15">
         <v>79</v>
       </c>
@@ -4736,7 +5375,7 @@
       <c r="C11" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="12">
         <v>43</v>
       </c>
@@ -4746,7 +5385,7 @@
       <c r="G11" s="14">
         <v>198.78</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="12">
         <v>80</v>
       </c>
@@ -4767,7 +5406,7 @@
       <c r="C12" s="16">
         <v>97.45</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="15">
         <v>44</v>
       </c>
@@ -4777,7 +5416,7 @@
       <c r="G12" s="16">
         <v>14.98</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="15">
         <v>81</v>
       </c>
@@ -4798,7 +5437,7 @@
       <c r="C13" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="12">
         <v>45</v>
       </c>
@@ -4808,7 +5447,7 @@
       <c r="G13" s="14">
         <v>6.46</v>
       </c>
-      <c r="H13" s="34"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="12">
         <v>82</v>
       </c>
@@ -4829,7 +5468,7 @@
       <c r="C14" s="16">
         <v>10</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="15">
         <v>46</v>
       </c>
@@ -4839,7 +5478,7 @@
       <c r="G14" s="16">
         <v>106.83</v>
       </c>
-      <c r="H14" s="34"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="15">
         <v>83</v>
       </c>
@@ -4860,7 +5499,7 @@
       <c r="C15" s="14">
         <v>10.38</v>
       </c>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="12">
         <v>47</v>
       </c>
@@ -4870,7 +5509,7 @@
       <c r="G15" s="14">
         <v>359.68</v>
       </c>
-      <c r="H15" s="34"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="12">
         <v>84</v>
       </c>
@@ -4891,7 +5530,7 @@
       <c r="C16" s="16">
         <v>25.29</v>
       </c>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="15">
         <v>48</v>
       </c>
@@ -4901,7 +5540,7 @@
       <c r="G16" s="16">
         <v>14.81</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="51"/>
       <c r="I16" s="15">
         <v>85</v>
       </c>
@@ -4922,7 +5561,7 @@
       <c r="C17" s="14">
         <v>21.62</v>
       </c>
-      <c r="D17" s="34"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="12">
         <v>49</v>
       </c>
@@ -4932,7 +5571,7 @@
       <c r="G17" s="14">
         <v>14.79</v>
       </c>
-      <c r="H17" s="34"/>
+      <c r="H17" s="51"/>
       <c r="I17" s="12">
         <v>86</v>
       </c>
@@ -4953,7 +5592,7 @@
       <c r="C18" s="16">
         <v>28.06</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="15">
         <v>50</v>
       </c>
@@ -4963,7 +5602,7 @@
       <c r="G18" s="16">
         <v>5.14</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="15">
         <v>87</v>
       </c>
@@ -4984,7 +5623,7 @@
       <c r="C19" s="14">
         <v>96.32</v>
       </c>
-      <c r="D19" s="34"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="12">
         <v>51</v>
       </c>
@@ -4994,7 +5633,7 @@
       <c r="G19" s="14">
         <v>10.32</v>
       </c>
-      <c r="H19" s="34"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="12">
         <v>88</v>
       </c>
@@ -5015,7 +5654,7 @@
       <c r="C20" s="16">
         <v>111.79</v>
       </c>
-      <c r="D20" s="34"/>
+      <c r="D20" s="51"/>
       <c r="E20" s="15">
         <v>52</v>
       </c>
@@ -5025,7 +5664,7 @@
       <c r="G20" s="16">
         <v>11.76</v>
       </c>
-      <c r="H20" s="34"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="15">
         <v>89</v>
       </c>
@@ -5046,7 +5685,7 @@
       <c r="C21" s="14">
         <v>6.45</v>
       </c>
-      <c r="D21" s="34"/>
+      <c r="D21" s="51"/>
       <c r="E21" s="12">
         <v>53</v>
       </c>
@@ -5056,7 +5695,7 @@
       <c r="G21" s="14">
         <v>30.61</v>
       </c>
-      <c r="H21" s="34"/>
+      <c r="H21" s="51"/>
       <c r="I21" s="12">
         <v>90</v>
       </c>
@@ -5077,7 +5716,7 @@
       <c r="C22" s="16">
         <v>9.91</v>
       </c>
-      <c r="D22" s="34"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="15">
         <v>54</v>
       </c>
@@ -5087,7 +5726,7 @@
       <c r="G22" s="16">
         <v>26.54</v>
       </c>
-      <c r="H22" s="34"/>
+      <c r="H22" s="51"/>
       <c r="I22" s="15">
         <v>91</v>
       </c>
@@ -5108,7 +5747,7 @@
       <c r="C23" s="14">
         <v>149.94999999999999</v>
       </c>
-      <c r="D23" s="34"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="12">
         <v>55</v>
       </c>
@@ -5118,7 +5757,7 @@
       <c r="G23" s="14">
         <v>13.17</v>
       </c>
-      <c r="H23" s="34"/>
+      <c r="H23" s="51"/>
       <c r="I23" s="12">
         <v>92</v>
       </c>
@@ -5139,7 +5778,7 @@
       <c r="C24" s="16">
         <v>14.81</v>
       </c>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="15">
         <v>56</v>
       </c>
@@ -5149,7 +5788,7 @@
       <c r="G24" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H24" s="34"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="15">
         <v>93</v>
       </c>
@@ -5170,7 +5809,7 @@
       <c r="C25" s="14">
         <v>5.19</v>
       </c>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="12">
         <v>57</v>
       </c>
@@ -5180,7 +5819,7 @@
       <c r="G25" s="14">
         <v>27.37</v>
       </c>
-      <c r="H25" s="34"/>
+      <c r="H25" s="51"/>
       <c r="I25" s="12">
         <v>94</v>
       </c>
@@ -5201,7 +5840,7 @@
       <c r="C26" s="16">
         <v>14.79</v>
       </c>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="15">
         <v>58</v>
       </c>
@@ -5211,7 +5850,7 @@
       <c r="G26" s="16">
         <v>78.58</v>
       </c>
-      <c r="H26" s="34"/>
+      <c r="H26" s="51"/>
       <c r="I26" s="15">
         <v>95</v>
       </c>
@@ -5232,7 +5871,7 @@
       <c r="C27" s="14">
         <v>3.8</v>
       </c>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="12">
         <v>59</v>
       </c>
@@ -5242,7 +5881,7 @@
       <c r="G27" s="14">
         <v>5.09</v>
       </c>
-      <c r="H27" s="34"/>
+      <c r="H27" s="51"/>
       <c r="I27" s="24">
         <v>96</v>
       </c>
@@ -5263,7 +5902,7 @@
       <c r="C28" s="16">
         <v>4.5</v>
       </c>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="15">
         <v>60</v>
       </c>
@@ -5273,7 +5912,7 @@
       <c r="G28" s="23">
         <v>11.06</v>
       </c>
-      <c r="H28" s="34"/>
+      <c r="H28" s="51"/>
       <c r="I28" s="15">
         <v>97</v>
       </c>
@@ -5294,7 +5933,7 @@
       <c r="C29" s="14">
         <v>5.67</v>
       </c>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="24">
         <v>61</v>
       </c>
@@ -5304,7 +5943,7 @@
       <c r="G29" s="25">
         <v>11.17</v>
       </c>
-      <c r="H29" s="34"/>
+      <c r="H29" s="51"/>
       <c r="I29" s="17"/>
       <c r="J29" s="18" t="s">
         <v>9</v>
@@ -5324,7 +5963,7 @@
       <c r="C30" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="15">
         <v>62</v>
       </c>
@@ -5334,10 +5973,10 @@
       <c r="G30" s="23">
         <v>8.33</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
@@ -5349,7 +5988,7 @@
       <c r="C31" s="14">
         <v>39.9</v>
       </c>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="24">
         <v>63</v>
       </c>
@@ -5359,12 +5998,12 @@
       <c r="G31" s="25">
         <v>5.6</v>
       </c>
-      <c r="H31" s="34"/>
-      <c r="I31" s="41" t="s">
+      <c r="H31" s="51"/>
+      <c r="I31" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="J31" s="42"/>
-      <c r="K31" s="43"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="59"/>
     </row>
     <row r="32" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A32" s="15">
@@ -5376,7 +6015,7 @@
       <c r="C32" s="16">
         <v>10.85</v>
       </c>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="15">
         <v>64</v>
       </c>
@@ -5386,7 +6025,7 @@
       <c r="G32" s="23">
         <v>6.02</v>
       </c>
-      <c r="H32" s="34"/>
+      <c r="H32" s="51"/>
       <c r="I32" s="27" t="s">
         <v>1</v>
       </c>
@@ -5407,7 +6046,7 @@
       <c r="C33" s="14">
         <v>5.49</v>
       </c>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="24">
         <v>65</v>
       </c>
@@ -5417,7 +6056,7 @@
       <c r="G33" s="25">
         <v>37.04</v>
       </c>
-      <c r="H33" s="34"/>
+      <c r="H33" s="51"/>
       <c r="I33" s="15" t="s">
         <v>153</v>
       </c>
@@ -5439,7 +6078,7 @@
       <c r="C34" s="16">
         <v>9.66</v>
       </c>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="15">
         <v>66</v>
       </c>
@@ -5449,7 +6088,7 @@
       <c r="G34" s="23">
         <v>6.28</v>
       </c>
-      <c r="H34" s="34"/>
+      <c r="H34" s="51"/>
       <c r="I34" s="17"/>
       <c r="J34" s="18" t="s">
         <v>9</v>
@@ -5469,7 +6108,7 @@
       <c r="C35" s="14">
         <v>6.28</v>
       </c>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="24">
         <v>67</v>
       </c>
@@ -5479,10 +6118,10 @@
       <c r="G35" s="25">
         <v>5.98</v>
       </c>
-      <c r="H35" s="34"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
@@ -5494,7 +6133,7 @@
       <c r="C36" s="16">
         <v>5.85</v>
       </c>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="15">
         <v>68</v>
       </c>
@@ -5504,10 +6143,10 @@
       <c r="G36" s="23">
         <v>6.34</v>
       </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
@@ -5519,7 +6158,7 @@
       <c r="C37" s="14">
         <v>29</v>
       </c>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="12">
         <v>69</v>
       </c>
@@ -5529,10 +6168,10 @@
       <c r="G37" s="14">
         <v>28.97</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
@@ -5544,7 +6183,7 @@
       <c r="C38" s="16">
         <v>67.27</v>
       </c>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="15">
         <v>70</v>
       </c>
@@ -5554,10 +6193,10 @@
       <c r="G38" s="16">
         <v>61.92</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="50"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
@@ -5569,7 +6208,7 @@
       <c r="C39" s="14">
         <v>60.17</v>
       </c>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="12">
         <v>71</v>
       </c>
@@ -5579,10 +6218,10 @@
       <c r="G39" s="14">
         <v>72.55</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="50"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="15">
@@ -5594,7 +6233,7 @@
       <c r="C40" s="16">
         <v>29.3</v>
       </c>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="15">
         <v>72</v>
       </c>
@@ -5604,10 +6243,10 @@
       <c r="G40" s="16">
         <v>6.34</v>
       </c>
-      <c r="H40" s="34"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="50"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="50"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
@@ -5619,7 +6258,7 @@
       <c r="C41" s="14">
         <v>15.63</v>
       </c>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="12">
         <v>73</v>
       </c>
@@ -5629,10 +6268,10 @@
       <c r="G41" s="14">
         <v>28.97</v>
       </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="15">
@@ -5644,7 +6283,7 @@
       <c r="C42" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="15">
         <v>74</v>
       </c>
@@ -5654,10 +6293,10 @@
       <c r="G42" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="50"/>
+      <c r="K42" s="50"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
@@ -5669,7 +6308,7 @@
       <c r="C43" s="14">
         <v>2.57</v>
       </c>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="12">
         <v>75</v>
       </c>
@@ -5679,10 +6318,10 @@
       <c r="G43" s="14">
         <v>6.35</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
     </row>
     <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="15">
@@ -5694,7 +6333,7 @@
       <c r="C44" s="16">
         <v>2.84</v>
       </c>
-      <c r="D44" s="34"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="17"/>
       <c r="F44" s="18" t="s">
         <v>9</v>
@@ -5703,10 +6342,10 @@
         <f>SUM(G7:G43)</f>
         <v>1417.3899999999994</v>
       </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
     </row>
     <row r="45" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="17"/>
@@ -5717,14 +6356,14 @@
         <f>SUM(C7:C44)</f>
         <v>1174.6799999999998</v>
       </c>
-      <c r="D45" s="34"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5751,7 +6390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5770,36 +6409,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -5811,18 +6450,18 @@
       <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -5832,17 +6471,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -5854,7 +6493,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="36"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -5864,7 +6503,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="34"/>
+      <c r="H5" s="51"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -5886,7 +6525,7 @@
         <f>114.61+85.5+5.75</f>
         <v>205.86</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="12">
         <v>39</v>
       </c>
@@ -5896,7 +6535,7 @@
       <c r="G6" s="14">
         <v>76.349999999999994</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="12">
         <v>76</v>
       </c>
@@ -5917,7 +6556,7 @@
       <c r="C7" s="16">
         <v>15.68</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="15">
         <v>40</v>
       </c>
@@ -5927,7 +6566,7 @@
       <c r="G7" s="16">
         <v>17.690000000000001</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="15">
         <v>77</v>
       </c>
@@ -5948,7 +6587,7 @@
       <c r="C8" s="14">
         <v>5.01</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="12">
         <v>41</v>
       </c>
@@ -5958,7 +6597,7 @@
       <c r="G8" s="14">
         <v>5.15</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="12">
         <v>78</v>
       </c>
@@ -5979,7 +6618,7 @@
       <c r="C9" s="16">
         <v>6.01</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="15">
         <v>42</v>
       </c>
@@ -5989,7 +6628,7 @@
       <c r="G9" s="16">
         <v>9.48</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="15">
         <v>79</v>
       </c>
@@ -6010,7 +6649,7 @@
       <c r="C10" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="12">
         <v>43</v>
       </c>
@@ -6020,7 +6659,7 @@
       <c r="G10" s="14">
         <v>198.78</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="12">
         <v>80</v>
       </c>
@@ -6041,7 +6680,7 @@
       <c r="C11" s="16">
         <v>97.45</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="15">
         <v>44</v>
       </c>
@@ -6051,7 +6690,7 @@
       <c r="G11" s="16">
         <v>14.98</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="15">
         <v>81</v>
       </c>
@@ -6072,7 +6711,7 @@
       <c r="C12" s="14">
         <v>9.7899999999999991</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="12">
         <v>45</v>
       </c>
@@ -6082,7 +6721,7 @@
       <c r="G12" s="14">
         <v>6.46</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="12">
         <v>82</v>
       </c>
@@ -6103,7 +6742,7 @@
       <c r="C13" s="16">
         <v>10</v>
       </c>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="15">
         <v>46</v>
       </c>
@@ -6113,7 +6752,7 @@
       <c r="G13" s="16">
         <v>106.83</v>
       </c>
-      <c r="H13" s="34"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="15">
         <v>83</v>
       </c>
@@ -6134,7 +6773,7 @@
       <c r="C14" s="14">
         <v>10.38</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="12">
         <v>47</v>
       </c>
@@ -6144,7 +6783,7 @@
       <c r="G14" s="14">
         <v>359.68</v>
       </c>
-      <c r="H14" s="34"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="12">
         <v>84</v>
       </c>
@@ -6165,7 +6804,7 @@
       <c r="C15" s="16">
         <v>25.29</v>
       </c>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="15">
         <v>48</v>
       </c>
@@ -6175,7 +6814,7 @@
       <c r="G15" s="16">
         <v>14.81</v>
       </c>
-      <c r="H15" s="34"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="15">
         <v>85</v>
       </c>
@@ -6196,7 +6835,7 @@
       <c r="C16" s="14">
         <v>21.62</v>
       </c>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="12">
         <v>49</v>
       </c>
@@ -6206,7 +6845,7 @@
       <c r="G16" s="14">
         <v>14.79</v>
       </c>
-      <c r="H16" s="34"/>
+      <c r="H16" s="51"/>
       <c r="I16" s="12">
         <v>86</v>
       </c>
@@ -6227,7 +6866,7 @@
       <c r="C17" s="16">
         <v>28.06</v>
       </c>
-      <c r="D17" s="34"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="15">
         <v>50</v>
       </c>
@@ -6237,7 +6876,7 @@
       <c r="G17" s="16">
         <v>5.14</v>
       </c>
-      <c r="H17" s="34"/>
+      <c r="H17" s="51"/>
       <c r="I17" s="15">
         <v>87</v>
       </c>
@@ -6258,7 +6897,7 @@
       <c r="C18" s="14">
         <v>96.32</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="12">
         <v>51</v>
       </c>
@@ -6268,7 +6907,7 @@
       <c r="G18" s="14">
         <v>10.32</v>
       </c>
-      <c r="H18" s="34"/>
+      <c r="H18" s="51"/>
       <c r="I18" s="12">
         <v>88</v>
       </c>
@@ -6289,7 +6928,7 @@
       <c r="C19" s="16">
         <v>111.79</v>
       </c>
-      <c r="D19" s="34"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="15">
         <v>52</v>
       </c>
@@ -6299,7 +6938,7 @@
       <c r="G19" s="16">
         <v>11.76</v>
       </c>
-      <c r="H19" s="34"/>
+      <c r="H19" s="51"/>
       <c r="I19" s="15">
         <v>89</v>
       </c>
@@ -6320,7 +6959,7 @@
       <c r="C20" s="14">
         <v>6.45</v>
       </c>
-      <c r="D20" s="34"/>
+      <c r="D20" s="51"/>
       <c r="E20" s="12">
         <v>53</v>
       </c>
@@ -6330,7 +6969,7 @@
       <c r="G20" s="14">
         <v>30.61</v>
       </c>
-      <c r="H20" s="34"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="12">
         <v>90</v>
       </c>
@@ -6351,7 +6990,7 @@
       <c r="C21" s="16">
         <v>9.91</v>
       </c>
-      <c r="D21" s="34"/>
+      <c r="D21" s="51"/>
       <c r="E21" s="15">
         <v>54</v>
       </c>
@@ -6361,7 +7000,7 @@
       <c r="G21" s="16">
         <v>26.54</v>
       </c>
-      <c r="H21" s="34"/>
+      <c r="H21" s="51"/>
       <c r="I21" s="15">
         <v>91</v>
       </c>
@@ -6382,7 +7021,7 @@
       <c r="C22" s="14">
         <v>149.94999999999999</v>
       </c>
-      <c r="D22" s="34"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="12">
         <v>55</v>
       </c>
@@ -6392,7 +7031,7 @@
       <c r="G22" s="14">
         <v>13.17</v>
       </c>
-      <c r="H22" s="34"/>
+      <c r="H22" s="51"/>
       <c r="I22" s="12">
         <v>92</v>
       </c>
@@ -6413,7 +7052,7 @@
       <c r="C23" s="16">
         <v>14.81</v>
       </c>
-      <c r="D23" s="34"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="15">
         <v>56</v>
       </c>
@@ -6423,7 +7062,7 @@
       <c r="G23" s="16">
         <v>8.1300000000000008</v>
       </c>
-      <c r="H23" s="34"/>
+      <c r="H23" s="51"/>
       <c r="I23" s="15">
         <v>93</v>
       </c>
@@ -6444,7 +7083,7 @@
       <c r="C24" s="14">
         <v>5.19</v>
       </c>
-      <c r="D24" s="34"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="12">
         <v>57</v>
       </c>
@@ -6454,7 +7093,7 @@
       <c r="G24" s="14">
         <v>27.37</v>
       </c>
-      <c r="H24" s="34"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="12">
         <v>94</v>
       </c>
@@ -6475,7 +7114,7 @@
       <c r="C25" s="16">
         <v>14.79</v>
       </c>
-      <c r="D25" s="34"/>
+      <c r="D25" s="51"/>
       <c r="E25" s="15">
         <v>58</v>
       </c>
@@ -6485,7 +7124,7 @@
       <c r="G25" s="16">
         <v>78.58</v>
       </c>
-      <c r="H25" s="34"/>
+      <c r="H25" s="51"/>
       <c r="I25" s="15">
         <v>95</v>
       </c>
@@ -6506,7 +7145,7 @@
       <c r="C26" s="14">
         <v>3.8</v>
       </c>
-      <c r="D26" s="34"/>
+      <c r="D26" s="51"/>
       <c r="E26" s="12">
         <v>59</v>
       </c>
@@ -6516,7 +7155,7 @@
       <c r="G26" s="14">
         <v>5.09</v>
       </c>
-      <c r="H26" s="34"/>
+      <c r="H26" s="51"/>
       <c r="I26" s="24">
         <v>96</v>
       </c>
@@ -6537,7 +7176,7 @@
       <c r="C27" s="16">
         <v>4.5</v>
       </c>
-      <c r="D27" s="34"/>
+      <c r="D27" s="51"/>
       <c r="E27" s="15">
         <v>60</v>
       </c>
@@ -6547,7 +7186,7 @@
       <c r="G27" s="23">
         <v>11.06</v>
       </c>
-      <c r="H27" s="34"/>
+      <c r="H27" s="51"/>
       <c r="I27" s="15">
         <v>97</v>
       </c>
@@ -6568,7 +7207,7 @@
       <c r="C28" s="14">
         <v>5.67</v>
       </c>
-      <c r="D28" s="34"/>
+      <c r="D28" s="51"/>
       <c r="E28" s="24">
         <v>61</v>
       </c>
@@ -6578,7 +7217,7 @@
       <c r="G28" s="25">
         <v>11.17</v>
       </c>
-      <c r="H28" s="34"/>
+      <c r="H28" s="51"/>
       <c r="I28" s="17"/>
       <c r="J28" s="18" t="s">
         <v>9</v>
@@ -6598,7 +7237,7 @@
       <c r="C29" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="D29" s="34"/>
+      <c r="D29" s="51"/>
       <c r="E29" s="15">
         <v>62</v>
       </c>
@@ -6608,10 +7247,10 @@
       <c r="G29" s="23">
         <v>8.33</v>
       </c>
-      <c r="H29" s="34"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
     </row>
     <row r="30" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
@@ -6623,7 +7262,7 @@
       <c r="C30" s="14">
         <v>39.9</v>
       </c>
-      <c r="D30" s="34"/>
+      <c r="D30" s="51"/>
       <c r="E30" s="24">
         <v>63</v>
       </c>
@@ -6633,12 +7272,12 @@
       <c r="G30" s="25">
         <v>5.6</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="41" t="s">
+      <c r="H30" s="51"/>
+      <c r="I30" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="J30" s="42"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="59"/>
     </row>
     <row r="31" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
@@ -6650,7 +7289,7 @@
       <c r="C31" s="16">
         <v>10.85</v>
       </c>
-      <c r="D31" s="34"/>
+      <c r="D31" s="51"/>
       <c r="E31" s="15">
         <v>64</v>
       </c>
@@ -6660,7 +7299,7 @@
       <c r="G31" s="23">
         <v>6.02</v>
       </c>
-      <c r="H31" s="34"/>
+      <c r="H31" s="51"/>
       <c r="I31" s="27" t="s">
         <v>1</v>
       </c>
@@ -6681,7 +7320,7 @@
       <c r="C32" s="14">
         <v>5.49</v>
       </c>
-      <c r="D32" s="34"/>
+      <c r="D32" s="51"/>
       <c r="E32" s="24">
         <v>65</v>
       </c>
@@ -6691,7 +7330,7 @@
       <c r="G32" s="25">
         <v>37.04</v>
       </c>
-      <c r="H32" s="34"/>
+      <c r="H32" s="51"/>
       <c r="I32" s="15" t="s">
         <v>153</v>
       </c>
@@ -6713,7 +7352,7 @@
       <c r="C33" s="16">
         <v>9.66</v>
       </c>
-      <c r="D33" s="34"/>
+      <c r="D33" s="51"/>
       <c r="E33" s="15">
         <v>66</v>
       </c>
@@ -6723,7 +7362,7 @@
       <c r="G33" s="23">
         <v>6.28</v>
       </c>
-      <c r="H33" s="34"/>
+      <c r="H33" s="51"/>
       <c r="I33" s="17"/>
       <c r="J33" s="18" t="s">
         <v>9</v>
@@ -6743,7 +7382,7 @@
       <c r="C34" s="14">
         <v>6.28</v>
       </c>
-      <c r="D34" s="34"/>
+      <c r="D34" s="51"/>
       <c r="E34" s="24">
         <v>67</v>
       </c>
@@ -6753,10 +7392,10 @@
       <c r="G34" s="25">
         <v>5.98</v>
       </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="49"/>
     </row>
     <row r="35" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
@@ -6768,7 +7407,7 @@
       <c r="C35" s="16">
         <v>5.85</v>
       </c>
-      <c r="D35" s="34"/>
+      <c r="D35" s="51"/>
       <c r="E35" s="15">
         <v>68</v>
       </c>
@@ -6778,10 +7417,10 @@
       <c r="G35" s="23">
         <v>6.34</v>
       </c>
-      <c r="H35" s="34"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
     </row>
     <row r="36" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
@@ -6793,7 +7432,7 @@
       <c r="C36" s="14">
         <v>29</v>
       </c>
-      <c r="D36" s="34"/>
+      <c r="D36" s="51"/>
       <c r="E36" s="12">
         <v>69</v>
       </c>
@@ -6803,10 +7442,10 @@
       <c r="G36" s="14">
         <v>28.97</v>
       </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
     </row>
     <row r="37" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
@@ -6818,7 +7457,7 @@
       <c r="C37" s="16">
         <v>67.27</v>
       </c>
-      <c r="D37" s="34"/>
+      <c r="D37" s="51"/>
       <c r="E37" s="15">
         <v>70</v>
       </c>
@@ -6828,10 +7467,10 @@
       <c r="G37" s="16">
         <v>61.92</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
     </row>
     <row r="38" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
@@ -6843,7 +7482,7 @@
       <c r="C38" s="14">
         <v>60.17</v>
       </c>
-      <c r="D38" s="34"/>
+      <c r="D38" s="51"/>
       <c r="E38" s="12">
         <v>71</v>
       </c>
@@ -6853,10 +7492,10 @@
       <c r="G38" s="14">
         <v>72.55</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="50"/>
     </row>
     <row r="39" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="15">
@@ -6868,7 +7507,7 @@
       <c r="C39" s="16">
         <v>29.3</v>
       </c>
-      <c r="D39" s="34"/>
+      <c r="D39" s="51"/>
       <c r="E39" s="15">
         <v>72</v>
       </c>
@@ -6878,10 +7517,10 @@
       <c r="G39" s="16">
         <v>6.34</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="50"/>
     </row>
     <row r="40" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
@@ -6893,7 +7532,7 @@
       <c r="C40" s="14">
         <v>15.63</v>
       </c>
-      <c r="D40" s="34"/>
+      <c r="D40" s="51"/>
       <c r="E40" s="12">
         <v>73</v>
       </c>
@@ -6903,10 +7542,10 @@
       <c r="G40" s="14">
         <v>28.97</v>
       </c>
-      <c r="H40" s="34"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="50"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="50"/>
     </row>
     <row r="41" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="15">
@@ -6918,7 +7557,7 @@
       <c r="C41" s="16">
         <v>2.1800000000000002</v>
       </c>
-      <c r="D41" s="34"/>
+      <c r="D41" s="51"/>
       <c r="E41" s="15">
         <v>74</v>
       </c>
@@ -6928,10 +7567,10 @@
       <c r="G41" s="16">
         <v>72.760000000000005</v>
       </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
     </row>
     <row r="42" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
@@ -6943,7 +7582,7 @@
       <c r="C42" s="14">
         <v>2.57</v>
       </c>
-      <c r="D42" s="34"/>
+      <c r="D42" s="51"/>
       <c r="E42" s="12">
         <v>75</v>
       </c>
@@ -6953,10 +7592,10 @@
       <c r="G42" s="14">
         <v>6.35</v>
       </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="50"/>
+      <c r="K42" s="50"/>
     </row>
     <row r="43" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A43" s="15">
@@ -6968,7 +7607,7 @@
       <c r="C43" s="16">
         <v>2.84</v>
       </c>
-      <c r="D43" s="34"/>
+      <c r="D43" s="51"/>
       <c r="E43" s="17"/>
       <c r="F43" s="18" t="s">
         <v>9</v>
@@ -6977,10 +7616,10 @@
         <f>SUM(G6:G42)</f>
         <v>1417.3899999999994</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
     </row>
     <row r="44" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
@@ -6991,14 +7630,14 @@
         <f>SUM(C6:C43)</f>
         <v>1174.6799999999998</v>
       </c>
-      <c r="D44" s="34"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="49"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -7020,7 +7659,105 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="3" max="3" width="45.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A3" s="46">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A4" s="46">
+        <v>2</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <v>455.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E8">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9">
+        <v>11.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -7043,36 +7780,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7084,18 +7821,18 @@
       <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="39" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55" t="s">
         <v>161</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -7105,17 +7842,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -7127,7 +7864,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="36"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -7137,7 +7874,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="34"/>
+      <c r="H5" s="51"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -7158,7 +7895,7 @@
       <c r="C6" s="14">
         <v>5.1100000000000003</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="12">
         <v>14</v>
       </c>
@@ -7168,7 +7905,7 @@
       <c r="G6" s="14">
         <v>5.19</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="12">
         <v>30</v>
       </c>
@@ -7189,7 +7926,7 @@
       <c r="C7" s="16">
         <v>5.51</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="30">
         <v>15</v>
       </c>
@@ -7199,7 +7936,7 @@
       <c r="G7" s="16">
         <v>11.2</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="30">
         <v>31</v>
       </c>
@@ -7220,7 +7957,7 @@
       <c r="C8" s="14">
         <v>10.08</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="12">
         <v>16</v>
       </c>
@@ -7230,7 +7967,7 @@
       <c r="G8" s="14">
         <v>11.31</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="12">
         <v>32</v>
       </c>
@@ -7251,7 +7988,7 @@
       <c r="C9" s="16">
         <v>149.28</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="30">
         <v>17</v>
       </c>
@@ -7261,7 +7998,7 @@
       <c r="G9" s="16">
         <v>26.54</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="30">
         <v>33</v>
       </c>
@@ -7282,7 +8019,7 @@
       <c r="C10" s="14">
         <v>15.01</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="12">
         <v>18</v>
       </c>
@@ -7292,7 +8029,7 @@
       <c r="G10" s="14">
         <v>13.17</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="12">
         <v>34</v>
       </c>
@@ -7313,7 +8050,7 @@
       <c r="C11" s="23">
         <v>5.22</v>
       </c>
-      <c r="D11" s="34"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="30">
         <v>19</v>
       </c>
@@ -7323,7 +8060,7 @@
       <c r="G11" s="16">
         <v>8.19</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="30">
         <v>35</v>
       </c>
@@ -7344,7 +8081,7 @@
       <c r="C12" s="25">
         <v>15</v>
       </c>
-      <c r="D12" s="34"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="12">
         <v>20</v>
       </c>
@@ -7354,7 +8091,7 @@
       <c r="G12" s="14">
         <v>27.38</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="12">
         <v>36</v>
       </c>
@@ -7375,7 +8112,7 @@
       <c r="C13" s="23">
         <v>6.27</v>
       </c>
-      <c r="D13" s="34"/>
+      <c r="D13" s="51"/>
       <c r="E13" s="30">
         <v>21</v>
       </c>
@@ -7385,7 +8122,7 @@
       <c r="G13" s="23">
         <v>10.44</v>
       </c>
-      <c r="H13" s="34"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="17"/>
       <c r="J13" s="18" t="s">
         <v>9</v>
@@ -7405,7 +8142,7 @@
       <c r="C14" s="25">
         <v>5.98</v>
       </c>
-      <c r="D14" s="34"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="12">
         <v>22</v>
       </c>
@@ -7415,10 +8152,10 @@
       <c r="G14" s="25">
         <v>11.73</v>
       </c>
-      <c r="H14" s="34"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
     </row>
     <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
@@ -7430,7 +8167,7 @@
       <c r="C15" s="23">
         <v>59.38</v>
       </c>
-      <c r="D15" s="34"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="30">
         <v>23</v>
       </c>
@@ -7440,10 +8177,10 @@
       <c r="G15" s="23">
         <v>30.61</v>
       </c>
-      <c r="H15" s="34"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
     </row>
     <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
@@ -7455,7 +8192,7 @@
       <c r="C16" s="25">
         <v>16.399999999999999</v>
       </c>
-      <c r="D16" s="34"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="12">
         <v>24</v>
       </c>
@@ -7465,10 +8202,10 @@
       <c r="G16" s="25">
         <v>15</v>
       </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="50"/>
     </row>
     <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
@@ -7480,7 +8217,7 @@
       <c r="C17" s="23">
         <v>29.22</v>
       </c>
-      <c r="D17" s="34"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="30">
         <v>25</v>
       </c>
@@ -7490,10 +8227,10 @@
       <c r="G17" s="23">
         <v>14.98</v>
       </c>
-      <c r="H17" s="34"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50"/>
     </row>
     <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
@@ -7505,7 +8242,7 @@
       <c r="C18" s="25">
         <v>29.54</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="12">
         <v>26</v>
       </c>
@@ -7515,10 +8252,10 @@
       <c r="G18" s="25">
         <v>5.23</v>
       </c>
-      <c r="H18" s="34"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="50"/>
     </row>
     <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
@@ -7529,7 +8266,7 @@
         <f>SUM(C6:C18)</f>
         <v>352.00000000000006</v>
       </c>
-      <c r="D19" s="34"/>
+      <c r="D19" s="51"/>
       <c r="E19" s="30">
         <v>27</v>
       </c>
@@ -7539,16 +8276,16 @@
       <c r="G19" s="23">
         <v>6.27</v>
       </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
     </row>
     <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="34"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="51"/>
       <c r="E20" s="12">
         <v>28</v>
       </c>
@@ -7558,16 +8295,16 @@
       <c r="G20" s="25">
         <v>29.19</v>
       </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
     </row>
     <row r="21" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
+      <c r="A21" s="50"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="51"/>
       <c r="E21" s="30">
         <v>29</v>
       </c>
@@ -7577,16 +8314,16 @@
       <c r="G21" s="23">
         <v>29.2</v>
       </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34"/>
+      <c r="A22" s="50"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18" t="s">
         <v>9</v>
@@ -7595,10 +8332,10 @@
         <f>SUM(G6:G21)</f>
         <v>255.62999999999997</v>
       </c>
-      <c r="H22" s="34"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7617,7 +8354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -7640,36 +8377,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
@@ -7681,18 +8418,18 @@
       <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="39" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
@@ -7702,17 +8439,17 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -7724,7 +8461,7 @@
       <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="36"/>
+      <c r="D5" s="53"/>
       <c r="E5" s="6" t="s">
         <v>1</v>
       </c>
@@ -7734,7 +8471,7 @@
       <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="34"/>
+      <c r="H5" s="51"/>
       <c r="I5" s="9" t="s">
         <v>1</v>
       </c>
@@ -7755,7 +8492,7 @@
       <c r="C6" s="14">
         <v>44.29</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="12">
         <v>5</v>
       </c>
@@ -7765,7 +8502,7 @@
       <c r="G6" s="14">
         <v>53.5</v>
       </c>
-      <c r="H6" s="34"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="12">
         <v>11</v>
       </c>
@@ -7786,7 +8523,7 @@
       <c r="C7" s="16">
         <v>47.34</v>
       </c>
-      <c r="D7" s="34"/>
+      <c r="D7" s="51"/>
       <c r="E7" s="15">
         <v>6</v>
       </c>
@@ -7796,7 +8533,7 @@
       <c r="G7" s="16">
         <v>74.430000000000007</v>
       </c>
-      <c r="H7" s="34"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="15">
         <v>12</v>
       </c>
@@ -7817,7 +8554,7 @@
       <c r="C8" s="14">
         <v>54.22</v>
       </c>
-      <c r="D8" s="34"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="12">
         <v>7</v>
       </c>
@@ -7827,7 +8564,7 @@
       <c r="G8" s="14">
         <v>53.83</v>
       </c>
-      <c r="H8" s="34"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="12">
         <v>13</v>
       </c>
@@ -7848,7 +8585,7 @@
       <c r="C9" s="16">
         <v>129.11000000000001</v>
       </c>
-      <c r="D9" s="34"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="15">
         <v>8</v>
       </c>
@@ -7858,7 +8595,7 @@
       <c r="G9" s="16">
         <v>55.33</v>
       </c>
-      <c r="H9" s="34"/>
+      <c r="H9" s="51"/>
       <c r="I9" s="15">
         <v>14</v>
       </c>
@@ -7878,7 +8615,7 @@
         <f>SUM(C6:C9)</f>
         <v>274.96000000000004</v>
       </c>
-      <c r="D10" s="34"/>
+      <c r="D10" s="51"/>
       <c r="E10" s="12">
         <v>9</v>
       </c>
@@ -7888,7 +8625,7 @@
       <c r="G10" s="14">
         <v>54.25</v>
       </c>
-      <c r="H10" s="34"/>
+      <c r="H10" s="51"/>
       <c r="I10" s="12">
         <v>15</v>
       </c>
@@ -7900,10 +8637,10 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="34"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="51"/>
       <c r="E11" s="15">
         <v>10</v>
       </c>
@@ -7913,7 +8650,7 @@
       <c r="G11" s="16">
         <v>54.3</v>
       </c>
-      <c r="H11" s="34"/>
+      <c r="H11" s="51"/>
       <c r="I11" s="15">
         <v>16</v>
       </c>
@@ -7925,10 +8662,10 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="34"/>
+      <c r="A12" s="50"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="50"/>
+      <c r="D12" s="51"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18" t="s">
         <v>9</v>
@@ -7937,7 +8674,7 @@
         <f>SUM(G6:G11)</f>
         <v>345.64</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="51"/>
       <c r="I12" s="12">
         <v>17</v>
       </c>
@@ -7949,14 +8686,14 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="34"/>
+      <c r="A13" s="50"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="15">
         <v>18</v>
       </c>
@@ -7968,14 +8705,14 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="34"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="12">
         <v>19</v>
       </c>
@@ -7987,14 +8724,14 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="34"/>
+      <c r="A15" s="50"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="51"/>
       <c r="I15" s="15">
         <v>20</v>
       </c>
@@ -8006,14 +8743,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="34"/>
+      <c r="A16" s="50"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="51"/>
       <c r="I16" s="17"/>
       <c r="J16" s="18" t="s">
         <v>9</v>
@@ -8038,4 +8775,789 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="3" max="3" width="45.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A3" s="46">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>104.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A4" s="46">
+        <v>2</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A5" s="46">
+        <v>3</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5">
+        <v>13.58</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.88671875" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A3" s="45">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>325.39999999999998</v>
+      </c>
+      <c r="G3">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+      <c r="A4" s="45">
+        <v>2</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <v>291.22000000000003</v>
+      </c>
+      <c r="G4">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A5" s="45">
+        <v>3</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5">
+        <v>34.049999999999997</v>
+      </c>
+      <c r="G5">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A6" s="45">
+        <v>4</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="5">
+        <v>197.66300000000001</v>
+      </c>
+      <c r="G6">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A7" s="45">
+        <v>5</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="5">
+        <v>39.417000000000002</v>
+      </c>
+      <c r="G7">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A8" s="45">
+        <v>6</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="5">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="G8">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A9" s="45">
+        <v>7</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="G9">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A10" s="45">
+        <v>8</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="5">
+        <v>13.5</v>
+      </c>
+      <c r="G10">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+      <c r="A11" s="45">
+        <v>9</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="5">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="G11">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E15">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <v>169.7</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <v>37.700000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <v>80.900000000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="3" max="3" width="45.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A3" s="46">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>66.17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>997.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3648.56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5">
+        <v>345.68</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.21875" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="36" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>894.84</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5546875" customWidth="1"/>
+    <col min="3" max="3" width="50.109375" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A3" s="45">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>303.92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="45">
+        <v>2</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3849.47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+      <c r="A5" s="45">
+        <v>3</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5">
+        <v>66.17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="135.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="38">
+        <v>1</v>
+      </c>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40">
+        <v>1548.3</v>
+      </c>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42">
+        <v>104.1</v>
+      </c>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="44">
+        <v>104.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>547.70000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>417.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>